--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2095E53-1B42-6447-ACE4-E43E46711CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB963BEB-474F-6649-A5EF-77A2C2D93A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1280" yWindow="920" windowWidth="29160" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="238">
   <si>
     <t>Surname</t>
   </si>
@@ -738,6 +738,18 @@
   </si>
   <si>
     <t>H250194E</t>
+  </si>
+  <si>
+    <t>Tsikai</t>
+  </si>
+  <si>
+    <t>H230565Q</t>
+  </si>
+  <si>
+    <t>Zivanai</t>
+  </si>
+  <si>
+    <t>H230224E</t>
   </si>
 </sst>
 </file>
@@ -889,7 +901,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -910,11 +922,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -961,7 +977,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M228" totalsRowShown="0">
   <autoFilter ref="A1:M228" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M228">
-    <sortCondition ref="A1:A228"/>
+    <sortCondition ref="C1:C228"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -1362,14 +1378,16 @@
       <c r="G2">
         <v>0.32</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="M2" s="18"/>
+      <c r="H2" s="5">
+        <v>0.66</v>
+      </c>
+      <c r="M2" s="17"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="18" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
@@ -1379,14 +1397,16 @@
       <c r="G3">
         <v>0.64</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="M3" s="18"/>
+      <c r="H3" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="19" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -1396,14 +1416,16 @@
       <c r="G4">
         <v>0.41</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="M4" s="18"/>
+      <c r="H4" s="5">
+        <v>0.63</v>
+      </c>
+      <c r="M4" s="17"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="15" t="s">
@@ -1413,8 +1435,10 @@
       <c r="G5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="M5" s="18"/>
+      <c r="H5" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="8" t="s">
@@ -1430,7 +1454,9 @@
       <c r="G6">
         <v>0.59</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="5">
+        <v>0.8</v>
+      </c>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13">
@@ -1447,7 +1473,9 @@
       <c r="G7">
         <v>0.34</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="5">
+        <v>0.73</v>
+      </c>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
@@ -1464,7 +1492,9 @@
       <c r="G8">
         <v>0.3</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="5">
+        <v>0.54</v>
+      </c>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
@@ -1481,7 +1511,9 @@
       <c r="G9">
         <v>0.43</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="5">
+        <v>0.68</v>
+      </c>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
@@ -1498,7 +1530,9 @@
       <c r="G10">
         <v>0.48</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="5">
+        <v>0.61</v>
+      </c>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13">
@@ -1515,7 +1549,9 @@
       <c r="G11">
         <v>0.73</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="5">
+        <v>0.68</v>
+      </c>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13">
@@ -1532,7 +1568,9 @@
       <c r="G12">
         <v>0.45</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="5">
+        <v>0.92</v>
+      </c>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13">
@@ -1549,7 +1587,9 @@
       <c r="G13">
         <v>0.59</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="5">
+        <v>0.54</v>
+      </c>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13">
@@ -1566,7 +1606,9 @@
       <c r="G14">
         <v>0.27</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="5">
+        <v>0.61</v>
+      </c>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13">
@@ -1583,7 +1625,9 @@
       <c r="G15">
         <v>0.2</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="5">
+        <v>0.63</v>
+      </c>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13">
@@ -1600,7 +1644,9 @@
       <c r="G16">
         <v>0.36</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="5">
+        <v>0.44</v>
+      </c>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
@@ -1617,7 +1663,9 @@
       <c r="G17">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H17" s="5"/>
+      <c r="H17" s="5">
+        <v>0.83</v>
+      </c>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13">
@@ -1634,7 +1682,9 @@
       <c r="G18">
         <v>0.41</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="H18" s="5">
+        <v>0.74</v>
+      </c>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
@@ -1651,7 +1701,9 @@
       <c r="G19">
         <v>0.32</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
@@ -1668,7 +1720,9 @@
       <c r="G20">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="5">
+        <v>0.78</v>
+      </c>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
@@ -1685,7 +1739,9 @@
       <c r="G21">
         <v>0.61</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="5">
+        <v>0.9</v>
+      </c>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
@@ -1702,7 +1758,9 @@
       <c r="G22">
         <v>0.39</v>
       </c>
-      <c r="H22" s="5"/>
+      <c r="H22" s="5">
+        <v>0.68</v>
+      </c>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
@@ -1719,7 +1777,9 @@
       <c r="G23">
         <v>0.23</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="5">
+        <v>0.68</v>
+      </c>
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
@@ -1736,7 +1796,9 @@
       <c r="G24">
         <v>0.45</v>
       </c>
-      <c r="H24" s="5"/>
+      <c r="H24" s="5">
+        <v>0.78</v>
+      </c>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
@@ -1753,7 +1815,9 @@
       <c r="G25">
         <v>0.41</v>
       </c>
-      <c r="H25" s="5"/>
+      <c r="H25" s="5">
+        <v>0.76</v>
+      </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
@@ -1770,7 +1834,9 @@
       <c r="G26">
         <v>0.3</v>
       </c>
-      <c r="H26" s="5"/>
+      <c r="H26" s="5">
+        <v>0.61</v>
+      </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
@@ -1787,7 +1853,9 @@
       <c r="G27">
         <v>0.3</v>
       </c>
-      <c r="H27" s="5"/>
+      <c r="H27" s="5">
+        <v>0.63</v>
+      </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
@@ -1804,7 +1872,9 @@
       <c r="G28">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H28" s="5"/>
+      <c r="H28" s="5">
+        <v>0.61</v>
+      </c>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
@@ -1821,7 +1891,9 @@
       <c r="G29">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="5">
+        <v>0.76</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -1838,7 +1910,9 @@
       <c r="G30">
         <v>0.5</v>
       </c>
-      <c r="H30" s="5"/>
+      <c r="H30" s="5">
+        <v>0.68</v>
+      </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
@@ -1855,7 +1929,9 @@
       <c r="G31">
         <v>0.32</v>
       </c>
-      <c r="H31" s="5"/>
+      <c r="H31" s="5">
+        <v>0.81</v>
+      </c>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
@@ -1872,7 +1948,9 @@
       <c r="G32">
         <v>0.36</v>
       </c>
-      <c r="H32" s="5"/>
+      <c r="H32" s="5">
+        <v>0.39</v>
+      </c>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13">
@@ -1889,7 +1967,9 @@
       <c r="G33">
         <v>0.23</v>
       </c>
-      <c r="H33" s="5"/>
+      <c r="H33" s="5">
+        <v>0.48</v>
+      </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
@@ -1906,6 +1986,9 @@
       <c r="G34">
         <v>0.52</v>
       </c>
+      <c r="H34" s="4">
+        <v>0.52</v>
+      </c>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="1:13">
@@ -1922,7 +2005,9 @@
       <c r="G35">
         <v>0</v>
       </c>
-      <c r="H35" s="5"/>
+      <c r="H35" s="5">
+        <v>0.74</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
@@ -1939,7 +2024,9 @@
       <c r="G36">
         <v>0.39</v>
       </c>
-      <c r="H36" s="5"/>
+      <c r="H36" s="5">
+        <v>0.76</v>
+      </c>
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="1:13">
@@ -1956,6 +2043,9 @@
       <c r="G37">
         <v>0.45</v>
       </c>
+      <c r="H37" s="4">
+        <v>0.61</v>
+      </c>
       <c r="M37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20">
@@ -1972,7 +2062,9 @@
       <c r="G38">
         <v>0.34</v>
       </c>
-      <c r="H38" s="5"/>
+      <c r="H38" s="5">
+        <v>0.7</v>
+      </c>
       <c r="M38" s="6"/>
     </row>
     <row r="39" spans="1:13">
@@ -1989,7 +2081,9 @@
       <c r="G39">
         <v>0.77</v>
       </c>
-      <c r="H39" s="5"/>
+      <c r="H39" s="5">
+        <v>0.52</v>
+      </c>
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13">
@@ -2006,7 +2100,9 @@
       <c r="G40">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H40" s="5"/>
+      <c r="H40" s="5">
+        <v>0.83</v>
+      </c>
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13">
@@ -2023,7 +2119,9 @@
       <c r="G41">
         <v>0.59</v>
       </c>
-      <c r="H41" s="5"/>
+      <c r="H41" s="5">
+        <v>0.85</v>
+      </c>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
@@ -2040,7 +2138,9 @@
       <c r="G42">
         <v>0.52</v>
       </c>
-      <c r="H42" s="5"/>
+      <c r="H42" s="5">
+        <v>0.59</v>
+      </c>
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
@@ -2057,7 +2157,9 @@
       <c r="G43">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H43" s="5"/>
+      <c r="H43" s="5">
+        <v>0.74</v>
+      </c>
       <c r="M43" s="6"/>
     </row>
     <row r="44" spans="1:13">
@@ -2074,7 +2176,9 @@
       <c r="G44">
         <v>0.36</v>
       </c>
-      <c r="H44" s="5"/>
+      <c r="H44" s="5">
+        <v>0.44</v>
+      </c>
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
@@ -2091,7 +2195,9 @@
       <c r="G45">
         <v>0.68</v>
       </c>
-      <c r="H45" s="5"/>
+      <c r="H45" s="5">
+        <v>0.78</v>
+      </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
@@ -2108,7 +2214,9 @@
       <c r="G46">
         <v>0.5</v>
       </c>
-      <c r="H46" s="5"/>
+      <c r="H46" s="5">
+        <v>0.83</v>
+      </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
@@ -2125,7 +2233,9 @@
       <c r="G47">
         <v>0.52</v>
       </c>
-      <c r="H47" s="5"/>
+      <c r="H47" s="5">
+        <v>0.85</v>
+      </c>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
@@ -2142,7 +2252,9 @@
       <c r="G48">
         <v>0.52</v>
       </c>
-      <c r="H48" s="5"/>
+      <c r="H48" s="5">
+        <v>0.68</v>
+      </c>
       <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13">
@@ -2159,7 +2271,9 @@
       <c r="G49">
         <v>0.39</v>
       </c>
-      <c r="H49" s="5"/>
+      <c r="H49" s="5">
+        <v>0.7</v>
+      </c>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
@@ -2176,7 +2290,9 @@
       <c r="G50">
         <v>0.23</v>
       </c>
-      <c r="H50" s="5"/>
+      <c r="H50" s="5">
+        <v>0.7</v>
+      </c>
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
@@ -2193,205 +2309,214 @@
       <c r="G51">
         <v>0.66</v>
       </c>
-      <c r="H51" s="5"/>
+      <c r="H51" s="5">
+        <v>0.88</v>
+      </c>
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="11" t="s">
-        <v>113</v>
+        <v>234</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>114</v>
+        <v>235</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D52" s="11"/>
       <c r="G52">
-        <v>0.45</v>
-      </c>
-      <c r="H52" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="H52" s="4">
+        <v>0.63</v>
+      </c>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D53" s="11"/>
       <c r="G53">
-        <v>0.34</v>
-      </c>
-      <c r="H53" s="5"/>
+        <v>0.45</v>
+      </c>
+      <c r="H53" s="5">
+        <v>0.88</v>
+      </c>
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>15</v>
       </c>
       <c r="D54" s="11"/>
       <c r="G54">
-        <v>0.5</v>
+        <v>0.34</v>
+      </c>
+      <c r="H54" s="5">
+        <v>0.49</v>
       </c>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="11" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="D55" s="11"/>
       <c r="G55">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="H55" s="4">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="11" t="s">
-        <v>122</v>
+        <v>236</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>123</v>
+        <v>237</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="D56" s="11"/>
       <c r="G56">
-        <v>0.69</v>
+        <v>0</v>
       </c>
       <c r="H56" s="4">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="11" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D57" s="11"/>
       <c r="G57">
-        <v>0.56000000000000005</v>
+        <v>0.45</v>
       </c>
       <c r="H57" s="4">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D58" s="11"/>
       <c r="G58">
-        <v>0</v>
+        <v>0.69</v>
       </c>
       <c r="H58" s="4">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>129</v>
+      <c r="A59" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>125</v>
       </c>
       <c r="C59" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D59" s="11"/>
       <c r="G59">
-        <v>0.47</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H59" s="4">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>131</v>
+      <c r="A60" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>127</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D60" s="11"/>
       <c r="G60">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="H60" s="4">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>133</v>
+      <c r="A61" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>129</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D61" s="11"/>
       <c r="G61">
-        <v>0.56000000000000005</v>
+        <v>0.47</v>
       </c>
       <c r="H61" s="4">
-        <v>0.31</v>
+        <v>0.65</v>
       </c>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>135</v>
+      <c r="A62" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D62" s="11"/>
       <c r="G62">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H62" s="4">
         <v>0</v>
@@ -2399,94 +2524,94 @@
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>137</v>
+      <c r="A63" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>133</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D63" s="11"/>
       <c r="G63">
-        <v>0.6</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H63" s="4">
-        <v>0.71</v>
+        <v>0.31</v>
       </c>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>139</v>
+      <c r="A64" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>135</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D64" s="11"/>
       <c r="G64">
-        <v>0.56000000000000005</v>
+        <v>0</v>
       </c>
       <c r="H64" s="4">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>141</v>
+      <c r="A65" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>137</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D65" s="11"/>
       <c r="G65">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H65" s="4">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>143</v>
+      <c r="A66" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>139</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D66" s="11"/>
       <c r="G66">
-        <v>0.27</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H66" s="4">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>145</v>
+      <c r="A67" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>141</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D67" s="11"/>
       <c r="G67">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="H67" s="4">
         <v>0</v>
@@ -2494,94 +2619,94 @@
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>147</v>
+      <c r="A68" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>143</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D68" s="11"/>
       <c r="G68">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
       <c r="H68" s="4">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>149</v>
+      <c r="A69" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>145</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D69" s="11"/>
       <c r="G69">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="H69" s="4">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>151</v>
+      <c r="A70" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>147</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D70" s="11"/>
       <c r="G70">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H70" s="4">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>153</v>
+      <c r="A71" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>149</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D71" s="11"/>
       <c r="G71">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H71" s="4">
-        <v>0.28999999999999998</v>
+        <v>0.63</v>
       </c>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>154</v>
+      <c r="A72" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>151</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D72" s="11"/>
       <c r="G72">
-        <v>0.28000000000000003</v>
+        <v>0.4</v>
       </c>
       <c r="H72" s="4">
         <v>0.31</v>
@@ -2589,448 +2714,448 @@
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>156</v>
+      <c r="A73" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>153</v>
       </c>
       <c r="C73" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D73" s="11"/>
       <c r="G73">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="H73" s="4">
-        <v>0.57999999999999996</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
-      <c r="A74" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>158</v>
+      <c r="A74" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>154</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D74" s="11"/>
       <c r="G74">
-        <v>0.57999999999999996</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H74" s="4">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>160</v>
+      <c r="A75" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="C75" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D75" s="11"/>
       <c r="G75">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="H75" s="4">
-        <v>0</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>162</v>
+      <c r="A76" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>158</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D76" s="11"/>
       <c r="G76">
-        <v>0.28999999999999998</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H76" s="4">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>164</v>
+      <c r="A77" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>160</v>
       </c>
       <c r="C77" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D77" s="11"/>
       <c r="G77">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="H77" s="4">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
-      <c r="A78" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>166</v>
+      <c r="A78" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B78" s="20" t="s">
+        <v>162</v>
       </c>
       <c r="C78" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D78" s="11"/>
       <c r="G78">
-        <v>0.08</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H78" s="4">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>168</v>
+      <c r="A79" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>164</v>
       </c>
       <c r="C79" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D79" s="11"/>
       <c r="G79">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="H79" s="4">
-        <v>0.56000000000000005</v>
+        <v>0.88</v>
       </c>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
-      <c r="A80" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>170</v>
+      <c r="A80" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B80" s="20" t="s">
+        <v>166</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D80" s="11"/>
       <c r="G80">
-        <v>0.46</v>
+        <v>0.08</v>
       </c>
       <c r="H80" s="4">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
-      <c r="A81" t="s">
-        <v>171</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C81" t="s">
-        <v>121</v>
-      </c>
-      <c r="D81" s="4"/>
+      <c r="A81" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D81" s="11"/>
       <c r="G81">
-        <v>0.4</v>
+        <v>0.72</v>
       </c>
       <c r="H81" s="4">
-        <v>0.31</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
-      <c r="A82" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>174</v>
+      <c r="A82" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>170</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D82" s="11"/>
       <c r="G82">
-        <v>0.15</v>
+        <v>0.46</v>
       </c>
       <c r="H82" s="4">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
-      <c r="A83" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" s="11"/>
+      <c r="A83" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C83" t="s">
+        <v>121</v>
+      </c>
+      <c r="D83" s="4"/>
       <c r="G83">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H83" s="4">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="11" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D84" s="11"/>
       <c r="G84">
-        <v>0.59</v>
+        <v>0.15</v>
       </c>
       <c r="H84" s="4">
-        <v>0.46</v>
+        <v>0.35</v>
       </c>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="11" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C85" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D85" s="11"/>
       <c r="G85">
-        <v>0.59</v>
+        <v>0.37</v>
       </c>
       <c r="H85" s="4">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C86" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D86" s="11"/>
       <c r="G86">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H86" s="4">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="11" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C87" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D87" s="11"/>
       <c r="G87">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="H87" s="4">
-        <v>0.83</v>
+        <v>0.44</v>
       </c>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D88" s="11"/>
       <c r="G88">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="H88" s="4">
-        <v>0.67</v>
+        <v>0.52</v>
       </c>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="11" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D89" s="11"/>
       <c r="G89">
-        <v>0.56000000000000005</v>
+        <v>0.65</v>
       </c>
       <c r="H89" s="4">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="11" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D90" s="11"/>
       <c r="G90">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="H90" s="4">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C91" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D91" s="11"/>
       <c r="G91">
-        <v>0.53</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H91" s="4">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="11" t="s">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D92" s="11"/>
       <c r="G92">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="H92" s="4">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="11" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D93" s="11"/>
       <c r="G93">
-        <v>0.63</v>
+        <v>0.53</v>
       </c>
       <c r="H93" s="4">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="11" t="s">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D94" s="11"/>
       <c r="G94">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="H94" s="4">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="11" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C95" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D95" s="11"/>
       <c r="G95">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="H95" s="4">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>121</v>
@@ -3046,335 +3171,359 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="11" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C97" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D97" s="11"/>
       <c r="G97">
-        <v>0.62</v>
+        <v>0.51</v>
       </c>
       <c r="H97" s="4">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="11" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C98" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D98" s="11"/>
       <c r="G98">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="H98" s="4">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="11" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C99" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D99" s="11"/>
       <c r="G99">
-        <v>0.19</v>
+        <v>0.62</v>
       </c>
       <c r="H99" s="4">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="11" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D100" s="11"/>
       <c r="G100">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="H100" s="4">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="11" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D101" s="11"/>
       <c r="G101">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="H101" s="4">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="11" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D102" s="11"/>
       <c r="G102">
-        <v>0.32</v>
+        <v>0.72</v>
       </c>
       <c r="H102" s="4">
-        <v>0.44</v>
+        <v>0.79</v>
       </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="11" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C103" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D103" s="11"/>
       <c r="G103">
-        <v>0.44</v>
+        <v>0.33</v>
       </c>
       <c r="H103" s="4">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="11" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C104" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D104" s="11"/>
       <c r="G104">
-        <v>0.59</v>
+        <v>0.32</v>
       </c>
       <c r="H104" s="4">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D105" s="11"/>
       <c r="G105">
-        <v>0.57999999999999996</v>
+        <v>0.44</v>
       </c>
       <c r="H105" s="4">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D106" s="11"/>
       <c r="G106">
-        <v>0.47</v>
+        <v>0.59</v>
       </c>
       <c r="H106" s="4">
-        <v>0.28999999999999998</v>
+        <v>0.42</v>
       </c>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C107" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D107" s="11"/>
       <c r="G107">
-        <v>0.54</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H107" s="4">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="11" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D108" s="11"/>
       <c r="G108">
-        <v>0.63</v>
+        <v>0.47</v>
       </c>
       <c r="H108" s="4">
-        <v>0.83</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="11" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C109" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D109" s="11"/>
       <c r="G109">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="H109" s="4">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="11" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D110" s="11"/>
       <c r="G110">
-        <v>0.49</v>
+        <v>0.63</v>
       </c>
       <c r="H110" s="4">
-        <v>0.46</v>
+        <v>0.83</v>
       </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D111" s="11"/>
       <c r="G111">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="H111" s="4">
-        <v>0.44</v>
+        <v>0.79</v>
       </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="11" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D112" s="11"/>
       <c r="G112">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="H112" s="4">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
-      <c r="A113" s="11"/>
-      <c r="B113" s="11"/>
+      <c r="A113" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>231</v>
+      </c>
       <c r="C113" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D113" s="11"/>
       <c r="G113">
+        <v>0.54</v>
+      </c>
+      <c r="H113" s="4">
+        <v>0.44</v>
+      </c>
+      <c r="M113" s="6"/>
+    </row>
+    <row r="114" spans="1:13">
+      <c r="A114" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D114" s="11"/>
+      <c r="G114">
+        <v>0.51</v>
+      </c>
+      <c r="H114" s="4">
         <v>0</v>
       </c>
-      <c r="H113" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="M113" s="6"/>
-    </row>
-    <row r="114" spans="1:13">
-      <c r="A114" s="11"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="11"/>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="11"/>
       <c r="B115" s="11"/>
-      <c r="C115" s="11"/>
+      <c r="C115" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D115" s="11"/>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115" s="4">
+        <v>0.1</v>
+      </c>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB963BEB-474F-6649-A5EF-77A2C2D93A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947DCD1A-94BD-AF4A-912F-D2CA60776626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="920" windowWidth="29160" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1280" yWindow="920" windowWidth="11160" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="239">
   <si>
     <t>Surname</t>
   </si>
@@ -750,6 +750,9 @@
   </si>
   <si>
     <t>H230224E</t>
+  </si>
+  <si>
+    <t>Samakande</t>
   </si>
 </sst>
 </file>
@@ -2419,12 +2422,17 @@
       <c r="C57" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D57" s="11"/>
+      <c r="D57" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G57">
         <v>0.45</v>
       </c>
       <c r="H57" s="4">
         <v>0.48</v>
+      </c>
+      <c r="I57">
+        <v>0.76</v>
       </c>
       <c r="M57" s="6"/>
     </row>
@@ -2438,12 +2446,17 @@
       <c r="C58" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D58" s="11"/>
+      <c r="D58" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G58">
         <v>0.69</v>
       </c>
       <c r="H58" s="4">
         <v>0.65</v>
+      </c>
+      <c r="I58">
+        <v>0.5</v>
       </c>
       <c r="M58" s="6"/>
     </row>
@@ -2457,12 +2470,17 @@
       <c r="C59" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D59" s="11"/>
+      <c r="D59" s="11">
+        <v>0.81</v>
+      </c>
       <c r="G59">
         <v>0.56000000000000005</v>
       </c>
       <c r="H59" s="4">
         <v>0.54</v>
+      </c>
+      <c r="I59">
+        <v>0.6</v>
       </c>
       <c r="M59" s="6"/>
     </row>
@@ -2476,12 +2494,17 @@
       <c r="C60" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D60" s="11"/>
+      <c r="D60" s="11">
+        <v>0.95</v>
+      </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60" s="4">
         <v>0.46</v>
+      </c>
+      <c r="I60">
+        <v>0.71</v>
       </c>
       <c r="M60" s="6"/>
     </row>
@@ -2495,12 +2518,17 @@
       <c r="C61" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D61" s="11"/>
+      <c r="D61" s="11">
+        <v>0.9</v>
+      </c>
       <c r="G61">
         <v>0.47</v>
       </c>
       <c r="H61" s="4">
         <v>0.65</v>
+      </c>
+      <c r="I61">
+        <v>0.46</v>
       </c>
       <c r="M61" s="6"/>
     </row>
@@ -2514,12 +2542,17 @@
       <c r="C62" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D62" s="11"/>
+      <c r="D62" s="11">
+        <v>0.9</v>
+      </c>
       <c r="G62">
         <v>0.45</v>
       </c>
       <c r="H62" s="4">
         <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0.44</v>
       </c>
       <c r="M62" s="6"/>
     </row>
@@ -2533,12 +2566,17 @@
       <c r="C63" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D63" s="11"/>
+      <c r="D63" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G63">
         <v>0.56000000000000005</v>
       </c>
       <c r="H63" s="4">
         <v>0.31</v>
+      </c>
+      <c r="I63">
+        <v>0.69</v>
       </c>
       <c r="M63" s="6"/>
     </row>
@@ -2552,11 +2590,16 @@
       <c r="C64" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D64" s="11"/>
+      <c r="D64" s="11">
+        <v>0</v>
+      </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64" s="4">
+        <v>0</v>
+      </c>
+      <c r="I64">
         <v>0</v>
       </c>
       <c r="M64" s="6"/>
@@ -2571,12 +2614,17 @@
       <c r="C65" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D65" s="11"/>
+      <c r="D65" s="11">
+        <v>0.89</v>
+      </c>
       <c r="G65">
         <v>0.6</v>
       </c>
       <c r="H65" s="4">
         <v>0.71</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
       </c>
       <c r="M65" s="6"/>
     </row>
@@ -2590,12 +2638,17 @@
       <c r="C66" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D66" s="11"/>
+      <c r="D66" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G66">
         <v>0.56000000000000005</v>
       </c>
       <c r="H66" s="4">
         <v>0.54</v>
+      </c>
+      <c r="I66">
+        <v>0.56000000000000005</v>
       </c>
       <c r="M66" s="6"/>
     </row>
@@ -2609,11 +2662,16 @@
       <c r="C67" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D67" s="11"/>
+      <c r="D67" s="11">
+        <v>0</v>
+      </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67" s="4">
+        <v>0</v>
+      </c>
+      <c r="I67">
         <v>0</v>
       </c>
       <c r="M67" s="6"/>
@@ -2628,12 +2686,17 @@
       <c r="C68" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D68" s="11"/>
+      <c r="D68" s="11">
+        <v>0.8</v>
+      </c>
       <c r="G68">
         <v>0.27</v>
       </c>
       <c r="H68" s="4">
         <v>0.63</v>
+      </c>
+      <c r="I68">
+        <v>0.65</v>
       </c>
       <c r="M68" s="6"/>
     </row>
@@ -2647,12 +2710,17 @@
       <c r="C69" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D69" s="11"/>
+      <c r="D69" s="11">
+        <v>0.92</v>
+      </c>
       <c r="G69">
         <v>0.45</v>
       </c>
       <c r="H69" s="4">
         <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0.34</v>
       </c>
       <c r="M69" s="6"/>
     </row>
@@ -2666,12 +2734,17 @@
       <c r="C70" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D70" s="11"/>
+      <c r="D70" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G70">
         <v>0.6</v>
       </c>
       <c r="H70" s="4">
         <v>0.33</v>
+      </c>
+      <c r="I70">
+        <v>0.32</v>
       </c>
       <c r="M70" s="6"/>
     </row>
@@ -2685,12 +2758,17 @@
       <c r="C71" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D71" s="11"/>
+      <c r="D71" s="11">
+        <v>0.75</v>
+      </c>
       <c r="G71">
         <v>0.42</v>
       </c>
       <c r="H71" s="4">
         <v>0.63</v>
+      </c>
+      <c r="I71">
+        <v>0.28999999999999998</v>
       </c>
       <c r="M71" s="6"/>
     </row>
@@ -2704,12 +2782,17 @@
       <c r="C72" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D72" s="11"/>
+      <c r="D72" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G72">
         <v>0.4</v>
       </c>
       <c r="H72" s="4">
         <v>0.31</v>
+      </c>
+      <c r="I72">
+        <v>0.38</v>
       </c>
       <c r="M72" s="6"/>
     </row>
@@ -2723,12 +2806,17 @@
       <c r="C73" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D73" s="11"/>
+      <c r="D73" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G73">
         <v>0.4</v>
       </c>
       <c r="H73" s="4">
         <v>0.28999999999999998</v>
+      </c>
+      <c r="I73">
+        <v>0.34</v>
       </c>
       <c r="M73" s="6"/>
     </row>
@@ -2742,12 +2830,17 @@
       <c r="C74" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="11"/>
+      <c r="D74" s="11">
+        <v>0.83</v>
+      </c>
       <c r="G74">
         <v>0.28000000000000003</v>
       </c>
       <c r="H74" s="4">
         <v>0.31</v>
+      </c>
+      <c r="I74">
+        <v>0.28999999999999998</v>
       </c>
       <c r="M74" s="6"/>
     </row>
@@ -2761,12 +2854,17 @@
       <c r="C75" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D75" s="11"/>
+      <c r="D75" s="11">
+        <v>0.88</v>
+      </c>
       <c r="G75">
         <v>0.06</v>
       </c>
       <c r="H75" s="4">
         <v>0.57999999999999996</v>
+      </c>
+      <c r="I75">
+        <v>0.41</v>
       </c>
       <c r="M75" s="6"/>
     </row>
@@ -2780,12 +2878,17 @@
       <c r="C76" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D76" s="11"/>
+      <c r="D76" s="11">
+        <v>0.82</v>
+      </c>
       <c r="G76">
         <v>0.57999999999999996</v>
       </c>
       <c r="H76" s="4">
         <v>0.38</v>
+      </c>
+      <c r="I76">
+        <v>0.56000000000000005</v>
       </c>
       <c r="M76" s="6"/>
     </row>
@@ -2799,12 +2902,17 @@
       <c r="C77" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D77" s="11"/>
+      <c r="D77" s="11">
+        <v>0.88</v>
+      </c>
       <c r="G77">
         <v>0.5</v>
       </c>
       <c r="H77" s="4">
         <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0.41</v>
       </c>
       <c r="M77" s="6"/>
     </row>
@@ -2818,12 +2926,17 @@
       <c r="C78" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D78" s="11"/>
+      <c r="D78" s="11">
+        <v>0.8</v>
+      </c>
       <c r="G78">
         <v>0.28999999999999998</v>
       </c>
       <c r="H78" s="4">
         <v>0.31</v>
+      </c>
+      <c r="I78">
+        <v>0.4</v>
       </c>
       <c r="M78" s="6"/>
     </row>
@@ -2837,12 +2950,17 @@
       <c r="C79" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D79" s="11"/>
+      <c r="D79" s="11">
+        <v>0.94</v>
+      </c>
       <c r="G79">
         <v>0.59</v>
       </c>
       <c r="H79" s="4">
         <v>0.88</v>
+      </c>
+      <c r="I79">
+        <v>0.69</v>
       </c>
       <c r="M79" s="6"/>
     </row>
@@ -2856,12 +2974,17 @@
       <c r="C80" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D80" s="11"/>
+      <c r="D80" s="11">
+        <v>0.95</v>
+      </c>
       <c r="G80">
         <v>0.08</v>
       </c>
       <c r="H80" s="4">
         <v>0.27</v>
+      </c>
+      <c r="I80">
+        <v>0.12</v>
       </c>
       <c r="M80" s="6"/>
     </row>
@@ -2875,12 +2998,17 @@
       <c r="C81" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D81" s="11"/>
+      <c r="D81" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G81">
         <v>0.72</v>
       </c>
       <c r="H81" s="4">
         <v>0.56000000000000005</v>
+      </c>
+      <c r="I81">
+        <v>0.82</v>
       </c>
       <c r="M81" s="6"/>
     </row>
@@ -2894,12 +3022,17 @@
       <c r="C82" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D82" s="11"/>
+      <c r="D82" s="11">
+        <v>0.95</v>
+      </c>
       <c r="G82">
         <v>0.46</v>
       </c>
       <c r="H82" s="4">
         <v>0.6</v>
+      </c>
+      <c r="I82">
+        <v>0.38</v>
       </c>
       <c r="M82" s="6"/>
     </row>
@@ -2913,12 +3046,17 @@
       <c r="C83" t="s">
         <v>121</v>
       </c>
-      <c r="D83" s="4"/>
+      <c r="D83" s="4">
+        <v>0.9</v>
+      </c>
       <c r="G83">
         <v>0.4</v>
       </c>
       <c r="H83" s="4">
         <v>0.31</v>
+      </c>
+      <c r="I83">
+        <v>0.25</v>
       </c>
       <c r="M83" s="6"/>
     </row>
@@ -2932,12 +3070,17 @@
       <c r="C84" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D84" s="11"/>
+      <c r="D84" s="11">
+        <v>0.81</v>
+      </c>
       <c r="G84">
         <v>0.15</v>
       </c>
       <c r="H84" s="4">
         <v>0.35</v>
+      </c>
+      <c r="I84">
+        <v>0.43</v>
       </c>
       <c r="M84" s="6"/>
     </row>
@@ -2951,12 +3094,17 @@
       <c r="C85" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D85" s="11"/>
+      <c r="D85" s="11">
+        <v>0</v>
+      </c>
       <c r="G85">
         <v>0.37</v>
       </c>
       <c r="H85" s="4">
         <v>0.38</v>
+      </c>
+      <c r="I85">
+        <v>0.31</v>
       </c>
       <c r="M85" s="6"/>
     </row>
@@ -2970,12 +3118,17 @@
       <c r="C86" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D86" s="11"/>
+      <c r="D86" s="11">
+        <v>0.89</v>
+      </c>
       <c r="G86">
         <v>0.59</v>
       </c>
       <c r="H86" s="4">
         <v>0.46</v>
+      </c>
+      <c r="I86">
+        <v>0.62</v>
       </c>
       <c r="M86" s="6"/>
     </row>
@@ -2989,12 +3142,17 @@
       <c r="C87" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D87" s="11"/>
+      <c r="D87" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G87">
         <v>0.59</v>
       </c>
       <c r="H87" s="4">
         <v>0.44</v>
+      </c>
+      <c r="I87">
+        <v>0.26</v>
       </c>
       <c r="M87" s="6"/>
     </row>
@@ -3008,12 +3166,17 @@
       <c r="C88" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D88" s="11"/>
+      <c r="D88" s="11">
+        <v>0.83</v>
+      </c>
       <c r="G88">
         <v>0.65</v>
       </c>
       <c r="H88" s="4">
         <v>0.52</v>
+      </c>
+      <c r="I88">
+        <v>0.56000000000000005</v>
       </c>
       <c r="M88" s="6"/>
     </row>
@@ -3027,12 +3190,17 @@
       <c r="C89" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D89" s="11"/>
+      <c r="D89" s="11">
+        <v>0.96</v>
+      </c>
       <c r="G89">
         <v>0.65</v>
       </c>
       <c r="H89" s="4">
         <v>0.83</v>
+      </c>
+      <c r="I89">
+        <v>0.68</v>
       </c>
       <c r="M89" s="6"/>
     </row>
@@ -3046,12 +3214,17 @@
       <c r="C90" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D90" s="11"/>
+      <c r="D90" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G90">
         <v>0.54</v>
       </c>
       <c r="H90" s="4">
         <v>0.67</v>
+      </c>
+      <c r="I90">
+        <v>0.75</v>
       </c>
       <c r="M90" s="6"/>
     </row>
@@ -3065,12 +3238,17 @@
       <c r="C91" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D91" s="11"/>
+      <c r="D91" s="11">
+        <v>0.82</v>
+      </c>
       <c r="G91">
         <v>0.56000000000000005</v>
       </c>
       <c r="H91" s="4">
         <v>0.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
       </c>
       <c r="M91" s="6"/>
     </row>
@@ -3084,12 +3262,17 @@
       <c r="C92" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D92" s="11"/>
+      <c r="D92" s="11">
+        <v>0.89</v>
+      </c>
       <c r="G92">
         <v>0.44</v>
       </c>
       <c r="H92" s="4">
         <v>0.75</v>
+      </c>
+      <c r="I92">
+        <v>0.63</v>
       </c>
       <c r="M92" s="6"/>
     </row>
@@ -3103,12 +3286,17 @@
       <c r="C93" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D93" s="11"/>
+      <c r="D93" s="11">
+        <v>0.94</v>
+      </c>
       <c r="G93">
         <v>0.53</v>
       </c>
       <c r="H93" s="4">
         <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0.51</v>
       </c>
       <c r="M93" s="6"/>
     </row>
@@ -3122,12 +3310,17 @@
       <c r="C94" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D94" s="11"/>
+      <c r="D94" s="11">
+        <v>0.94</v>
+      </c>
       <c r="G94">
         <v>0.71</v>
       </c>
       <c r="H94" s="4">
         <v>0.42</v>
+      </c>
+      <c r="I94">
+        <v>0.44</v>
       </c>
       <c r="M94" s="6"/>
     </row>
@@ -3141,12 +3334,17 @@
       <c r="C95" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D95" s="11"/>
+      <c r="D95" s="11">
+        <v>0.94</v>
+      </c>
       <c r="G95">
         <v>0.63</v>
       </c>
       <c r="H95" s="4">
         <v>0.46</v>
+      </c>
+      <c r="I95">
+        <v>0.69</v>
       </c>
       <c r="M95" s="6"/>
     </row>
@@ -3160,11 +3358,16 @@
       <c r="C96" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D96" s="11"/>
+      <c r="D96" s="11">
+        <v>0</v>
+      </c>
       <c r="G96">
         <v>0</v>
       </c>
       <c r="H96" s="4">
+        <v>0</v>
+      </c>
+      <c r="I96">
         <v>0</v>
       </c>
       <c r="M96" s="6"/>
@@ -3179,12 +3382,17 @@
       <c r="C97" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D97" s="11"/>
+      <c r="D97" s="11">
+        <v>0.91</v>
+      </c>
       <c r="G97">
         <v>0.51</v>
       </c>
       <c r="H97" s="4">
         <v>0.52</v>
+      </c>
+      <c r="I97">
+        <v>0.56000000000000005</v>
       </c>
       <c r="M97" s="6"/>
     </row>
@@ -3198,11 +3406,16 @@
       <c r="C98" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D98" s="11"/>
+      <c r="D98" s="11">
+        <v>0</v>
+      </c>
       <c r="G98">
         <v>0</v>
       </c>
       <c r="H98" s="4">
+        <v>0</v>
+      </c>
+      <c r="I98">
         <v>0</v>
       </c>
       <c r="M98" s="6"/>
@@ -3217,12 +3430,17 @@
       <c r="C99" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D99" s="11"/>
+      <c r="D99" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G99">
         <v>0.62</v>
       </c>
       <c r="H99" s="4">
         <v>0.54</v>
+      </c>
+      <c r="I99">
+        <v>0.78</v>
       </c>
       <c r="M99" s="6"/>
     </row>
@@ -3236,12 +3454,17 @@
       <c r="C100" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D100" s="11"/>
+      <c r="D100" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G100">
         <v>0.54</v>
       </c>
       <c r="H100" s="4">
         <v>0.65</v>
+      </c>
+      <c r="I100">
+        <v>0.44</v>
       </c>
       <c r="M100" s="6"/>
     </row>
@@ -3255,12 +3478,17 @@
       <c r="C101" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D101" s="11"/>
+      <c r="D101" s="11">
+        <v>0.88</v>
+      </c>
       <c r="G101">
         <v>0.19</v>
       </c>
       <c r="H101" s="4">
         <v>0.46</v>
+      </c>
+      <c r="I101">
+        <v>0.56000000000000005</v>
       </c>
       <c r="M101" s="6"/>
     </row>
@@ -3274,12 +3502,17 @@
       <c r="C102" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D102" s="11"/>
+      <c r="D102" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G102">
         <v>0.72</v>
       </c>
       <c r="H102" s="4">
         <v>0.79</v>
+      </c>
+      <c r="I102">
+        <v>0.82</v>
       </c>
       <c r="M102" s="6"/>
     </row>
@@ -3293,12 +3526,17 @@
       <c r="C103" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D103" s="11"/>
+      <c r="D103" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G103">
         <v>0.33</v>
       </c>
       <c r="H103" s="4">
         <v>0.38</v>
+      </c>
+      <c r="I103">
+        <v>0.28000000000000003</v>
       </c>
       <c r="M103" s="6"/>
     </row>
@@ -3312,12 +3550,17 @@
       <c r="C104" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D104" s="11"/>
+      <c r="D104" s="11">
+        <v>0.96</v>
+      </c>
       <c r="G104">
         <v>0.32</v>
       </c>
       <c r="H104" s="4">
         <v>0.44</v>
+      </c>
+      <c r="I104">
+        <v>0.35</v>
       </c>
       <c r="M104" s="6"/>
     </row>
@@ -3331,12 +3574,17 @@
       <c r="C105" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D105" s="11"/>
+      <c r="D105" s="11">
+        <v>0.85</v>
+      </c>
       <c r="G105">
         <v>0.44</v>
       </c>
       <c r="H105" s="4">
         <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0.28000000000000003</v>
       </c>
       <c r="M105" s="6"/>
     </row>
@@ -3350,12 +3598,17 @@
       <c r="C106" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D106" s="11"/>
+      <c r="D106" s="11">
+        <v>0.91</v>
+      </c>
       <c r="G106">
         <v>0.59</v>
       </c>
       <c r="H106" s="4">
-        <v>0.42</v>
+        <v>0.46</v>
+      </c>
+      <c r="I106">
+        <v>0.75</v>
       </c>
       <c r="M106" s="6"/>
     </row>
@@ -3369,12 +3622,17 @@
       <c r="C107" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D107" s="11"/>
+      <c r="D107" s="11">
+        <v>0.94</v>
+      </c>
       <c r="G107">
         <v>0.57999999999999996</v>
       </c>
       <c r="H107" s="4">
         <v>0.71</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
       </c>
       <c r="M107" s="6"/>
     </row>
@@ -3388,141 +3646,183 @@
       <c r="C108" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D108" s="11"/>
+      <c r="D108" s="11">
+        <v>0.94</v>
+      </c>
       <c r="G108">
         <v>0.47</v>
       </c>
       <c r="H108" s="4">
         <v>0.28999999999999998</v>
       </c>
+      <c r="I108">
+        <v>0.44</v>
+      </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B109" s="11" t="s">
-        <v>223</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="B109" s="11"/>
       <c r="C109" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D109" s="11"/>
+      <c r="D109" s="11">
+        <v>0</v>
+      </c>
       <c r="G109">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="H109" s="4">
-        <v>0.67</v>
+        <v>0.1</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
       </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C110" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D110" s="11"/>
+      <c r="D110" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G110">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="H110" s="4">
-        <v>0.83</v>
+        <v>0.67</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
       </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C111" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D111" s="11"/>
+      <c r="D111" s="11">
+        <v>0.94</v>
+      </c>
       <c r="G111">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="H111" s="4">
-        <v>0.79</v>
+        <v>0.83</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
       </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C112" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="11"/>
+      <c r="D112" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G112">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="H112" s="4">
-        <v>0.46</v>
+        <v>0.79</v>
+      </c>
+      <c r="I112">
+        <v>0.6</v>
       </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C113" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D113" s="11"/>
+      <c r="D113" s="11">
+        <v>0.97</v>
+      </c>
       <c r="G113">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="H113" s="4">
-        <v>0.44</v>
+        <v>0.46</v>
+      </c>
+      <c r="I113">
+        <v>0.32</v>
       </c>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D114" s="11">
+        <v>0.97</v>
+      </c>
+      <c r="G114">
+        <v>0.54</v>
+      </c>
+      <c r="H114" s="4">
+        <v>0.44</v>
+      </c>
+      <c r="I114">
+        <v>0.43</v>
+      </c>
+      <c r="M114" s="6"/>
+    </row>
+    <row r="115" spans="1:13">
+      <c r="A115" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="B114" s="11" t="s">
+      <c r="B115" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="C114" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D114" s="11"/>
-      <c r="G114">
+      <c r="C115" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D115" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="G115">
         <v>0.51</v>
       </c>
-      <c r="H114" s="4">
+      <c r="H115" s="4">
         <v>0</v>
       </c>
-      <c r="M114" s="6"/>
-    </row>
-    <row r="115" spans="1:13">
-      <c r="A115" s="11"/>
-      <c r="B115" s="11"/>
-      <c r="C115" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D115" s="11"/>
-      <c r="G115">
-        <v>0</v>
-      </c>
-      <c r="H115" s="4">
-        <v>0.1</v>
+      <c r="I115">
+        <v>0.32</v>
       </c>
       <c r="M115" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947DCD1A-94BD-AF4A-912F-D2CA60776626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFED85B-EFB8-2648-909D-009C1890FACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1280" yWindow="920" windowWidth="11160" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -904,7 +904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -929,11 +929,7 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1377,7 +1373,9 @@
       <c r="C2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4">
+        <v>0.73</v>
+      </c>
       <c r="G2">
         <v>0.32</v>
       </c>
@@ -1396,7 +1394,9 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="4">
+        <v>0.85</v>
+      </c>
       <c r="G3">
         <v>0.64</v>
       </c>
@@ -1406,16 +1406,18 @@
       <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="15" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4">
+        <v>0.46</v>
+      </c>
       <c r="G4">
         <v>0.41</v>
       </c>
@@ -1434,7 +1436,9 @@
       <c r="C5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4">
+        <v>0.82</v>
+      </c>
       <c r="G5">
         <v>0.14000000000000001</v>
       </c>
@@ -1453,7 +1457,9 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>0.9</v>
+      </c>
       <c r="G6">
         <v>0.59</v>
       </c>
@@ -1472,7 +1478,9 @@
       <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>0.76</v>
+      </c>
       <c r="G7">
         <v>0.34</v>
       </c>
@@ -1491,7 +1499,9 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>0.91</v>
+      </c>
       <c r="G8">
         <v>0.3</v>
       </c>
@@ -1510,7 +1520,9 @@
       <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="G9">
         <v>0.43</v>
       </c>
@@ -1529,7 +1541,9 @@
       <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>0.78</v>
+      </c>
       <c r="G10">
         <v>0.48</v>
       </c>
@@ -1548,7 +1562,9 @@
       <c r="C11" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>0.71</v>
+      </c>
       <c r="G11">
         <v>0.73</v>
       </c>
@@ -1567,7 +1583,9 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>0.85</v>
+      </c>
       <c r="G12">
         <v>0.45</v>
       </c>
@@ -1586,7 +1604,9 @@
       <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G13">
         <v>0.59</v>
       </c>
@@ -1605,7 +1625,9 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>0.91</v>
+      </c>
       <c r="G14">
         <v>0.27</v>
       </c>
@@ -1624,7 +1646,9 @@
       <c r="C15" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>0.89</v>
+      </c>
       <c r="G15">
         <v>0.2</v>
       </c>
@@ -1643,7 +1667,9 @@
       <c r="C16" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="G16">
         <v>0.36</v>
       </c>
@@ -1662,7 +1688,9 @@
       <c r="C17" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>0.85</v>
+      </c>
       <c r="G17">
         <v>0.55000000000000004</v>
       </c>
@@ -1681,7 +1709,9 @@
       <c r="C18" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G18">
         <v>0.41</v>
       </c>
@@ -1700,7 +1730,9 @@
       <c r="C19" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>0.85</v>
+      </c>
       <c r="G19">
         <v>0.32</v>
       </c>
@@ -1719,7 +1751,9 @@
       <c r="C20" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G20">
         <v>0.56999999999999995</v>
       </c>
@@ -1738,7 +1772,9 @@
       <c r="C21" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4">
+        <v>0.85</v>
+      </c>
       <c r="G21">
         <v>0.61</v>
       </c>
@@ -1757,7 +1793,9 @@
       <c r="C22" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4">
+        <v>0.78</v>
+      </c>
       <c r="G22">
         <v>0.39</v>
       </c>
@@ -1776,7 +1814,9 @@
       <c r="C23" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="4">
+        <v>0.82</v>
+      </c>
       <c r="G23">
         <v>0.23</v>
       </c>
@@ -1795,7 +1835,9 @@
       <c r="C24" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="4">
+        <v>0.82</v>
+      </c>
       <c r="G24">
         <v>0.45</v>
       </c>
@@ -1814,7 +1856,9 @@
       <c r="C25" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="4"/>
+      <c r="D25" s="4">
+        <v>0.85</v>
+      </c>
       <c r="G25">
         <v>0.41</v>
       </c>
@@ -1833,7 +1877,9 @@
       <c r="C26" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="4">
+        <v>0</v>
+      </c>
       <c r="G26">
         <v>0.3</v>
       </c>
@@ -1852,7 +1898,9 @@
       <c r="C27" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="4">
+        <v>0.78</v>
+      </c>
       <c r="G27">
         <v>0.3</v>
       </c>
@@ -1871,7 +1919,9 @@
       <c r="C28" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4">
+        <v>0.5</v>
+      </c>
       <c r="G28">
         <v>0.56999999999999995</v>
       </c>
@@ -1890,7 +1940,9 @@
       <c r="C29" t="s">
         <v>15</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G29">
         <v>0.55000000000000004</v>
       </c>
@@ -1909,7 +1961,9 @@
       <c r="C30" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G30">
         <v>0.5</v>
       </c>
@@ -1928,7 +1982,9 @@
       <c r="C31" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="4"/>
+      <c r="D31" s="4">
+        <v>0.72</v>
+      </c>
       <c r="G31">
         <v>0.32</v>
       </c>
@@ -1947,7 +2003,9 @@
       <c r="C32" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="4">
+        <v>0.46</v>
+      </c>
       <c r="G32">
         <v>0.36</v>
       </c>
@@ -1966,7 +2024,9 @@
       <c r="C33" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="4">
+        <v>0.9</v>
+      </c>
       <c r="G33">
         <v>0.23</v>
       </c>
@@ -1985,7 +2045,9 @@
       <c r="C34" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="4">
+        <v>0.89</v>
+      </c>
       <c r="G34">
         <v>0.52</v>
       </c>
@@ -2004,7 +2066,9 @@
       <c r="C35" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="4"/>
+      <c r="D35" s="4">
+        <v>0</v>
+      </c>
       <c r="G35">
         <v>0</v>
       </c>
@@ -2023,7 +2087,9 @@
       <c r="C36" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="4"/>
+      <c r="D36" s="4">
+        <v>0.63</v>
+      </c>
       <c r="G36">
         <v>0.39</v>
       </c>
@@ -2042,7 +2108,9 @@
       <c r="C37" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="4"/>
+      <c r="D37" s="4">
+        <v>0.85</v>
+      </c>
       <c r="G37">
         <v>0.45</v>
       </c>
@@ -2061,7 +2129,9 @@
       <c r="C38" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="4"/>
+      <c r="D38" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G38">
         <v>0.34</v>
       </c>
@@ -2080,7 +2150,9 @@
       <c r="C39" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="4"/>
+      <c r="D39" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G39">
         <v>0.77</v>
       </c>
@@ -2099,7 +2171,9 @@
       <c r="C40" t="s">
         <v>15</v>
       </c>
-      <c r="D40" s="4"/>
+      <c r="D40" s="4">
+        <v>0.77</v>
+      </c>
       <c r="G40">
         <v>0.55000000000000004</v>
       </c>
@@ -2118,7 +2192,9 @@
       <c r="C41" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="4"/>
+      <c r="D41" s="4">
+        <v>0.78</v>
+      </c>
       <c r="G41">
         <v>0.59</v>
       </c>
@@ -2137,7 +2213,9 @@
       <c r="C42" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="4"/>
+      <c r="D42" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G42">
         <v>0.52</v>
       </c>
@@ -2156,7 +2234,9 @@
       <c r="C43" t="s">
         <v>15</v>
       </c>
-      <c r="D43" s="4"/>
+      <c r="D43" s="4">
+        <v>0.78</v>
+      </c>
       <c r="G43">
         <v>0.56999999999999995</v>
       </c>
@@ -2175,7 +2255,9 @@
       <c r="C44" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="4"/>
+      <c r="D44" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G44">
         <v>0.36</v>
       </c>
@@ -2194,7 +2276,9 @@
       <c r="C45" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="4"/>
+      <c r="D45" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G45">
         <v>0.68</v>
       </c>
@@ -2213,7 +2297,9 @@
       <c r="C46" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="4"/>
+      <c r="D46" s="4">
+        <v>0.93</v>
+      </c>
       <c r="G46">
         <v>0.5</v>
       </c>
@@ -2232,7 +2318,9 @@
       <c r="C47" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="11"/>
+      <c r="D47" s="11">
+        <v>0.6</v>
+      </c>
       <c r="G47">
         <v>0.52</v>
       </c>
@@ -2251,7 +2339,9 @@
       <c r="C48" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D48" s="11"/>
+      <c r="D48" s="11">
+        <v>0.93</v>
+      </c>
       <c r="G48">
         <v>0.52</v>
       </c>
@@ -2270,7 +2360,9 @@
       <c r="C49" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="11"/>
+      <c r="D49" s="11">
+        <v>0.67</v>
+      </c>
       <c r="G49">
         <v>0.39</v>
       </c>
@@ -2289,7 +2381,9 @@
       <c r="C50" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="11"/>
+      <c r="D50" s="11">
+        <v>0</v>
+      </c>
       <c r="G50">
         <v>0.23</v>
       </c>
@@ -2308,7 +2402,9 @@
       <c r="C51" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="11"/>
+      <c r="D51" s="11">
+        <v>0.82</v>
+      </c>
       <c r="G51">
         <v>0.66</v>
       </c>
@@ -2327,7 +2423,9 @@
       <c r="C52" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D52" s="11"/>
+      <c r="D52" s="11">
+        <v>0.82</v>
+      </c>
       <c r="G52">
         <v>0</v>
       </c>
@@ -2346,7 +2444,9 @@
       <c r="C53" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="11"/>
+      <c r="D53" s="11">
+        <v>0.9</v>
+      </c>
       <c r="G53">
         <v>0.45</v>
       </c>
@@ -2365,7 +2465,9 @@
       <c r="C54" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D54" s="11"/>
+      <c r="D54" s="11">
+        <v>0.93</v>
+      </c>
       <c r="G54">
         <v>0.34</v>
       </c>
@@ -2384,7 +2486,9 @@
       <c r="C55" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D55" s="11"/>
+      <c r="D55" s="11">
+        <v>0.83</v>
+      </c>
       <c r="G55">
         <v>0.5</v>
       </c>
@@ -2403,7 +2507,9 @@
       <c r="C56" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="11"/>
+      <c r="D56" s="11">
+        <v>0.85</v>
+      </c>
       <c r="G56">
         <v>0</v>
       </c>
@@ -2461,10 +2567,10 @@
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="20" t="s">
+      <c r="A59" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c r="B59" s="11" t="s">
         <v>125</v>
       </c>
       <c r="C59" s="11" t="s">
@@ -2485,10 +2591,10 @@
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="20" t="s">
+      <c r="A60" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="B60" s="11" t="s">
         <v>127</v>
       </c>
       <c r="C60" s="11" t="s">
@@ -2509,10 +2615,10 @@
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="20" t="s">
+      <c r="A61" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="B61" s="11" t="s">
         <v>129</v>
       </c>
       <c r="C61" s="11" t="s">
@@ -2533,10 +2639,10 @@
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="20" t="s">
+      <c r="A62" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B62" s="20" t="s">
+      <c r="B62" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C62" s="11" t="s">
@@ -2557,10 +2663,10 @@
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="20" t="s">
+      <c r="A63" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="11" t="s">
         <v>133</v>
       </c>
       <c r="C63" s="11" t="s">
@@ -2581,10 +2687,10 @@
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="20" t="s">
+      <c r="A64" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="20" t="s">
+      <c r="B64" s="11" t="s">
         <v>135</v>
       </c>
       <c r="C64" s="11" t="s">
@@ -2605,10 +2711,10 @@
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="20" t="s">
+      <c r="A65" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="11" t="s">
         <v>137</v>
       </c>
       <c r="C65" s="11" t="s">
@@ -2629,10 +2735,10 @@
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="20" t="s">
+      <c r="A66" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B66" s="20" t="s">
+      <c r="B66" s="11" t="s">
         <v>139</v>
       </c>
       <c r="C66" s="11" t="s">
@@ -2653,10 +2759,10 @@
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="20" t="s">
+      <c r="A67" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B67" s="20" t="s">
+      <c r="B67" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C67" s="11" t="s">
@@ -2677,10 +2783,10 @@
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="20" t="s">
+      <c r="A68" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="20" t="s">
+      <c r="B68" s="11" t="s">
         <v>143</v>
       </c>
       <c r="C68" s="11" t="s">
@@ -2701,10 +2807,10 @@
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="20" t="s">
+      <c r="A69" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="20" t="s">
+      <c r="B69" s="11" t="s">
         <v>145</v>
       </c>
       <c r="C69" s="11" t="s">
@@ -2725,10 +2831,10 @@
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="20" t="s">
+      <c r="A70" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="11" t="s">
         <v>147</v>
       </c>
       <c r="C70" s="11" t="s">
@@ -2749,10 +2855,10 @@
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B71" s="20" t="s">
+      <c r="B71" s="11" t="s">
         <v>149</v>
       </c>
       <c r="C71" s="11" t="s">
@@ -2773,10 +2879,10 @@
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B72" s="20" t="s">
+      <c r="B72" s="11" t="s">
         <v>151</v>
       </c>
       <c r="C72" s="11" t="s">
@@ -2797,10 +2903,10 @@
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" s="20" t="s">
+      <c r="A73" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="20" t="s">
+      <c r="B73" s="11" t="s">
         <v>153</v>
       </c>
       <c r="C73" s="11" t="s">
@@ -2821,10 +2927,10 @@
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B74" s="20" t="s">
+      <c r="B74" s="11" t="s">
         <v>154</v>
       </c>
       <c r="C74" s="11" t="s">
@@ -2845,10 +2951,10 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="20" t="s">
+      <c r="A75" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B75" s="20" t="s">
+      <c r="B75" s="11" t="s">
         <v>156</v>
       </c>
       <c r="C75" s="11" t="s">
@@ -2869,10 +2975,10 @@
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="20" t="s">
+      <c r="A76" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B76" s="20" t="s">
+      <c r="B76" s="11" t="s">
         <v>158</v>
       </c>
       <c r="C76" s="11" t="s">
@@ -2893,10 +2999,10 @@
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="20" t="s">
+      <c r="A77" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B77" s="20" t="s">
+      <c r="B77" s="11" t="s">
         <v>160</v>
       </c>
       <c r="C77" s="11" t="s">
@@ -2917,10 +3023,10 @@
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
-      <c r="A78" s="20" t="s">
+      <c r="A78" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B78" s="20" t="s">
+      <c r="B78" s="11" t="s">
         <v>162</v>
       </c>
       <c r="C78" s="11" t="s">
@@ -2941,10 +3047,10 @@
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" s="20" t="s">
+      <c r="A79" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B79" s="20" t="s">
+      <c r="B79" s="11" t="s">
         <v>164</v>
       </c>
       <c r="C79" s="11" t="s">
@@ -2965,10 +3071,10 @@
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
-      <c r="A80" s="20" t="s">
+      <c r="A80" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B80" s="20" t="s">
+      <c r="B80" s="11" t="s">
         <v>166</v>
       </c>
       <c r="C80" s="11" t="s">
@@ -2989,10 +3095,10 @@
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
-      <c r="A81" s="20" t="s">
+      <c r="A81" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B81" s="20" t="s">
+      <c r="B81" s="11" t="s">
         <v>168</v>
       </c>
       <c r="C81" s="11" t="s">
@@ -3013,10 +3119,10 @@
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
-      <c r="A82" s="20" t="s">
+      <c r="A82" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B82" s="20" t="s">
+      <c r="B82" s="11" t="s">
         <v>170</v>
       </c>
       <c r="C82" s="11" t="s">
@@ -3037,10 +3143,10 @@
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
-      <c r="A83" s="21" t="s">
+      <c r="A83" t="s">
         <v>171</v>
       </c>
-      <c r="B83" s="22" t="s">
+      <c r="B83" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C83" t="s">

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFED85B-EFB8-2648-909D-009C1890FACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04188049-4199-4441-9AEB-0CF4E56AB0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="920" windowWidth="11160" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1280" yWindow="920" windowWidth="25080" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2948,6 +2948,9 @@
       <c r="I74">
         <v>0.28999999999999998</v>
       </c>
+      <c r="J74">
+        <v>0.69</v>
+      </c>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
@@ -2972,6 +2975,9 @@
       <c r="I75">
         <v>0.41</v>
       </c>
+      <c r="J75">
+        <v>0.81</v>
+      </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
@@ -3020,6 +3026,9 @@
       <c r="I77">
         <v>0.41</v>
       </c>
+      <c r="J77">
+        <v>0.53</v>
+      </c>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
@@ -3308,6 +3317,9 @@
       <c r="I89">
         <v>0.68</v>
       </c>
+      <c r="J89">
+        <v>0.83</v>
+      </c>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
@@ -3356,6 +3368,9 @@
       <c r="I91">
         <v>0</v>
       </c>
+      <c r="J91">
+        <v>0.75</v>
+      </c>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
@@ -3403,6 +3418,9 @@
       </c>
       <c r="I93">
         <v>0.51</v>
+      </c>
+      <c r="J93">
+        <v>0.75</v>
       </c>
       <c r="M93" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04188049-4199-4441-9AEB-0CF4E56AB0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A3E419-69F2-F245-96B5-7DB58B48AE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1280" yWindow="920" windowWidth="25080" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2564,6 +2564,9 @@
       <c r="I58">
         <v>0.5</v>
       </c>
+      <c r="J58">
+        <v>0.94</v>
+      </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
@@ -2924,6 +2927,9 @@
       <c r="I73">
         <v>0.34</v>
       </c>
+      <c r="J73">
+        <v>0.72</v>
+      </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
@@ -3125,6 +3131,9 @@
       <c r="I81">
         <v>0.82</v>
       </c>
+      <c r="J81">
+        <v>0.89</v>
+      </c>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
@@ -3638,6 +3647,9 @@
       <c r="I102">
         <v>0.82</v>
       </c>
+      <c r="J102">
+        <v>0.92</v>
+      </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
@@ -3733,6 +3745,9 @@
       </c>
       <c r="I106">
         <v>0.75</v>
+      </c>
+      <c r="J106">
+        <v>0.81</v>
       </c>
       <c r="M106" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A3E419-69F2-F245-96B5-7DB58B48AE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE5E105-F530-3949-B940-7B6EF2A9312C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1280" yWindow="920" windowWidth="25080" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1382,6 +1382,9 @@
       <c r="H2" s="5">
         <v>0.66</v>
       </c>
+      <c r="I2">
+        <v>0.41</v>
+      </c>
       <c r="M2" s="17"/>
     </row>
     <row r="3" spans="1:13">
@@ -1403,6 +1406,9 @@
       <c r="H3" s="5">
         <v>0.56000000000000005</v>
       </c>
+      <c r="I3">
+        <v>0.7</v>
+      </c>
       <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:13">
@@ -1424,6 +1430,9 @@
       <c r="H4" s="5">
         <v>0.63</v>
       </c>
+      <c r="I4">
+        <v>0.35</v>
+      </c>
       <c r="M4" s="17"/>
     </row>
     <row r="5" spans="1:13">
@@ -1445,6 +1454,9 @@
       <c r="H5" s="5">
         <v>0.44</v>
       </c>
+      <c r="I5">
+        <v>0.17</v>
+      </c>
       <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:13">
@@ -1466,6 +1478,9 @@
       <c r="H6" s="5">
         <v>0.8</v>
       </c>
+      <c r="I6">
+        <v>0.61</v>
+      </c>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13">
@@ -1487,6 +1502,9 @@
       <c r="H7" s="5">
         <v>0.73</v>
       </c>
+      <c r="I7">
+        <v>0.3</v>
+      </c>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
@@ -1508,6 +1526,9 @@
       <c r="H8" s="5">
         <v>0.54</v>
       </c>
+      <c r="I8">
+        <v>0.3</v>
+      </c>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
@@ -1529,6 +1550,9 @@
       <c r="H9" s="5">
         <v>0.68</v>
       </c>
+      <c r="I9">
+        <v>0.39</v>
+      </c>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
@@ -1550,6 +1574,9 @@
       <c r="H10" s="5">
         <v>0.61</v>
       </c>
+      <c r="I10">
+        <v>0.43</v>
+      </c>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13">
@@ -1571,6 +1598,9 @@
       <c r="H11" s="5">
         <v>0.68</v>
       </c>
+      <c r="I11">
+        <v>0.52</v>
+      </c>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13">
@@ -1592,6 +1622,9 @@
       <c r="H12" s="5">
         <v>0.92</v>
       </c>
+      <c r="I12">
+        <v>0.74</v>
+      </c>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13">
@@ -1613,6 +1646,9 @@
       <c r="H13" s="5">
         <v>0.54</v>
       </c>
+      <c r="I13">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13">
@@ -1634,6 +1670,9 @@
       <c r="H14" s="5">
         <v>0.61</v>
       </c>
+      <c r="I14">
+        <v>0.5</v>
+      </c>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13">
@@ -1655,6 +1694,9 @@
       <c r="H15" s="5">
         <v>0.63</v>
       </c>
+      <c r="I15">
+        <v>0.63</v>
+      </c>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13">
@@ -1676,6 +1718,9 @@
       <c r="H16" s="5">
         <v>0.44</v>
       </c>
+      <c r="I16">
+        <v>0.3</v>
+      </c>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
@@ -1697,6 +1742,9 @@
       <c r="H17" s="5">
         <v>0.83</v>
       </c>
+      <c r="I17">
+        <v>0.59</v>
+      </c>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13">
@@ -1718,6 +1766,9 @@
       <c r="H18" s="5">
         <v>0.74</v>
       </c>
+      <c r="I18">
+        <v>0.54</v>
+      </c>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
@@ -1739,6 +1790,9 @@
       <c r="H19" s="5">
         <v>0</v>
       </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
@@ -1760,6 +1814,9 @@
       <c r="H20" s="5">
         <v>0.78</v>
       </c>
+      <c r="I20">
+        <v>0.46</v>
+      </c>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
@@ -1781,6 +1838,9 @@
       <c r="H21" s="5">
         <v>0.9</v>
       </c>
+      <c r="I21">
+        <v>0.52</v>
+      </c>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
@@ -1802,6 +1862,9 @@
       <c r="H22" s="5">
         <v>0.68</v>
       </c>
+      <c r="I22">
+        <v>0.76</v>
+      </c>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
@@ -1823,6 +1886,9 @@
       <c r="H23" s="5">
         <v>0.68</v>
       </c>
+      <c r="I23">
+        <v>0.33</v>
+      </c>
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
@@ -1844,6 +1910,9 @@
       <c r="H24" s="5">
         <v>0.78</v>
       </c>
+      <c r="I24">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
@@ -1865,6 +1934,9 @@
       <c r="H25" s="5">
         <v>0.76</v>
       </c>
+      <c r="I25">
+        <v>0.5</v>
+      </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
@@ -1886,6 +1958,9 @@
       <c r="H26" s="5">
         <v>0.61</v>
       </c>
+      <c r="I26">
+        <v>0.5</v>
+      </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
@@ -1907,6 +1982,9 @@
       <c r="H27" s="5">
         <v>0.63</v>
       </c>
+      <c r="I27">
+        <v>0.5</v>
+      </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
@@ -1928,6 +2006,9 @@
       <c r="H28" s="5">
         <v>0.61</v>
       </c>
+      <c r="I28">
+        <v>0.39</v>
+      </c>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
@@ -1949,6 +2030,9 @@
       <c r="H29" s="5">
         <v>0.76</v>
       </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -1970,6 +2054,9 @@
       <c r="H30" s="5">
         <v>0.68</v>
       </c>
+      <c r="I30">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
@@ -1991,6 +2078,9 @@
       <c r="H31" s="5">
         <v>0.81</v>
       </c>
+      <c r="I31">
+        <v>0.52</v>
+      </c>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
@@ -2012,6 +2102,9 @@
       <c r="H32" s="5">
         <v>0.39</v>
       </c>
+      <c r="I32">
+        <v>0.41</v>
+      </c>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13">
@@ -2033,6 +2126,9 @@
       <c r="H33" s="5">
         <v>0.48</v>
       </c>
+      <c r="I33">
+        <v>0.39</v>
+      </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
@@ -2054,6 +2150,9 @@
       <c r="H34" s="4">
         <v>0.52</v>
       </c>
+      <c r="I34">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="1:13">
@@ -2075,6 +2174,9 @@
       <c r="H35" s="5">
         <v>0.74</v>
       </c>
+      <c r="I35">
+        <v>0.52</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
@@ -2096,6 +2198,9 @@
       <c r="H36" s="5">
         <v>0.76</v>
       </c>
+      <c r="I36">
+        <v>0.74</v>
+      </c>
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="1:13">
@@ -2117,6 +2222,9 @@
       <c r="H37" s="4">
         <v>0.61</v>
       </c>
+      <c r="I37">
+        <v>0.5</v>
+      </c>
       <c r="M37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20">
@@ -2138,6 +2246,9 @@
       <c r="H38" s="5">
         <v>0.7</v>
       </c>
+      <c r="I38">
+        <v>0.5</v>
+      </c>
       <c r="M38" s="6"/>
     </row>
     <row r="39" spans="1:13">
@@ -2159,6 +2270,9 @@
       <c r="H39" s="5">
         <v>0.52</v>
       </c>
+      <c r="I39">
+        <v>0.7</v>
+      </c>
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13">
@@ -2180,6 +2294,9 @@
       <c r="H40" s="5">
         <v>0.83</v>
       </c>
+      <c r="I40">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13">
@@ -2201,6 +2318,9 @@
       <c r="H41" s="5">
         <v>0.85</v>
       </c>
+      <c r="I41">
+        <v>0.5</v>
+      </c>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
@@ -2222,6 +2342,9 @@
       <c r="H42" s="5">
         <v>0.59</v>
       </c>
+      <c r="I42">
+        <v>0.5</v>
+      </c>
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
@@ -2243,6 +2366,9 @@
       <c r="H43" s="5">
         <v>0.74</v>
       </c>
+      <c r="I43">
+        <v>0.52</v>
+      </c>
       <c r="M43" s="6"/>
     </row>
     <row r="44" spans="1:13">
@@ -2264,6 +2390,9 @@
       <c r="H44" s="5">
         <v>0.44</v>
       </c>
+      <c r="I44">
+        <v>0.48</v>
+      </c>
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
@@ -2285,6 +2414,9 @@
       <c r="H45" s="5">
         <v>0.78</v>
       </c>
+      <c r="I45">
+        <v>0.67</v>
+      </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
@@ -2306,6 +2438,9 @@
       <c r="H46" s="5">
         <v>0.83</v>
       </c>
+      <c r="I46">
+        <v>0.43</v>
+      </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
@@ -2327,6 +2462,9 @@
       <c r="H47" s="5">
         <v>0.85</v>
       </c>
+      <c r="I47">
+        <v>0.61</v>
+      </c>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
@@ -2348,6 +2486,9 @@
       <c r="H48" s="5">
         <v>0.68</v>
       </c>
+      <c r="I48">
+        <v>0.59</v>
+      </c>
       <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13">
@@ -2369,6 +2510,9 @@
       <c r="H49" s="5">
         <v>0.7</v>
       </c>
+      <c r="I49">
+        <v>0.43</v>
+      </c>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
@@ -2390,6 +2534,9 @@
       <c r="H50" s="5">
         <v>0.7</v>
       </c>
+      <c r="I50">
+        <v>0.39</v>
+      </c>
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
@@ -2411,6 +2558,9 @@
       <c r="H51" s="5">
         <v>0.88</v>
       </c>
+      <c r="I51">
+        <v>0.76</v>
+      </c>
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
@@ -2432,6 +2582,9 @@
       <c r="H52" s="4">
         <v>0.63</v>
       </c>
+      <c r="I52">
+        <v>0.67</v>
+      </c>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
@@ -2453,6 +2606,9 @@
       <c r="H53" s="5">
         <v>0.88</v>
       </c>
+      <c r="I53">
+        <v>0.52</v>
+      </c>
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
@@ -2474,6 +2630,9 @@
       <c r="H54" s="5">
         <v>0.49</v>
       </c>
+      <c r="I54">
+        <v>0.72</v>
+      </c>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
@@ -2495,6 +2654,9 @@
       <c r="H55" s="4">
         <v>0.76</v>
       </c>
+      <c r="I55">
+        <v>0.8</v>
+      </c>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
@@ -2515,6 +2677,9 @@
       </c>
       <c r="H56" s="4">
         <v>0.78</v>
+      </c>
+      <c r="I56">
+        <v>0.54</v>
       </c>
       <c r="M56" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE5E105-F530-3949-B940-7B6EF2A9312C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F14AD2F-A08C-DF4F-87BC-32FF8EA87DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1280" yWindow="920" windowWidth="25080" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1385,6 +1385,9 @@
       <c r="I2">
         <v>0.41</v>
       </c>
+      <c r="J2">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="M2" s="17"/>
     </row>
     <row r="3" spans="1:13">
@@ -1769,6 +1772,9 @@
       <c r="I18">
         <v>0.54</v>
       </c>
+      <c r="J18">
+        <v>0.26</v>
+      </c>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
@@ -1793,6 +1799,9 @@
       <c r="I19">
         <v>0</v>
       </c>
+      <c r="J19">
+        <v>0.94</v>
+      </c>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
@@ -1865,6 +1874,9 @@
       <c r="I22">
         <v>0.76</v>
       </c>
+      <c r="J22">
+        <v>0.65</v>
+      </c>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
@@ -1889,6 +1901,9 @@
       <c r="I23">
         <v>0.33</v>
       </c>
+      <c r="J23">
+        <v>0.85</v>
+      </c>
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
@@ -2033,6 +2048,9 @@
       <c r="I29">
         <v>0</v>
       </c>
+      <c r="J29">
+        <v>0.88</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -2057,6 +2075,9 @@
       <c r="I30">
         <v>0.56999999999999995</v>
       </c>
+      <c r="J30">
+        <v>0.62</v>
+      </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
@@ -2201,6 +2222,9 @@
       <c r="I36">
         <v>0.74</v>
       </c>
+      <c r="J36">
+        <v>0.83</v>
+      </c>
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="1:13">
@@ -2321,6 +2345,9 @@
       <c r="I41">
         <v>0.5</v>
       </c>
+      <c r="J41">
+        <v>0.86</v>
+      </c>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
@@ -2369,6 +2396,9 @@
       <c r="I43">
         <v>0.52</v>
       </c>
+      <c r="J43">
+        <v>0.94</v>
+      </c>
       <c r="M43" s="6"/>
     </row>
     <row r="44" spans="1:13">
@@ -2417,6 +2447,9 @@
       <c r="I45">
         <v>0.67</v>
       </c>
+      <c r="J45">
+        <v>0.77</v>
+      </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
@@ -2465,6 +2498,9 @@
       <c r="I47">
         <v>0.61</v>
       </c>
+      <c r="J47">
+        <v>0.86</v>
+      </c>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
@@ -2633,6 +2669,9 @@
       <c r="I54">
         <v>0.72</v>
       </c>
+      <c r="J54">
+        <v>0.45</v>
+      </c>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
@@ -2656,6 +2695,9 @@
       </c>
       <c r="I55">
         <v>0.8</v>
+      </c>
+      <c r="J55">
+        <v>0.77</v>
       </c>
       <c r="M55" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F14AD2F-A08C-DF4F-87BC-32FF8EA87DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE61CE0-A6EA-844D-A9CA-AAAB6754BE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="920" windowWidth="25080" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1280" yWindow="920" windowWidth="14580" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1376,6 +1376,9 @@
       <c r="D2" s="4">
         <v>0.73</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
       <c r="G2">
         <v>0.32</v>
       </c>
@@ -1403,6 +1406,9 @@
       <c r="D3" s="4">
         <v>0.85</v>
       </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>0.64</v>
       </c>
@@ -1427,6 +1433,9 @@
       <c r="D4" s="4">
         <v>0.46</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
       <c r="G4">
         <v>0.41</v>
       </c>
@@ -1451,6 +1460,9 @@
       <c r="D5" s="4">
         <v>0.82</v>
       </c>
+      <c r="E5">
+        <v>0.83</v>
+      </c>
       <c r="G5">
         <v>0.14000000000000001</v>
       </c>
@@ -1475,6 +1487,9 @@
       <c r="D6" s="4">
         <v>0.9</v>
       </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
       <c r="G6">
         <v>0.59</v>
       </c>
@@ -1499,6 +1514,9 @@
       <c r="D7" s="4">
         <v>0.76</v>
       </c>
+      <c r="E7">
+        <v>0.68</v>
+      </c>
       <c r="G7">
         <v>0.34</v>
       </c>
@@ -1523,6 +1541,9 @@
       <c r="D8" s="4">
         <v>0.91</v>
       </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
       <c r="G8">
         <v>0.3</v>
       </c>
@@ -1547,6 +1568,9 @@
       <c r="D9" s="4">
         <v>0.56000000000000005</v>
       </c>
+      <c r="E9">
+        <v>0.81</v>
+      </c>
       <c r="G9">
         <v>0.43</v>
       </c>
@@ -1571,6 +1595,9 @@
       <c r="D10" s="4">
         <v>0.78</v>
       </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
       <c r="G10">
         <v>0.48</v>
       </c>
@@ -1595,6 +1622,9 @@
       <c r="D11" s="4">
         <v>0.71</v>
       </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
       <c r="G11">
         <v>0.73</v>
       </c>
@@ -1619,6 +1649,9 @@
       <c r="D12" s="4">
         <v>0.85</v>
       </c>
+      <c r="E12">
+        <v>0.87</v>
+      </c>
       <c r="G12">
         <v>0.45</v>
       </c>
@@ -1643,6 +1676,9 @@
       <c r="D13" s="4">
         <v>0.93</v>
       </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
       <c r="G13">
         <v>0.59</v>
       </c>
@@ -1667,6 +1703,9 @@
       <c r="D14" s="4">
         <v>0.91</v>
       </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
       <c r="G14">
         <v>0.27</v>
       </c>
@@ -1691,6 +1730,9 @@
       <c r="D15" s="4">
         <v>0.89</v>
       </c>
+      <c r="E15">
+        <v>0.81</v>
+      </c>
       <c r="G15">
         <v>0.2</v>
       </c>
@@ -1715,6 +1757,9 @@
       <c r="D16" s="4">
         <v>0.55000000000000004</v>
       </c>
+      <c r="E16">
+        <v>0.87</v>
+      </c>
       <c r="G16">
         <v>0.36</v>
       </c>
@@ -1739,6 +1784,9 @@
       <c r="D17" s="4">
         <v>0.85</v>
       </c>
+      <c r="E17">
+        <v>0.87</v>
+      </c>
       <c r="G17">
         <v>0.55000000000000004</v>
       </c>
@@ -1763,6 +1811,9 @@
       <c r="D18" s="4">
         <v>0.93</v>
       </c>
+      <c r="E18">
+        <v>0.94</v>
+      </c>
       <c r="G18">
         <v>0.41</v>
       </c>
@@ -1790,6 +1841,9 @@
       <c r="D19" s="4">
         <v>0.85</v>
       </c>
+      <c r="E19">
+        <v>0.94</v>
+      </c>
       <c r="G19">
         <v>0.32</v>
       </c>
@@ -1817,6 +1871,9 @@
       <c r="D20" s="4">
         <v>0.93</v>
       </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
       <c r="G20">
         <v>0.56999999999999995</v>
       </c>
@@ -1841,6 +1898,9 @@
       <c r="D21" s="4">
         <v>0.85</v>
       </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
       <c r="G21">
         <v>0.61</v>
       </c>
@@ -1865,6 +1925,9 @@
       <c r="D22" s="4">
         <v>0.78</v>
       </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
       <c r="G22">
         <v>0.39</v>
       </c>
@@ -1892,6 +1955,9 @@
       <c r="D23" s="4">
         <v>0.82</v>
       </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
       <c r="G23">
         <v>0.23</v>
       </c>
@@ -1919,6 +1985,9 @@
       <c r="D24" s="4">
         <v>0.82</v>
       </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
       <c r="G24">
         <v>0.45</v>
       </c>
@@ -1943,6 +2012,9 @@
       <c r="D25" s="4">
         <v>0.85</v>
       </c>
+      <c r="E25">
+        <v>0.81</v>
+      </c>
       <c r="G25">
         <v>0.41</v>
       </c>
@@ -1967,6 +2039,9 @@
       <c r="D26" s="4">
         <v>0</v>
       </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
       <c r="G26">
         <v>0.3</v>
       </c>
@@ -1991,6 +2066,9 @@
       <c r="D27" s="4">
         <v>0.78</v>
       </c>
+      <c r="E27">
+        <v>0.74</v>
+      </c>
       <c r="G27">
         <v>0.3</v>
       </c>
@@ -2015,6 +2093,9 @@
       <c r="D28" s="4">
         <v>0.5</v>
       </c>
+      <c r="E28">
+        <v>0.87</v>
+      </c>
       <c r="G28">
         <v>0.56999999999999995</v>
       </c>
@@ -2039,6 +2120,9 @@
       <c r="D29" s="4">
         <v>0.93</v>
       </c>
+      <c r="E29">
+        <v>0.94</v>
+      </c>
       <c r="G29">
         <v>0.55000000000000004</v>
       </c>
@@ -2066,6 +2150,9 @@
       <c r="D30" s="4">
         <v>0.93</v>
       </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
       <c r="G30">
         <v>0.5</v>
       </c>
@@ -2093,6 +2180,9 @@
       <c r="D31" s="4">
         <v>0.72</v>
       </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
       <c r="G31">
         <v>0.32</v>
       </c>
@@ -2117,6 +2207,9 @@
       <c r="D32" s="4">
         <v>0.46</v>
       </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
       <c r="G32">
         <v>0.36</v>
       </c>
@@ -2141,6 +2234,9 @@
       <c r="D33" s="4">
         <v>0.9</v>
       </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
       <c r="G33">
         <v>0.23</v>
       </c>
@@ -2165,6 +2261,9 @@
       <c r="D34" s="4">
         <v>0.89</v>
       </c>
+      <c r="E34">
+        <v>0.94</v>
+      </c>
       <c r="G34">
         <v>0.52</v>
       </c>
@@ -2189,6 +2288,9 @@
       <c r="D35" s="4">
         <v>0</v>
       </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
       <c r="G35">
         <v>0</v>
       </c>
@@ -2213,6 +2315,9 @@
       <c r="D36" s="4">
         <v>0.63</v>
       </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
       <c r="G36">
         <v>0.39</v>
       </c>
@@ -2240,6 +2345,9 @@
       <c r="D37" s="4">
         <v>0.85</v>
       </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
       <c r="G37">
         <v>0.45</v>
       </c>
@@ -2264,6 +2372,9 @@
       <c r="D38" s="4">
         <v>0.93</v>
       </c>
+      <c r="E38">
+        <v>0.83</v>
+      </c>
       <c r="G38">
         <v>0.34</v>
       </c>
@@ -2288,6 +2399,9 @@
       <c r="D39" s="4">
         <v>0.93</v>
       </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
       <c r="G39">
         <v>0.77</v>
       </c>
@@ -2312,6 +2426,9 @@
       <c r="D40" s="4">
         <v>0.77</v>
       </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
       <c r="G40">
         <v>0.55000000000000004</v>
       </c>
@@ -2336,6 +2453,9 @@
       <c r="D41" s="4">
         <v>0.78</v>
       </c>
+      <c r="E41">
+        <v>0.87</v>
+      </c>
       <c r="G41">
         <v>0.59</v>
       </c>
@@ -2363,6 +2483,9 @@
       <c r="D42" s="4">
         <v>0.93</v>
       </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
       <c r="G42">
         <v>0.52</v>
       </c>
@@ -2387,6 +2510,9 @@
       <c r="D43" s="4">
         <v>0.78</v>
       </c>
+      <c r="E43">
+        <v>0.94</v>
+      </c>
       <c r="G43">
         <v>0.56999999999999995</v>
       </c>
@@ -2414,6 +2540,9 @@
       <c r="D44" s="4">
         <v>0.93</v>
       </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
       <c r="G44">
         <v>0.36</v>
       </c>
@@ -2438,6 +2567,9 @@
       <c r="D45" s="4">
         <v>0.93</v>
       </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
       <c r="G45">
         <v>0.68</v>
       </c>
@@ -2465,6 +2597,9 @@
       <c r="D46" s="4">
         <v>0.93</v>
       </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
       <c r="G46">
         <v>0.5</v>
       </c>
@@ -2489,6 +2624,9 @@
       <c r="D47" s="11">
         <v>0.6</v>
       </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
       <c r="G47">
         <v>0.52</v>
       </c>
@@ -2516,6 +2654,9 @@
       <c r="D48" s="11">
         <v>0.93</v>
       </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
       <c r="G48">
         <v>0.52</v>
       </c>
@@ -2540,6 +2681,9 @@
       <c r="D49" s="11">
         <v>0.67</v>
       </c>
+      <c r="E49">
+        <v>0.74</v>
+      </c>
       <c r="G49">
         <v>0.39</v>
       </c>
@@ -2564,6 +2708,9 @@
       <c r="D50" s="11">
         <v>0</v>
       </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
       <c r="G50">
         <v>0.23</v>
       </c>
@@ -2588,6 +2735,9 @@
       <c r="D51" s="11">
         <v>0.82</v>
       </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
       <c r="G51">
         <v>0.66</v>
       </c>
@@ -2612,6 +2762,9 @@
       <c r="D52" s="11">
         <v>0.82</v>
       </c>
+      <c r="E52">
+        <v>0.83</v>
+      </c>
       <c r="G52">
         <v>0</v>
       </c>
@@ -2636,6 +2789,9 @@
       <c r="D53" s="11">
         <v>0.9</v>
       </c>
+      <c r="E53">
+        <v>0.81</v>
+      </c>
       <c r="G53">
         <v>0.45</v>
       </c>
@@ -2660,6 +2816,9 @@
       <c r="D54" s="11">
         <v>0.93</v>
       </c>
+      <c r="E54">
+        <v>0.87</v>
+      </c>
       <c r="G54">
         <v>0.34</v>
       </c>
@@ -2687,6 +2846,9 @@
       <c r="D55" s="11">
         <v>0.83</v>
       </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
       <c r="G55">
         <v>0.5</v>
       </c>
@@ -2714,6 +2876,9 @@
       <c r="D56" s="11">
         <v>0.85</v>
       </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
       <c r="G56">
         <v>0</v>
       </c>
@@ -2738,6 +2903,9 @@
       <c r="D57" s="11">
         <v>0.97</v>
       </c>
+      <c r="E57">
+        <v>0.96</v>
+      </c>
       <c r="G57">
         <v>0.45</v>
       </c>
@@ -2762,6 +2930,9 @@
       <c r="D58" s="11">
         <v>0.97</v>
       </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
       <c r="G58">
         <v>0.69</v>
       </c>
@@ -2789,6 +2960,9 @@
       <c r="D59" s="11">
         <v>0.81</v>
       </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
       <c r="G59">
         <v>0.56000000000000005</v>
       </c>
@@ -2813,6 +2987,9 @@
       <c r="D60" s="11">
         <v>0.95</v>
       </c>
+      <c r="E60">
+        <v>0.88</v>
+      </c>
       <c r="G60">
         <v>0</v>
       </c>
@@ -2837,6 +3014,9 @@
       <c r="D61" s="11">
         <v>0.9</v>
       </c>
+      <c r="E61">
+        <v>0.88</v>
+      </c>
       <c r="G61">
         <v>0.47</v>
       </c>
@@ -2861,6 +3041,9 @@
       <c r="D62" s="11">
         <v>0.9</v>
       </c>
+      <c r="E62">
+        <v>0.96</v>
+      </c>
       <c r="G62">
         <v>0.45</v>
       </c>
@@ -2885,6 +3068,9 @@
       <c r="D63" s="11">
         <v>0.97</v>
       </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
       <c r="G63">
         <v>0.56000000000000005</v>
       </c>
@@ -2909,6 +3095,9 @@
       <c r="D64" s="11">
         <v>0</v>
       </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
       <c r="G64">
         <v>0</v>
       </c>
@@ -2933,6 +3122,9 @@
       <c r="D65" s="11">
         <v>0.89</v>
       </c>
+      <c r="E65">
+        <v>0.96</v>
+      </c>
       <c r="G65">
         <v>0.6</v>
       </c>
@@ -2957,6 +3149,9 @@
       <c r="D66" s="11">
         <v>0.97</v>
       </c>
+      <c r="E66">
+        <v>0.96</v>
+      </c>
       <c r="G66">
         <v>0.56000000000000005</v>
       </c>
@@ -2981,6 +3176,9 @@
       <c r="D67" s="11">
         <v>0</v>
       </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
       <c r="G67">
         <v>0</v>
       </c>
@@ -3005,6 +3203,9 @@
       <c r="D68" s="11">
         <v>0.8</v>
       </c>
+      <c r="E68">
+        <v>0.85</v>
+      </c>
       <c r="G68">
         <v>0.27</v>
       </c>
@@ -3029,6 +3230,9 @@
       <c r="D69" s="11">
         <v>0.92</v>
       </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
       <c r="G69">
         <v>0.45</v>
       </c>
@@ -3053,6 +3257,9 @@
       <c r="D70" s="11">
         <v>0.97</v>
       </c>
+      <c r="E70">
+        <v>0.92</v>
+      </c>
       <c r="G70">
         <v>0.6</v>
       </c>
@@ -3077,6 +3284,9 @@
       <c r="D71" s="11">
         <v>0.75</v>
       </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
       <c r="G71">
         <v>0.42</v>
       </c>
@@ -3101,6 +3311,9 @@
       <c r="D72" s="11">
         <v>0.97</v>
       </c>
+      <c r="E72">
+        <v>0.92</v>
+      </c>
       <c r="G72">
         <v>0.4</v>
       </c>
@@ -3125,6 +3338,9 @@
       <c r="D73" s="11">
         <v>0.97</v>
       </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
       <c r="G73">
         <v>0.4</v>
       </c>
@@ -3152,6 +3368,9 @@
       <c r="D74" s="11">
         <v>0.83</v>
       </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
       <c r="G74">
         <v>0.28000000000000003</v>
       </c>
@@ -3179,6 +3398,9 @@
       <c r="D75" s="11">
         <v>0.88</v>
       </c>
+      <c r="E75">
+        <v>0.96</v>
+      </c>
       <c r="G75">
         <v>0.06</v>
       </c>
@@ -3206,6 +3428,9 @@
       <c r="D76" s="11">
         <v>0.82</v>
       </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
       <c r="G76">
         <v>0.57999999999999996</v>
       </c>
@@ -3230,6 +3455,9 @@
       <c r="D77" s="11">
         <v>0.88</v>
       </c>
+      <c r="E77">
+        <v>0.92</v>
+      </c>
       <c r="G77">
         <v>0.5</v>
       </c>
@@ -3257,6 +3485,9 @@
       <c r="D78" s="11">
         <v>0.8</v>
       </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
       <c r="G78">
         <v>0.28999999999999998</v>
       </c>
@@ -3281,6 +3512,9 @@
       <c r="D79" s="11">
         <v>0.94</v>
       </c>
+      <c r="E79">
+        <v>0.92</v>
+      </c>
       <c r="G79">
         <v>0.59</v>
       </c>
@@ -3305,6 +3539,9 @@
       <c r="D80" s="11">
         <v>0.95</v>
       </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
       <c r="G80">
         <v>0.08</v>
       </c>
@@ -3329,6 +3566,9 @@
       <c r="D81" s="11">
         <v>0.97</v>
       </c>
+      <c r="E81">
+        <v>0.92</v>
+      </c>
       <c r="G81">
         <v>0.72</v>
       </c>
@@ -3356,6 +3596,9 @@
       <c r="D82" s="11">
         <v>0.95</v>
       </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
       <c r="G82">
         <v>0.46</v>
       </c>
@@ -3380,6 +3623,9 @@
       <c r="D83" s="4">
         <v>0.9</v>
       </c>
+      <c r="E83">
+        <v>0.85</v>
+      </c>
       <c r="G83">
         <v>0.4</v>
       </c>
@@ -3404,6 +3650,9 @@
       <c r="D84" s="11">
         <v>0.81</v>
       </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
       <c r="G84">
         <v>0.15</v>
       </c>
@@ -3428,6 +3677,9 @@
       <c r="D85" s="11">
         <v>0</v>
       </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
       <c r="G85">
         <v>0.37</v>
       </c>
@@ -3452,6 +3704,9 @@
       <c r="D86" s="11">
         <v>0.89</v>
       </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
       <c r="G86">
         <v>0.59</v>
       </c>
@@ -3476,6 +3731,9 @@
       <c r="D87" s="11">
         <v>0.97</v>
       </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
       <c r="G87">
         <v>0.59</v>
       </c>
@@ -3500,6 +3758,9 @@
       <c r="D88" s="11">
         <v>0.83</v>
       </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
       <c r="G88">
         <v>0.65</v>
       </c>
@@ -3524,6 +3785,9 @@
       <c r="D89" s="11">
         <v>0.96</v>
       </c>
+      <c r="E89">
+        <v>0.73</v>
+      </c>
       <c r="G89">
         <v>0.65</v>
       </c>
@@ -3551,6 +3815,9 @@
       <c r="D90" s="11">
         <v>0.97</v>
       </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
       <c r="G90">
         <v>0.54</v>
       </c>
@@ -3575,6 +3842,9 @@
       <c r="D91" s="11">
         <v>0.82</v>
       </c>
+      <c r="E91">
+        <v>0.85</v>
+      </c>
       <c r="G91">
         <v>0.56000000000000005</v>
       </c>
@@ -3602,6 +3872,9 @@
       <c r="D92" s="11">
         <v>0.89</v>
       </c>
+      <c r="E92">
+        <v>0.96</v>
+      </c>
       <c r="G92">
         <v>0.44</v>
       </c>
@@ -3626,6 +3899,9 @@
       <c r="D93" s="11">
         <v>0.94</v>
       </c>
+      <c r="E93">
+        <v>0.96</v>
+      </c>
       <c r="G93">
         <v>0.53</v>
       </c>
@@ -3653,6 +3929,9 @@
       <c r="D94" s="11">
         <v>0.94</v>
       </c>
+      <c r="E94">
+        <v>0.92</v>
+      </c>
       <c r="G94">
         <v>0.71</v>
       </c>
@@ -3677,6 +3956,9 @@
       <c r="D95" s="11">
         <v>0.94</v>
       </c>
+      <c r="E95">
+        <v>0.85</v>
+      </c>
       <c r="G95">
         <v>0.63</v>
       </c>
@@ -3701,6 +3983,9 @@
       <c r="D96" s="11">
         <v>0</v>
       </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
       <c r="G96">
         <v>0</v>
       </c>
@@ -3725,6 +4010,9 @@
       <c r="D97" s="11">
         <v>0.91</v>
       </c>
+      <c r="E97">
+        <v>0.92</v>
+      </c>
       <c r="G97">
         <v>0.51</v>
       </c>
@@ -3749,6 +4037,9 @@
       <c r="D98" s="11">
         <v>0</v>
       </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
       <c r="G98">
         <v>0</v>
       </c>
@@ -3773,6 +4064,9 @@
       <c r="D99" s="11">
         <v>0.97</v>
       </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
       <c r="G99">
         <v>0.62</v>
       </c>
@@ -3797,6 +4091,9 @@
       <c r="D100" s="11">
         <v>0.97</v>
       </c>
+      <c r="E100">
+        <v>0.96</v>
+      </c>
       <c r="G100">
         <v>0.54</v>
       </c>
@@ -3821,6 +4118,9 @@
       <c r="D101" s="11">
         <v>0.88</v>
       </c>
+      <c r="E101">
+        <v>0.96</v>
+      </c>
       <c r="G101">
         <v>0.19</v>
       </c>
@@ -3845,6 +4145,9 @@
       <c r="D102" s="11">
         <v>0.97</v>
       </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
       <c r="G102">
         <v>0.72</v>
       </c>
@@ -3872,6 +4175,9 @@
       <c r="D103" s="11">
         <v>0.97</v>
       </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
       <c r="G103">
         <v>0.33</v>
       </c>
@@ -3896,6 +4202,9 @@
       <c r="D104" s="11">
         <v>0.96</v>
       </c>
+      <c r="E104">
+        <v>0.92</v>
+      </c>
       <c r="G104">
         <v>0.32</v>
       </c>
@@ -3920,6 +4229,9 @@
       <c r="D105" s="11">
         <v>0.85</v>
       </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
       <c r="G105">
         <v>0.44</v>
       </c>
@@ -3944,6 +4256,9 @@
       <c r="D106" s="11">
         <v>0.91</v>
       </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
       <c r="G106">
         <v>0.59</v>
       </c>
@@ -3971,6 +4286,9 @@
       <c r="D107" s="11">
         <v>0.94</v>
       </c>
+      <c r="E107">
+        <v>0.96</v>
+      </c>
       <c r="G107">
         <v>0.57999999999999996</v>
       </c>
@@ -3995,6 +4313,9 @@
       <c r="D108" s="11">
         <v>0.94</v>
       </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
       <c r="G108">
         <v>0.47</v>
       </c>
@@ -4017,6 +4338,9 @@
       <c r="D109" s="11">
         <v>0</v>
       </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
       <c r="G109">
         <v>0</v>
       </c>
@@ -4041,6 +4365,9 @@
       <c r="D110" s="11">
         <v>0.97</v>
       </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
       <c r="G110">
         <v>0.54</v>
       </c>
@@ -4065,6 +4392,9 @@
       <c r="D111" s="11">
         <v>0.94</v>
       </c>
+      <c r="E111">
+        <v>0.96</v>
+      </c>
       <c r="G111">
         <v>0.63</v>
       </c>
@@ -4089,6 +4419,9 @@
       <c r="D112" s="11">
         <v>0.97</v>
       </c>
+      <c r="E112">
+        <v>0.92</v>
+      </c>
       <c r="G112">
         <v>0.53</v>
       </c>
@@ -4113,6 +4446,9 @@
       <c r="D113" s="11">
         <v>0.97</v>
       </c>
+      <c r="E113">
+        <v>0.96</v>
+      </c>
       <c r="G113">
         <v>0.49</v>
       </c>
@@ -4137,6 +4473,9 @@
       <c r="D114" s="11">
         <v>0.97</v>
       </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
       <c r="G114">
         <v>0.54</v>
       </c>
@@ -4160,6 +4499,9 @@
       </c>
       <c r="D115" s="11">
         <v>0.89</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
       </c>
       <c r="G115">
         <v>0.51</v>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE61CE0-A6EA-844D-A9CA-AAAB6754BE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05DFC0E-1A9E-7948-B598-CC90CC768EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="920" windowWidth="14580" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1280" yWindow="920" windowWidth="29640" windowHeight="17080" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <webPublishing allowPng="1" targetScreenSize="1024x768" codePage="10000"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05DFC0E-1A9E-7948-B598-CC90CC768EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D16C70-FAB9-CA40-B804-C8B4C7C044C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="920" windowWidth="29640" windowHeight="17080" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="20" yWindow="720" windowWidth="17360" windowHeight="17100" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2934,6 +2934,9 @@
       <c r="E58">
         <v>1</v>
       </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
       <c r="G58">
         <v>0.69</v>
       </c>
@@ -2964,6 +2967,9 @@
       <c r="E59">
         <v>1</v>
       </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
       <c r="G59">
         <v>0.56000000000000005</v>
       </c>
@@ -2991,6 +2997,9 @@
       <c r="E60">
         <v>0.88</v>
       </c>
+      <c r="F60">
+        <v>0.89</v>
+      </c>
       <c r="G60">
         <v>0</v>
       </c>
@@ -3018,6 +3027,9 @@
       <c r="E61">
         <v>0.88</v>
       </c>
+      <c r="F61">
+        <v>0.96</v>
+      </c>
       <c r="G61">
         <v>0.47</v>
       </c>
@@ -3026,6 +3038,9 @@
       </c>
       <c r="I61">
         <v>0.46</v>
+      </c>
+      <c r="J61">
+        <v>0.86</v>
       </c>
       <c r="M61" s="6"/>
     </row>
@@ -3045,6 +3060,9 @@
       <c r="E62">
         <v>0.96</v>
       </c>
+      <c r="F62">
+        <v>0.96</v>
+      </c>
       <c r="G62">
         <v>0.45</v>
       </c>
@@ -3053,6 +3071,9 @@
       </c>
       <c r="I62">
         <v>0.44</v>
+      </c>
+      <c r="J62">
+        <v>0.94</v>
       </c>
       <c r="M62" s="6"/>
     </row>
@@ -3072,6 +3093,9 @@
       <c r="E63">
         <v>1</v>
       </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
       <c r="G63">
         <v>0.56000000000000005</v>
       </c>
@@ -3099,6 +3123,9 @@
       <c r="E64">
         <v>0</v>
       </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
       <c r="G64">
         <v>0</v>
       </c>
@@ -3126,6 +3153,9 @@
       <c r="E65">
         <v>0.96</v>
       </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
       <c r="G65">
         <v>0.6</v>
       </c>
@@ -3134,6 +3164,9 @@
       </c>
       <c r="I65">
         <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.94</v>
       </c>
       <c r="M65" s="6"/>
     </row>
@@ -3153,6 +3186,9 @@
       <c r="E66">
         <v>0.96</v>
       </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
       <c r="G66">
         <v>0.56000000000000005</v>
       </c>
@@ -3180,6 +3216,9 @@
       <c r="E67">
         <v>0</v>
       </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
       <c r="G67">
         <v>0</v>
       </c>
@@ -3207,6 +3246,9 @@
       <c r="E68">
         <v>0.85</v>
       </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
       <c r="G68">
         <v>0.27</v>
       </c>
@@ -3215,6 +3257,9 @@
       </c>
       <c r="I68">
         <v>0.65</v>
+      </c>
+      <c r="J68">
+        <v>0.83</v>
       </c>
       <c r="M68" s="6"/>
     </row>
@@ -3234,6 +3279,9 @@
       <c r="E69">
         <v>1</v>
       </c>
+      <c r="F69">
+        <v>0.93</v>
+      </c>
       <c r="G69">
         <v>0.45</v>
       </c>
@@ -3261,6 +3309,9 @@
       <c r="E70">
         <v>0.92</v>
       </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
       <c r="G70">
         <v>0.6</v>
       </c>
@@ -3288,6 +3339,9 @@
       <c r="E71">
         <v>1</v>
       </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
       <c r="G71">
         <v>0.42</v>
       </c>
@@ -3296,6 +3350,9 @@
       </c>
       <c r="I71">
         <v>0.28999999999999998</v>
+      </c>
+      <c r="J71">
+        <v>0.83</v>
       </c>
       <c r="M71" s="6"/>
     </row>
@@ -3315,6 +3372,9 @@
       <c r="E72">
         <v>0.92</v>
       </c>
+      <c r="F72">
+        <v>0.85</v>
+      </c>
       <c r="G72">
         <v>0.4</v>
       </c>
@@ -3342,6 +3402,9 @@
       <c r="E73">
         <v>0</v>
       </c>
+      <c r="F73">
+        <v>0.93</v>
+      </c>
       <c r="G73">
         <v>0.4</v>
       </c>
@@ -3372,6 +3435,9 @@
       <c r="E74">
         <v>0</v>
       </c>
+      <c r="F74">
+        <v>0.96</v>
+      </c>
       <c r="G74">
         <v>0.28000000000000003</v>
       </c>
@@ -3402,6 +3468,9 @@
       <c r="E75">
         <v>0.96</v>
       </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
       <c r="G75">
         <v>0.06</v>
       </c>
@@ -3432,6 +3501,9 @@
       <c r="E76">
         <v>1</v>
       </c>
+      <c r="F76">
+        <v>0.96</v>
+      </c>
       <c r="G76">
         <v>0.57999999999999996</v>
       </c>
@@ -3440,6 +3512,9 @@
       </c>
       <c r="I76">
         <v>0.56000000000000005</v>
+      </c>
+      <c r="J76">
+        <v>0.86</v>
       </c>
       <c r="M76" s="6"/>
     </row>
@@ -3459,6 +3534,9 @@
       <c r="E77">
         <v>0.92</v>
       </c>
+      <c r="F77">
+        <v>0.85</v>
+      </c>
       <c r="G77">
         <v>0.5</v>
       </c>
@@ -3489,6 +3567,9 @@
       <c r="E78">
         <v>1</v>
       </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
       <c r="G78">
         <v>0.28999999999999998</v>
       </c>
@@ -3516,6 +3597,9 @@
       <c r="E79">
         <v>0.92</v>
       </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
       <c r="G79">
         <v>0.59</v>
       </c>
@@ -3524,6 +3608,9 @@
       </c>
       <c r="I79">
         <v>0.69</v>
+      </c>
+      <c r="J79">
+        <v>0.94</v>
       </c>
       <c r="M79" s="6"/>
     </row>
@@ -3543,6 +3630,9 @@
       <c r="E80">
         <v>1</v>
       </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
       <c r="G80">
         <v>0.08</v>
       </c>
@@ -3551,6 +3641,9 @@
       </c>
       <c r="I80">
         <v>0.12</v>
+      </c>
+      <c r="J80">
+        <v>0.94</v>
       </c>
       <c r="M80" s="6"/>
     </row>
@@ -3570,6 +3663,9 @@
       <c r="E81">
         <v>0.92</v>
       </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
       <c r="G81">
         <v>0.72</v>
       </c>
@@ -3600,6 +3696,9 @@
       <c r="E82">
         <v>1</v>
       </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
       <c r="G82">
         <v>0.46</v>
       </c>
@@ -3627,6 +3726,9 @@
       <c r="E83">
         <v>0.85</v>
       </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
       <c r="G83">
         <v>0.4</v>
       </c>
@@ -3635,6 +3737,9 @@
       </c>
       <c r="I83">
         <v>0.25</v>
+      </c>
+      <c r="J83">
+        <v>0.69</v>
       </c>
       <c r="M83" s="6"/>
     </row>
@@ -3654,6 +3759,9 @@
       <c r="E84">
         <v>1</v>
       </c>
+      <c r="F84">
+        <v>0.89</v>
+      </c>
       <c r="G84">
         <v>0.15</v>
       </c>
@@ -3681,6 +3789,9 @@
       <c r="E85">
         <v>0</v>
       </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
       <c r="G85">
         <v>0.37</v>
       </c>
@@ -3708,6 +3819,9 @@
       <c r="E86">
         <v>1</v>
       </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
       <c r="G86">
         <v>0.59</v>
       </c>
@@ -3735,6 +3849,9 @@
       <c r="E87">
         <v>1</v>
       </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
       <c r="G87">
         <v>0.59</v>
       </c>
@@ -3762,6 +3879,9 @@
       <c r="E88">
         <v>1</v>
       </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
       <c r="G88">
         <v>0.65</v>
       </c>
@@ -3770,6 +3890,9 @@
       </c>
       <c r="I88">
         <v>0.56000000000000005</v>
+      </c>
+      <c r="J88">
+        <v>0.86</v>
       </c>
       <c r="M88" s="6"/>
     </row>
@@ -3789,6 +3912,9 @@
       <c r="E89">
         <v>0.73</v>
       </c>
+      <c r="F89">
+        <v>0.74</v>
+      </c>
       <c r="G89">
         <v>0.65</v>
       </c>
@@ -3819,6 +3945,9 @@
       <c r="E90">
         <v>1</v>
       </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
       <c r="G90">
         <v>0.54</v>
       </c>
@@ -3846,6 +3975,9 @@
       <c r="E91">
         <v>0.85</v>
       </c>
+      <c r="F91">
+        <v>0.93</v>
+      </c>
       <c r="G91">
         <v>0.56000000000000005</v>
       </c>
@@ -3876,6 +4008,9 @@
       <c r="E92">
         <v>0.96</v>
       </c>
+      <c r="F92">
+        <v>0.93</v>
+      </c>
       <c r="G92">
         <v>0.44</v>
       </c>
@@ -3903,6 +4038,9 @@
       <c r="E93">
         <v>0.96</v>
       </c>
+      <c r="F93">
+        <v>0.96</v>
+      </c>
       <c r="G93">
         <v>0.53</v>
       </c>
@@ -3933,6 +4071,9 @@
       <c r="E94">
         <v>0.92</v>
       </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
       <c r="G94">
         <v>0.71</v>
       </c>
@@ -3941,6 +4082,9 @@
       </c>
       <c r="I94">
         <v>0.44</v>
+      </c>
+      <c r="J94">
+        <v>0.83</v>
       </c>
       <c r="M94" s="6"/>
     </row>
@@ -3960,6 +4104,9 @@
       <c r="E95">
         <v>0.85</v>
       </c>
+      <c r="F95">
+        <v>0.67</v>
+      </c>
       <c r="G95">
         <v>0.63</v>
       </c>
@@ -3987,6 +4134,9 @@
       <c r="E96">
         <v>0</v>
       </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
       <c r="G96">
         <v>0</v>
       </c>
@@ -4014,6 +4164,9 @@
       <c r="E97">
         <v>0.92</v>
       </c>
+      <c r="F97">
+        <v>0.96</v>
+      </c>
       <c r="G97">
         <v>0.51</v>
       </c>
@@ -4041,6 +4194,9 @@
       <c r="E98">
         <v>0</v>
       </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
       <c r="G98">
         <v>0</v>
       </c>
@@ -4068,6 +4224,9 @@
       <c r="E99">
         <v>1</v>
       </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
       <c r="G99">
         <v>0.62</v>
       </c>
@@ -4076,6 +4235,9 @@
       </c>
       <c r="I99">
         <v>0.78</v>
+      </c>
+      <c r="J99">
+        <v>0.83</v>
       </c>
       <c r="M99" s="6"/>
     </row>
@@ -4095,6 +4257,9 @@
       <c r="E100">
         <v>0.96</v>
       </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
       <c r="G100">
         <v>0.54</v>
       </c>
@@ -4103,6 +4268,9 @@
       </c>
       <c r="I100">
         <v>0.44</v>
+      </c>
+      <c r="J100">
+        <v>0.86</v>
       </c>
       <c r="M100" s="6"/>
     </row>
@@ -4122,6 +4290,9 @@
       <c r="E101">
         <v>0.96</v>
       </c>
+      <c r="F101">
+        <v>0.89</v>
+      </c>
       <c r="G101">
         <v>0.19</v>
       </c>
@@ -4149,6 +4320,9 @@
       <c r="E102">
         <v>1</v>
       </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
       <c r="G102">
         <v>0.72</v>
       </c>
@@ -4179,6 +4353,9 @@
       <c r="E103">
         <v>1</v>
       </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
       <c r="G103">
         <v>0.33</v>
       </c>
@@ -4187,6 +4364,9 @@
       </c>
       <c r="I103">
         <v>0.28000000000000003</v>
+      </c>
+      <c r="J103">
+        <v>0.92</v>
       </c>
       <c r="M103" s="6"/>
     </row>
@@ -4206,6 +4386,9 @@
       <c r="E104">
         <v>0.92</v>
       </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
       <c r="G104">
         <v>0.32</v>
       </c>
@@ -4233,6 +4416,9 @@
       <c r="E105">
         <v>1</v>
       </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
       <c r="G105">
         <v>0.44</v>
       </c>
@@ -4260,6 +4446,9 @@
       <c r="E106">
         <v>1</v>
       </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
       <c r="G106">
         <v>0.59</v>
       </c>
@@ -4290,6 +4479,9 @@
       <c r="E107">
         <v>0.96</v>
       </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
       <c r="G107">
         <v>0.57999999999999996</v>
       </c>
@@ -4317,6 +4509,9 @@
       <c r="E108">
         <v>1</v>
       </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
       <c r="G108">
         <v>0.47</v>
       </c>
@@ -4325,6 +4520,9 @@
       </c>
       <c r="I108">
         <v>0.44</v>
+      </c>
+      <c r="J108">
+        <v>0.89</v>
       </c>
       <c r="M108" s="6"/>
     </row>
@@ -4342,6 +4540,9 @@
       <c r="E109">
         <v>0</v>
       </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
       <c r="G109">
         <v>0</v>
       </c>
@@ -4369,6 +4570,9 @@
       <c r="E110">
         <v>1</v>
       </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
       <c r="G110">
         <v>0.54</v>
       </c>
@@ -4396,6 +4600,9 @@
       <c r="E111">
         <v>0.96</v>
       </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
       <c r="G111">
         <v>0.63</v>
       </c>
@@ -4423,6 +4630,9 @@
       <c r="E112">
         <v>0.92</v>
       </c>
+      <c r="F112">
+        <v>0.96</v>
+      </c>
       <c r="G112">
         <v>0.53</v>
       </c>
@@ -4431,6 +4641,9 @@
       </c>
       <c r="I112">
         <v>0.6</v>
+      </c>
+      <c r="J112">
+        <v>0.92</v>
       </c>
       <c r="M112" s="6"/>
     </row>
@@ -4450,6 +4663,9 @@
       <c r="E113">
         <v>0.96</v>
       </c>
+      <c r="F113">
+        <v>0.93</v>
+      </c>
       <c r="G113">
         <v>0.49</v>
       </c>
@@ -4458,6 +4674,9 @@
       </c>
       <c r="I113">
         <v>0.32</v>
+      </c>
+      <c r="J113">
+        <v>0.89</v>
       </c>
       <c r="M113" s="6"/>
     </row>
@@ -4477,6 +4696,9 @@
       <c r="E114">
         <v>1</v>
       </c>
+      <c r="F114">
+        <v>0.96</v>
+      </c>
       <c r="G114">
         <v>0.54</v>
       </c>
@@ -4502,6 +4724,9 @@
         <v>0.89</v>
       </c>
       <c r="E115">
+        <v>1</v>
+      </c>
+      <c r="F115">
         <v>1</v>
       </c>
       <c r="G115">

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D16C70-FAB9-CA40-B804-C8B4C7C044C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A006F1-3C66-AD4A-9672-2E1418FB340B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="720" windowWidth="17360" windowHeight="17100" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="20" yWindow="720" windowWidth="23300" windowHeight="17100" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="231">
   <si>
     <t>Surname</t>
   </si>
@@ -441,12 +441,6 @@
     <t>H250427H</t>
   </si>
   <si>
-    <t>Chiota</t>
-  </si>
-  <si>
-    <t>H210130v</t>
-  </si>
-  <si>
     <t>Chishowerere</t>
   </si>
   <si>
@@ -459,12 +453,6 @@
     <t>H250352B</t>
   </si>
   <si>
-    <t>Chitsa</t>
-  </si>
-  <si>
-    <t>H250395M</t>
-  </si>
-  <si>
     <t>Chiwambutsa</t>
   </si>
   <si>
@@ -627,22 +615,10 @@
     <t>H250503V</t>
   </si>
   <si>
-    <t>Mukwara</t>
-  </si>
-  <si>
-    <t>H240380W</t>
-  </si>
-  <si>
     <t>Murasha</t>
   </si>
   <si>
     <t>H250702v</t>
-  </si>
-  <si>
-    <t>Mushayapokuvaka</t>
-  </si>
-  <si>
-    <t>H220311Y</t>
   </si>
   <si>
     <t>MUSINGADI</t>
@@ -974,10 +950,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M228" totalsRowShown="0">
-  <autoFilter ref="A1:M228" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M228">
-    <sortCondition ref="C1:C228"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M224" totalsRowShown="0">
+  <autoFilter ref="A1:M224" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M224">
+    <sortCondition ref="C1:C224"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -1315,7 +1291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CD7F812-EED8-C54E-9DE9-E7B571F78166}">
-  <dimension ref="A1:M228"/>
+  <dimension ref="A1:M224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -2752,10 +2728,10 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="11" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C52" s="11" t="s">
         <v>15</v>
@@ -2866,10 +2842,10 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="11" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>15</v>
@@ -2979,6 +2955,9 @@
       <c r="I59">
         <v>0.6</v>
       </c>
+      <c r="J59">
+        <v>0.72</v>
+      </c>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
@@ -3118,22 +3097,25 @@
         <v>121</v>
       </c>
       <c r="D64" s="11">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H64" s="4">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="I64">
         <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.94</v>
       </c>
       <c r="M64" s="6"/>
     </row>
@@ -3148,7 +3130,7 @@
         <v>121</v>
       </c>
       <c r="D65" s="11">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="E65">
         <v>0.96</v>
@@ -3157,16 +3139,13 @@
         <v>1</v>
       </c>
       <c r="G65">
-        <v>0.6</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H65" s="4">
-        <v>0.71</v>
+        <v>0.54</v>
       </c>
       <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0.94</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M65" s="6"/>
     </row>
@@ -3181,22 +3160,25 @@
         <v>121</v>
       </c>
       <c r="D66" s="11">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="E66">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66">
-        <v>0.56000000000000005</v>
+        <v>0.27</v>
       </c>
       <c r="H66" s="4">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="I66">
-        <v>0.56000000000000005</v>
+        <v>0.65</v>
+      </c>
+      <c r="J66">
+        <v>0.83</v>
       </c>
       <c r="M66" s="6"/>
     </row>
@@ -3211,22 +3193,22 @@
         <v>121</v>
       </c>
       <c r="D67" s="11">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="H67" s="4">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="M67" s="6"/>
     </row>
@@ -3241,25 +3223,25 @@
         <v>121</v>
       </c>
       <c r="D68" s="11">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="E68">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="H68" s="4">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="I68">
-        <v>0.65</v>
+        <v>0.32</v>
       </c>
       <c r="J68">
-        <v>0.83</v>
+        <v>0.69</v>
       </c>
       <c r="M68" s="6"/>
     </row>
@@ -3274,22 +3256,25 @@
         <v>121</v>
       </c>
       <c r="D69" s="11">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="E69">
         <v>1</v>
       </c>
       <c r="F69">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="G69">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="H69" s="4">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="I69">
-        <v>0.34</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J69">
+        <v>0.83</v>
       </c>
       <c r="M69" s="6"/>
     </row>
@@ -3310,16 +3295,19 @@
         <v>0.92</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="G70">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H70" s="4">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="I70">
-        <v>0.32</v>
+        <v>0.38</v>
+      </c>
+      <c r="J70">
+        <v>0.86</v>
       </c>
       <c r="M70" s="6"/>
     </row>
@@ -3334,94 +3322,97 @@
         <v>121</v>
       </c>
       <c r="D71" s="11">
-        <v>0.75</v>
+        <v>0.97</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="G71">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="H71" s="4">
-        <v>0.63</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I71">
-        <v>0.28999999999999998</v>
+        <v>0.34</v>
       </c>
       <c r="J71">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B72" s="11" t="s">
         <v>150</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>151</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D72" s="11">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="E72">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="G72">
-        <v>0.4</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H72" s="4">
         <v>0.31</v>
       </c>
       <c r="I72">
-        <v>0.38</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J72">
+        <v>0.69</v>
       </c>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B73" s="11" t="s">
         <v>152</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>153</v>
       </c>
       <c r="C73" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D73" s="11">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="E73">
+        <v>0.96</v>
+      </c>
+      <c r="F73">
         <v>0</v>
       </c>
-      <c r="F73">
-        <v>0.93</v>
-      </c>
       <c r="G73">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="H73" s="4">
-        <v>0.28999999999999998</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I73">
-        <v>0.34</v>
+        <v>0.41</v>
       </c>
       <c r="J73">
-        <v>0.72</v>
+        <v>0.81</v>
       </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>154</v>
@@ -3430,25 +3421,25 @@
         <v>121</v>
       </c>
       <c r="D74" s="11">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74">
         <v>0.96</v>
       </c>
       <c r="G74">
-        <v>0.28000000000000003</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H74" s="4">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="I74">
-        <v>0.28999999999999998</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="J74">
-        <v>0.69</v>
+        <v>0.86</v>
       </c>
       <c r="M74" s="6"/>
     </row>
@@ -3466,22 +3457,22 @@
         <v>0.88</v>
       </c>
       <c r="E75">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="F75">
+        <v>0.85</v>
+      </c>
+      <c r="G75">
+        <v>0.5</v>
+      </c>
+      <c r="H75" s="4">
         <v>0</v>
-      </c>
-      <c r="G75">
-        <v>0.06</v>
-      </c>
-      <c r="H75" s="4">
-        <v>0.57999999999999996</v>
       </c>
       <c r="I75">
         <v>0.41</v>
       </c>
       <c r="J75">
-        <v>0.81</v>
+        <v>0.53</v>
       </c>
       <c r="M75" s="6"/>
     </row>
@@ -3496,25 +3487,25 @@
         <v>121</v>
       </c>
       <c r="D76" s="11">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
       <c r="F76">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="G76">
-        <v>0.57999999999999996</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H76" s="4">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="I76">
-        <v>0.56000000000000005</v>
+        <v>0.4</v>
       </c>
       <c r="J76">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="M76" s="6"/>
     </row>
@@ -3529,25 +3520,25 @@
         <v>121</v>
       </c>
       <c r="D77" s="11">
-        <v>0.88</v>
+        <v>0.94</v>
       </c>
       <c r="E77">
         <v>0.92</v>
       </c>
       <c r="F77">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="H77" s="4">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="I77">
-        <v>0.41</v>
+        <v>0.69</v>
       </c>
       <c r="J77">
-        <v>0.53</v>
+        <v>0.94</v>
       </c>
       <c r="M77" s="6"/>
     </row>
@@ -3562,7 +3553,7 @@
         <v>121</v>
       </c>
       <c r="D78" s="11">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -3571,13 +3562,16 @@
         <v>1</v>
       </c>
       <c r="G78">
-        <v>0.28999999999999998</v>
+        <v>0.08</v>
       </c>
       <c r="H78" s="4">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="I78">
-        <v>0.4</v>
+        <v>0.12</v>
+      </c>
+      <c r="J78">
+        <v>0.94</v>
       </c>
       <c r="M78" s="6"/>
     </row>
@@ -3592,7 +3586,7 @@
         <v>121</v>
       </c>
       <c r="D79" s="11">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="E79">
         <v>0.92</v>
@@ -3601,16 +3595,16 @@
         <v>1</v>
       </c>
       <c r="G79">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="H79" s="4">
-        <v>0.88</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I79">
-        <v>0.69</v>
+        <v>0.82</v>
       </c>
       <c r="J79">
-        <v>0.94</v>
+        <v>0.89</v>
       </c>
       <c r="M79" s="6"/>
     </row>
@@ -3631,52 +3625,49 @@
         <v>1</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80">
-        <v>0.08</v>
+        <v>0.46</v>
       </c>
       <c r="H80" s="4">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="I80">
-        <v>0.12</v>
-      </c>
-      <c r="J80">
-        <v>0.94</v>
+        <v>0.38</v>
       </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
-      <c r="A81" s="11" t="s">
+      <c r="A81" t="s">
         <v>167</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" t="s">
         <v>121</v>
       </c>
-      <c r="D81" s="11">
-        <v>0.97</v>
+      <c r="D81" s="4">
+        <v>0.9</v>
       </c>
       <c r="E81">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>0.72</v>
+        <v>0.4</v>
       </c>
       <c r="H81" s="4">
-        <v>0.56000000000000005</v>
+        <v>0.31</v>
       </c>
       <c r="I81">
-        <v>0.82</v>
+        <v>0.25</v>
       </c>
       <c r="J81">
-        <v>0.89</v>
+        <v>0.69</v>
       </c>
       <c r="M81" s="6"/>
     </row>
@@ -3691,55 +3682,52 @@
         <v>121</v>
       </c>
       <c r="D82" s="11">
-        <v>0.95</v>
+        <v>0.81</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82">
+        <v>0.89</v>
+      </c>
+      <c r="G82">
+        <v>0.15</v>
+      </c>
+      <c r="H82" s="4">
+        <v>0.35</v>
+      </c>
+      <c r="I82">
+        <v>0.43</v>
+      </c>
+      <c r="M82" s="6"/>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="A83" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D83" s="11">
         <v>0</v>
       </c>
-      <c r="G82">
-        <v>0.46</v>
-      </c>
-      <c r="H82" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I82">
-        <v>0.38</v>
-      </c>
-      <c r="M82" s="6"/>
-    </row>
-    <row r="83" spans="1:13">
-      <c r="A83" t="s">
-        <v>171</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C83" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" s="4">
-        <v>0.9</v>
-      </c>
       <c r="E83">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="F83">
         <v>0</v>
       </c>
       <c r="G83">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="H83" s="4">
+        <v>0.38</v>
+      </c>
+      <c r="I83">
         <v>0.31</v>
-      </c>
-      <c r="I83">
-        <v>0.25</v>
-      </c>
-      <c r="J83">
-        <v>0.69</v>
       </c>
       <c r="M83" s="6"/>
     </row>
@@ -3754,22 +3742,25 @@
         <v>121</v>
       </c>
       <c r="D84" s="11">
-        <v>0.81</v>
+        <v>0.89</v>
       </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="F84">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="G84">
-        <v>0.15</v>
+        <v>0.59</v>
       </c>
       <c r="H84" s="4">
-        <v>0.35</v>
+        <v>0.46</v>
       </c>
       <c r="I84">
-        <v>0.43</v>
+        <v>0.62</v>
+      </c>
+      <c r="J84">
+        <v>0.78</v>
       </c>
       <c r="M84" s="6"/>
     </row>
@@ -3784,22 +3775,25 @@
         <v>121</v>
       </c>
       <c r="D85" s="11">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85">
-        <v>0.37</v>
+        <v>0.59</v>
       </c>
       <c r="H85" s="4">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="I85">
-        <v>0.31</v>
+        <v>0.26</v>
+      </c>
+      <c r="J85">
+        <v>0.86</v>
       </c>
       <c r="M85" s="6"/>
     </row>
@@ -3814,7 +3808,7 @@
         <v>121</v>
       </c>
       <c r="D86" s="11">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="E86">
         <v>1</v>
@@ -3823,13 +3817,16 @@
         <v>1</v>
       </c>
       <c r="G86">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H86" s="4">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="I86">
-        <v>0.62</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J86">
+        <v>0.86</v>
       </c>
       <c r="M86" s="6"/>
     </row>
@@ -3844,22 +3841,25 @@
         <v>121</v>
       </c>
       <c r="D87" s="11">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="G87">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="H87" s="4">
-        <v>0.44</v>
+        <v>0.83</v>
       </c>
       <c r="I87">
-        <v>0.26</v>
+        <v>0.68</v>
+      </c>
+      <c r="J87">
+        <v>0.83</v>
       </c>
       <c r="M87" s="6"/>
     </row>
@@ -3874,25 +3874,25 @@
         <v>121</v>
       </c>
       <c r="D88" s="11">
+        <v>0.97</v>
+      </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>0.54</v>
+      </c>
+      <c r="H88" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="I88">
+        <v>0.75</v>
+      </c>
+      <c r="J88">
         <v>0.83</v>
-      </c>
-      <c r="E88">
-        <v>1</v>
-      </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-      <c r="G88">
-        <v>0.65</v>
-      </c>
-      <c r="H88" s="4">
-        <v>0.52</v>
-      </c>
-      <c r="I88">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="J88">
-        <v>0.86</v>
       </c>
       <c r="M88" s="6"/>
     </row>
@@ -3907,25 +3907,25 @@
         <v>121</v>
       </c>
       <c r="D89" s="11">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="E89">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="F89">
-        <v>0.74</v>
+        <v>0.93</v>
       </c>
       <c r="G89">
-        <v>0.65</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H89" s="4">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="I89">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="J89">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="M89" s="6"/>
     </row>
@@ -3940,22 +3940,22 @@
         <v>121</v>
       </c>
       <c r="D90" s="11">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="E90">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="G90">
-        <v>0.54</v>
+        <v>0.44</v>
       </c>
       <c r="H90" s="4">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="I90">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="M90" s="6"/>
     </row>
@@ -3970,22 +3970,22 @@
         <v>121</v>
       </c>
       <c r="D91" s="11">
-        <v>0.82</v>
+        <v>0.94</v>
       </c>
       <c r="E91">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="F91">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="G91">
-        <v>0.56000000000000005</v>
+        <v>0.53</v>
       </c>
       <c r="H91" s="4">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="J91">
         <v>0.75</v>
@@ -3994,40 +3994,43 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B92" s="11" t="s">
         <v>189</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>190</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D92" s="11">
-        <v>0.89</v>
+        <v>0.94</v>
       </c>
       <c r="E92">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="F92">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="G92">
+        <v>0.71</v>
+      </c>
+      <c r="H92" s="4">
+        <v>0.42</v>
+      </c>
+      <c r="I92">
         <v>0.44</v>
       </c>
-      <c r="H92" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="I92">
-        <v>0.63</v>
+      <c r="J92">
+        <v>0.83</v>
       </c>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B93" s="11" t="s">
         <v>191</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>192</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>121</v>
@@ -4036,28 +4039,28 @@
         <v>0.94</v>
       </c>
       <c r="E93">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="F93">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="G93">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="H93" s="4">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="I93">
-        <v>0.51</v>
+        <v>0.69</v>
       </c>
       <c r="J93">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="11" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>193</v>
@@ -4066,25 +4069,25 @@
         <v>121</v>
       </c>
       <c r="D94" s="11">
-        <v>0.94</v>
+        <v>0.91</v>
       </c>
       <c r="E94">
         <v>0.92</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="G94">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="H94" s="4">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="I94">
-        <v>0.44</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="J94">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="M94" s="6"/>
     </row>
@@ -4099,22 +4102,25 @@
         <v>121</v>
       </c>
       <c r="D95" s="11">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="E95">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="F95">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="G95">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H95" s="4">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="I95">
-        <v>0.69</v>
+        <v>0.78</v>
+      </c>
+      <c r="J95">
+        <v>0.83</v>
       </c>
       <c r="M95" s="6"/>
     </row>
@@ -4129,22 +4135,25 @@
         <v>121</v>
       </c>
       <c r="D96" s="11">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="H96" s="4">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="J96">
+        <v>0.86</v>
       </c>
       <c r="M96" s="6"/>
     </row>
@@ -4159,19 +4168,19 @@
         <v>121</v>
       </c>
       <c r="D97" s="11">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="E97">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="F97">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="G97">
-        <v>0.51</v>
+        <v>0.19</v>
       </c>
       <c r="H97" s="4">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="I97">
         <v>0.56000000000000005</v>
@@ -4189,22 +4198,25 @@
         <v>121</v>
       </c>
       <c r="D98" s="11">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="H98" s="4">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="I98">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="J98">
+        <v>0.92</v>
       </c>
       <c r="M98" s="6"/>
     </row>
@@ -4228,16 +4240,16 @@
         <v>1</v>
       </c>
       <c r="G99">
-        <v>0.62</v>
+        <v>0.33</v>
       </c>
       <c r="H99" s="4">
-        <v>0.54</v>
+        <v>0.38</v>
       </c>
       <c r="I99">
-        <v>0.78</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J99">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="M99" s="6"/>
     </row>
@@ -4252,25 +4264,25 @@
         <v>121</v>
       </c>
       <c r="D100" s="11">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="E100">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100">
-        <v>0.54</v>
+        <v>0.32</v>
       </c>
       <c r="H100" s="4">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="I100">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="J100">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="M100" s="6"/>
     </row>
@@ -4285,22 +4297,25 @@
         <v>121</v>
       </c>
       <c r="D101" s="11">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="E101">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="F101">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="G101">
-        <v>0.19</v>
+        <v>0.44</v>
       </c>
       <c r="H101" s="4">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="I101">
-        <v>0.56000000000000005</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J101">
+        <v>0.81</v>
       </c>
       <c r="M101" s="6"/>
     </row>
@@ -4315,7 +4330,7 @@
         <v>121</v>
       </c>
       <c r="D102" s="11">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -4324,16 +4339,16 @@
         <v>1</v>
       </c>
       <c r="G102">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="H102" s="4">
-        <v>0.79</v>
+        <v>0.46</v>
       </c>
       <c r="I102">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="J102">
-        <v>0.92</v>
+        <v>0.81</v>
       </c>
       <c r="M102" s="6"/>
     </row>
@@ -4348,25 +4363,25 @@
         <v>121</v>
       </c>
       <c r="D103" s="11">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103">
-        <v>0.33</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H103" s="4">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="I103">
-        <v>0.28000000000000003</v>
+        <v>0</v>
       </c>
       <c r="J103">
-        <v>0.92</v>
+        <v>0.69</v>
       </c>
       <c r="M103" s="6"/>
     </row>
@@ -4381,67 +4396,68 @@
         <v>121</v>
       </c>
       <c r="D104" s="11">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="E104">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104">
-        <v>0.32</v>
+        <v>0.47</v>
       </c>
       <c r="H104" s="4">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="I104">
         <v>0.44</v>
       </c>
-      <c r="I104">
-        <v>0.35</v>
+      <c r="J104">
+        <v>0.89</v>
       </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="B105" s="11" t="s">
-        <v>215</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="B105" s="11"/>
       <c r="C105" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D105" s="11">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="E105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="H105" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="I105">
         <v>0</v>
-      </c>
-      <c r="I105">
-        <v>0.28000000000000003</v>
       </c>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C106" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D106" s="11">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="E106">
         <v>1</v>
@@ -4450,25 +4466,25 @@
         <v>1</v>
       </c>
       <c r="G106">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="H106" s="4">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="I106">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="J106">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C107" s="11" t="s">
         <v>121</v>
@@ -4483,74 +4499,82 @@
         <v>0</v>
       </c>
       <c r="G107">
-        <v>0.57999999999999996</v>
+        <v>0.63</v>
       </c>
       <c r="H107" s="4">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="I107">
         <v>0</v>
       </c>
+      <c r="J107">
+        <v>0.81</v>
+      </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C108" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D108" s="11">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="E108">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="G108">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="H108" s="4">
-        <v>0.28999999999999998</v>
+        <v>0.79</v>
       </c>
       <c r="I108">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="J108">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B109" s="11"/>
+        <v>220</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>221</v>
+      </c>
       <c r="C109" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D109" s="11">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="H109" s="4">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>0.32</v>
+      </c>
+      <c r="J109">
+        <v>0.89</v>
       </c>
       <c r="M109" s="6"/>
     </row>
@@ -4571,16 +4595,16 @@
         <v>1</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="G110">
         <v>0.54</v>
       </c>
       <c r="H110" s="4">
-        <v>0.67</v>
+        <v>0.44</v>
       </c>
       <c r="I110">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="M110" s="6"/>
     </row>
@@ -4595,149 +4619,51 @@
         <v>121</v>
       </c>
       <c r="D111" s="11">
-        <v>0.94</v>
+        <v>0.89</v>
       </c>
       <c r="E111">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111">
+        <v>0.51</v>
+      </c>
+      <c r="H111" s="4">
         <v>0</v>
       </c>
-      <c r="G111">
-        <v>0.63</v>
-      </c>
-      <c r="H111" s="4">
-        <v>0.83</v>
-      </c>
       <c r="I111">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
-      <c r="A112" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B112" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="C112" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D112" s="11">
-        <v>0.97</v>
-      </c>
-      <c r="E112">
-        <v>0.92</v>
-      </c>
-      <c r="F112">
-        <v>0.96</v>
-      </c>
-      <c r="G112">
-        <v>0.53</v>
-      </c>
-      <c r="H112" s="4">
-        <v>0.79</v>
-      </c>
-      <c r="I112">
-        <v>0.6</v>
-      </c>
-      <c r="J112">
-        <v>0.92</v>
-      </c>
+      <c r="A112" s="11"/>
+      <c r="B112" s="11"/>
+      <c r="C112" s="11"/>
+      <c r="D112" s="11"/>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
-      <c r="A113" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D113" s="11">
-        <v>0.97</v>
-      </c>
-      <c r="E113">
-        <v>0.96</v>
-      </c>
-      <c r="F113">
-        <v>0.93</v>
-      </c>
-      <c r="G113">
-        <v>0.49</v>
-      </c>
-      <c r="H113" s="4">
-        <v>0.46</v>
-      </c>
-      <c r="I113">
-        <v>0.32</v>
-      </c>
-      <c r="J113">
-        <v>0.89</v>
-      </c>
+      <c r="A113" s="11"/>
+      <c r="B113" s="11"/>
+      <c r="C113" s="11"/>
+      <c r="D113" s="11"/>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
-      <c r="A114" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D114" s="11">
-        <v>0.97</v>
-      </c>
-      <c r="E114">
-        <v>1</v>
-      </c>
-      <c r="F114">
-        <v>0.96</v>
-      </c>
-      <c r="G114">
-        <v>0.54</v>
-      </c>
-      <c r="H114" s="4">
-        <v>0.44</v>
-      </c>
-      <c r="I114">
-        <v>0.43</v>
-      </c>
+      <c r="A114" s="11"/>
+      <c r="B114" s="11"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="11"/>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
-      <c r="A115" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B115" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="C115" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D115" s="11">
-        <v>0.89</v>
-      </c>
-      <c r="E115">
-        <v>1</v>
-      </c>
-      <c r="F115">
-        <v>1</v>
-      </c>
-      <c r="G115">
-        <v>0.51</v>
-      </c>
-      <c r="H115" s="4">
-        <v>0</v>
-      </c>
-      <c r="I115">
-        <v>0.32</v>
-      </c>
+      <c r="A115" s="11"/>
+      <c r="B115" s="11"/>
+      <c r="C115" s="11"/>
+      <c r="D115" s="11"/>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
@@ -5070,10 +4996,8 @@
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
-      <c r="A163" s="11"/>
-      <c r="B163" s="11"/>
-      <c r="C163" s="11"/>
-      <c r="D163" s="11"/>
+      <c r="B163" s="3"/>
+      <c r="D163" s="4"/>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
@@ -5084,10 +5008,8 @@
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
-      <c r="A165" s="11"/>
-      <c r="B165" s="11"/>
-      <c r="C165" s="11"/>
-      <c r="D165" s="11"/>
+      <c r="B165" s="3"/>
+      <c r="D165" s="4"/>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
@@ -5098,8 +5020,10 @@
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
-      <c r="B167" s="3"/>
-      <c r="D167" s="4"/>
+      <c r="A167" s="11"/>
+      <c r="B167" s="11"/>
+      <c r="C167" s="11"/>
+      <c r="D167" s="11"/>
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
@@ -5110,8 +5034,10 @@
       <c r="M168" s="6"/>
     </row>
     <row r="169" spans="1:13">
-      <c r="B169" s="3"/>
-      <c r="D169" s="4"/>
+      <c r="A169" s="11"/>
+      <c r="B169" s="11"/>
+      <c r="C169" s="11"/>
+      <c r="D169" s="11"/>
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13">
@@ -5150,10 +5076,8 @@
       <c r="M174" s="6"/>
     </row>
     <row r="175" spans="1:13">
-      <c r="A175" s="11"/>
-      <c r="B175" s="11"/>
-      <c r="C175" s="11"/>
-      <c r="D175" s="11"/>
+      <c r="B175" s="3"/>
+      <c r="D175" s="4"/>
       <c r="M175" s="6"/>
     </row>
     <row r="176" spans="1:13">
@@ -5178,8 +5102,10 @@
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
-      <c r="B179" s="3"/>
-      <c r="D179" s="4"/>
+      <c r="A179" s="11"/>
+      <c r="B179" s="11"/>
+      <c r="C179" s="11"/>
+      <c r="D179" s="11"/>
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
@@ -5211,10 +5137,8 @@
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
-      <c r="A184" s="11"/>
-      <c r="B184" s="11"/>
-      <c r="C184" s="11"/>
-      <c r="D184" s="11"/>
+      <c r="B184" s="2"/>
+      <c r="D184" s="4"/>
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13">
@@ -5239,8 +5163,10 @@
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
-      <c r="B188" s="2"/>
-      <c r="D188" s="4"/>
+      <c r="A188" s="11"/>
+      <c r="B188" s="11"/>
+      <c r="C188" s="11"/>
+      <c r="D188" s="11"/>
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
@@ -5279,10 +5205,8 @@
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
-      <c r="A194" s="11"/>
-      <c r="B194" s="11"/>
-      <c r="C194" s="11"/>
-      <c r="D194" s="11"/>
+      <c r="B194" s="2"/>
+      <c r="D194" s="4"/>
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
@@ -5307,8 +5231,10 @@
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
-      <c r="B198" s="2"/>
-      <c r="D198" s="4"/>
+      <c r="A198" s="11"/>
+      <c r="B198" s="11"/>
+      <c r="C198" s="11"/>
+      <c r="D198" s="11"/>
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
@@ -5326,10 +5252,8 @@
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
-      <c r="A201" s="11"/>
-      <c r="B201" s="11"/>
-      <c r="C201" s="11"/>
-      <c r="D201" s="11"/>
+      <c r="B201" s="2"/>
+      <c r="D201" s="4"/>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
@@ -5347,15 +5271,15 @@
       <c r="M203" s="6"/>
     </row>
     <row r="204" spans="1:13">
-      <c r="A204" s="11"/>
-      <c r="B204" s="11"/>
-      <c r="C204" s="11"/>
-      <c r="D204" s="11"/>
+      <c r="B204" s="2"/>
+      <c r="D204" s="4"/>
       <c r="M204" s="6"/>
     </row>
     <row r="205" spans="1:13">
-      <c r="B205" s="2"/>
-      <c r="D205" s="4"/>
+      <c r="A205" s="11"/>
+      <c r="B205" s="11"/>
+      <c r="C205" s="11"/>
+      <c r="D205" s="11"/>
       <c r="M205" s="6"/>
     </row>
     <row r="206" spans="1:13">
@@ -5373,8 +5297,10 @@
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
-      <c r="B208" s="2"/>
-      <c r="D208" s="4"/>
+      <c r="A208" s="11"/>
+      <c r="B208" s="11"/>
+      <c r="C208" s="11"/>
+      <c r="D208" s="11"/>
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
@@ -5488,34 +5414,6 @@
       <c r="C224" s="11"/>
       <c r="D224" s="11"/>
       <c r="M224" s="6"/>
-    </row>
-    <row r="225" spans="1:13">
-      <c r="A225" s="11"/>
-      <c r="B225" s="11"/>
-      <c r="C225" s="11"/>
-      <c r="D225" s="11"/>
-      <c r="M225" s="6"/>
-    </row>
-    <row r="226" spans="1:13">
-      <c r="A226" s="11"/>
-      <c r="B226" s="11"/>
-      <c r="C226" s="11"/>
-      <c r="D226" s="11"/>
-      <c r="M226" s="6"/>
-    </row>
-    <row r="227" spans="1:13">
-      <c r="A227" s="11"/>
-      <c r="B227" s="11"/>
-      <c r="C227" s="11"/>
-      <c r="D227" s="11"/>
-      <c r="M227" s="6"/>
-    </row>
-    <row r="228" spans="1:13">
-      <c r="A228" s="11"/>
-      <c r="B228" s="11"/>
-      <c r="C228" s="11"/>
-      <c r="D228" s="11"/>
-      <c r="M228" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A006F1-3C66-AD4A-9672-2E1418FB340B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466E746C-0700-B64E-82C6-9A41AB73966D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="720" windowWidth="23300" windowHeight="17100" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="140" yWindow="1760" windowWidth="17960" windowHeight="17100" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1356,6 +1356,9 @@
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="G2">
         <v>0.32</v>
       </c>
@@ -1386,6 +1389,9 @@
       <c r="E3">
         <v>1</v>
       </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3">
         <v>0.64</v>
       </c>
@@ -1413,6 +1419,9 @@
       <c r="E4">
         <v>1</v>
       </c>
+      <c r="F4">
+        <v>0.95</v>
+      </c>
       <c r="G4">
         <v>0.41</v>
       </c>
@@ -1421,6 +1430,9 @@
       </c>
       <c r="I4">
         <v>0.35</v>
+      </c>
+      <c r="J4">
+        <v>0.91</v>
       </c>
       <c r="M4" s="17"/>
     </row>
@@ -1440,6 +1452,9 @@
       <c r="E5">
         <v>0.83</v>
       </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
       <c r="G5">
         <v>0.14000000000000001</v>
       </c>
@@ -1467,6 +1482,9 @@
       <c r="E6">
         <v>1</v>
       </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
       <c r="G6">
         <v>0.59</v>
       </c>
@@ -1494,6 +1512,9 @@
       <c r="E7">
         <v>0.68</v>
       </c>
+      <c r="F7">
+        <v>0.95</v>
+      </c>
       <c r="G7">
         <v>0.34</v>
       </c>
@@ -1521,6 +1542,9 @@
       <c r="E8">
         <v>1</v>
       </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
       <c r="G8">
         <v>0.3</v>
       </c>
@@ -1548,6 +1572,9 @@
       <c r="E9">
         <v>0.81</v>
       </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
       <c r="G9">
         <v>0.43</v>
       </c>
@@ -1575,6 +1602,9 @@
       <c r="E10">
         <v>1</v>
       </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
       <c r="G10">
         <v>0.48</v>
       </c>
@@ -1583,6 +1613,9 @@
       </c>
       <c r="I10">
         <v>0.43</v>
+      </c>
+      <c r="J10">
+        <v>0.82</v>
       </c>
       <c r="M10" s="6"/>
     </row>
@@ -1602,6 +1635,9 @@
       <c r="E11">
         <v>1</v>
       </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
       <c r="G11">
         <v>0.73</v>
       </c>
@@ -1610,6 +1646,9 @@
       </c>
       <c r="I11">
         <v>0.52</v>
+      </c>
+      <c r="J11">
+        <v>0.91</v>
       </c>
       <c r="M11" s="6"/>
     </row>
@@ -1629,6 +1668,9 @@
       <c r="E12">
         <v>0.87</v>
       </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
       <c r="G12">
         <v>0.45</v>
       </c>
@@ -1637,6 +1679,9 @@
       </c>
       <c r="I12">
         <v>0.74</v>
+      </c>
+      <c r="J12">
+        <v>0.7</v>
       </c>
       <c r="M12" s="6"/>
     </row>
@@ -1656,6 +1701,9 @@
       <c r="E13">
         <v>1</v>
       </c>
+      <c r="F13">
+        <v>0.89</v>
+      </c>
       <c r="G13">
         <v>0.59</v>
       </c>
@@ -1683,6 +1731,9 @@
       <c r="E14">
         <v>1</v>
       </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
       <c r="G14">
         <v>0.27</v>
       </c>
@@ -1710,6 +1761,9 @@
       <c r="E15">
         <v>0.81</v>
       </c>
+      <c r="F15">
+        <v>0.84</v>
+      </c>
       <c r="G15">
         <v>0.2</v>
       </c>
@@ -1737,6 +1791,9 @@
       <c r="E16">
         <v>0.87</v>
       </c>
+      <c r="F16">
+        <v>0.95</v>
+      </c>
       <c r="G16">
         <v>0.36</v>
       </c>
@@ -1764,6 +1821,9 @@
       <c r="E17">
         <v>0.87</v>
       </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
       <c r="G17">
         <v>0.55000000000000004</v>
       </c>
@@ -1791,6 +1851,9 @@
       <c r="E18">
         <v>0.94</v>
       </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
       <c r="G18">
         <v>0.41</v>
       </c>
@@ -1821,6 +1884,9 @@
       <c r="E19">
         <v>0.94</v>
       </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
       <c r="G19">
         <v>0.32</v>
       </c>
@@ -1851,6 +1917,9 @@
       <c r="E20">
         <v>1</v>
       </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
       <c r="G20">
         <v>0.56999999999999995</v>
       </c>
@@ -1859,6 +1928,9 @@
       </c>
       <c r="I20">
         <v>0.46</v>
+      </c>
+      <c r="J20">
+        <v>0.92</v>
       </c>
       <c r="M20" s="6"/>
     </row>
@@ -1878,6 +1950,9 @@
       <c r="E21">
         <v>1</v>
       </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
       <c r="G21">
         <v>0.61</v>
       </c>
@@ -1905,6 +1980,9 @@
       <c r="E22">
         <v>1</v>
       </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
       <c r="G22">
         <v>0.39</v>
       </c>
@@ -1935,6 +2013,9 @@
       <c r="E23">
         <v>1</v>
       </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
       <c r="G23">
         <v>0.23</v>
       </c>
@@ -1965,6 +2046,9 @@
       <c r="E24">
         <v>1</v>
       </c>
+      <c r="F24">
+        <v>0.89</v>
+      </c>
       <c r="G24">
         <v>0.45</v>
       </c>
@@ -1992,6 +2076,9 @@
       <c r="E25">
         <v>0.81</v>
       </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
       <c r="G25">
         <v>0.41</v>
       </c>
@@ -2019,6 +2106,9 @@
       <c r="E26">
         <v>1</v>
       </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
       <c r="G26">
         <v>0.3</v>
       </c>
@@ -2046,6 +2136,9 @@
       <c r="E27">
         <v>0.74</v>
       </c>
+      <c r="F27">
+        <v>0.89</v>
+      </c>
       <c r="G27">
         <v>0.3</v>
       </c>
@@ -2054,6 +2147,9 @@
       </c>
       <c r="I27">
         <v>0.5</v>
+      </c>
+      <c r="J27">
+        <v>0.62</v>
       </c>
       <c r="M27" s="6"/>
     </row>
@@ -2073,6 +2169,9 @@
       <c r="E28">
         <v>0.87</v>
       </c>
+      <c r="F28">
+        <v>0.95</v>
+      </c>
       <c r="G28">
         <v>0.56999999999999995</v>
       </c>
@@ -2081,6 +2180,9 @@
       </c>
       <c r="I28">
         <v>0.39</v>
+      </c>
+      <c r="J28">
+        <v>0.94</v>
       </c>
       <c r="M28" s="6"/>
     </row>
@@ -2100,6 +2202,9 @@
       <c r="E29">
         <v>0.94</v>
       </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
       <c r="G29">
         <v>0.55000000000000004</v>
       </c>
@@ -2130,6 +2235,9 @@
       <c r="E30">
         <v>1</v>
       </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
       <c r="G30">
         <v>0.5</v>
       </c>
@@ -2160,6 +2268,9 @@
       <c r="E31">
         <v>1</v>
       </c>
+      <c r="F31">
+        <v>0.84</v>
+      </c>
       <c r="G31">
         <v>0.32</v>
       </c>
@@ -2187,6 +2298,9 @@
       <c r="E32">
         <v>1</v>
       </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
       <c r="G32">
         <v>0.36</v>
       </c>
@@ -2195,6 +2309,9 @@
       </c>
       <c r="I32">
         <v>0.41</v>
+      </c>
+      <c r="J32">
+        <v>0.64</v>
       </c>
       <c r="M32" s="6"/>
     </row>
@@ -2214,6 +2331,9 @@
       <c r="E33">
         <v>1</v>
       </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
       <c r="G33">
         <v>0.23</v>
       </c>
@@ -2241,6 +2361,9 @@
       <c r="E34">
         <v>0.94</v>
       </c>
+      <c r="F34">
+        <v>0.95</v>
+      </c>
       <c r="G34">
         <v>0.52</v>
       </c>
@@ -2268,6 +2391,9 @@
       <c r="E35">
         <v>1</v>
       </c>
+      <c r="F35">
+        <v>0.89</v>
+      </c>
       <c r="G35">
         <v>0</v>
       </c>
@@ -2295,6 +2421,9 @@
       <c r="E36">
         <v>1</v>
       </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
       <c r="G36">
         <v>0.39</v>
       </c>
@@ -2325,6 +2454,9 @@
       <c r="E37">
         <v>1</v>
       </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
       <c r="G37">
         <v>0.45</v>
       </c>
@@ -2352,6 +2484,9 @@
       <c r="E38">
         <v>0.83</v>
       </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
       <c r="G38">
         <v>0.34</v>
       </c>
@@ -2360,6 +2495,9 @@
       </c>
       <c r="I38">
         <v>0.5</v>
+      </c>
+      <c r="J38">
+        <v>0.65</v>
       </c>
       <c r="M38" s="6"/>
     </row>
@@ -2379,6 +2517,9 @@
       <c r="E39">
         <v>1</v>
       </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
       <c r="G39">
         <v>0.77</v>
       </c>
@@ -2406,6 +2547,9 @@
       <c r="E40">
         <v>1</v>
       </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
       <c r="G40">
         <v>0.55000000000000004</v>
       </c>
@@ -2433,6 +2577,9 @@
       <c r="E41">
         <v>0.87</v>
       </c>
+      <c r="F41">
+        <v>0.84</v>
+      </c>
       <c r="G41">
         <v>0.59</v>
       </c>
@@ -2463,6 +2610,9 @@
       <c r="E42">
         <v>1</v>
       </c>
+      <c r="F42">
+        <v>0.95</v>
+      </c>
       <c r="G42">
         <v>0.52</v>
       </c>
@@ -2490,6 +2640,9 @@
       <c r="E43">
         <v>0.94</v>
       </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
       <c r="G43">
         <v>0.56999999999999995</v>
       </c>
@@ -2520,6 +2673,9 @@
       <c r="E44">
         <v>1</v>
       </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
       <c r="G44">
         <v>0.36</v>
       </c>
@@ -2547,6 +2703,9 @@
       <c r="E45">
         <v>1</v>
       </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
       <c r="G45">
         <v>0.68</v>
       </c>
@@ -2577,6 +2736,9 @@
       <c r="E46">
         <v>0</v>
       </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
       <c r="G46">
         <v>0.5</v>
       </c>
@@ -2604,6 +2766,9 @@
       <c r="E47">
         <v>1</v>
       </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
       <c r="G47">
         <v>0.52</v>
       </c>
@@ -2634,6 +2799,9 @@
       <c r="E48">
         <v>1</v>
       </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
       <c r="G48">
         <v>0.52</v>
       </c>
@@ -2661,6 +2829,9 @@
       <c r="E49">
         <v>0.74</v>
       </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
       <c r="G49">
         <v>0.39</v>
       </c>
@@ -2669,6 +2840,9 @@
       </c>
       <c r="I49">
         <v>0.43</v>
+      </c>
+      <c r="J49">
+        <v>0.89</v>
       </c>
       <c r="M49" s="6"/>
     </row>
@@ -2688,6 +2862,9 @@
       <c r="E50">
         <v>1</v>
       </c>
+      <c r="F50">
+        <v>0.95</v>
+      </c>
       <c r="G50">
         <v>0.23</v>
       </c>
@@ -2715,6 +2892,9 @@
       <c r="E51">
         <v>1</v>
       </c>
+      <c r="F51">
+        <v>0.95</v>
+      </c>
       <c r="G51">
         <v>0.66</v>
       </c>
@@ -2723,6 +2903,9 @@
       </c>
       <c r="I51">
         <v>0.76</v>
+      </c>
+      <c r="J51">
+        <v>0.94</v>
       </c>
       <c r="M51" s="6"/>
     </row>
@@ -2742,6 +2925,9 @@
       <c r="E52">
         <v>0.83</v>
       </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
       <c r="G52">
         <v>0</v>
       </c>
@@ -2769,6 +2955,9 @@
       <c r="E53">
         <v>0.81</v>
       </c>
+      <c r="F53">
+        <v>0.95</v>
+      </c>
       <c r="G53">
         <v>0.45</v>
       </c>
@@ -2777,6 +2966,9 @@
       </c>
       <c r="I53">
         <v>0.52</v>
+      </c>
+      <c r="J53">
+        <v>0.91</v>
       </c>
       <c r="M53" s="6"/>
     </row>
@@ -2796,6 +2988,9 @@
       <c r="E54">
         <v>0.87</v>
       </c>
+      <c r="F54">
+        <v>0.79</v>
+      </c>
       <c r="G54">
         <v>0.34</v>
       </c>
@@ -2826,6 +3021,9 @@
       <c r="E55">
         <v>1</v>
       </c>
+      <c r="F55">
+        <v>0.95</v>
+      </c>
       <c r="G55">
         <v>0.5</v>
       </c>
@@ -2856,6 +3054,9 @@
       <c r="E56">
         <v>1</v>
       </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
       <c r="G56">
         <v>0</v>
       </c>
@@ -2883,6 +3084,9 @@
       <c r="E57">
         <v>0.96</v>
       </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
       <c r="G57">
         <v>0.45</v>
       </c>
@@ -2891,6 +3095,9 @@
       </c>
       <c r="I57">
         <v>0.76</v>
+      </c>
+      <c r="J57">
+        <v>0.86</v>
       </c>
       <c r="M57" s="6"/>
     </row>
@@ -2988,6 +3195,9 @@
       <c r="I60">
         <v>0.71</v>
       </c>
+      <c r="J60">
+        <v>0.72</v>
+      </c>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
@@ -3084,6 +3294,9 @@
       <c r="I63">
         <v>0.69</v>
       </c>
+      <c r="J63">
+        <v>0.81</v>
+      </c>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
@@ -3147,6 +3360,9 @@
       <c r="I65">
         <v>0.56000000000000005</v>
       </c>
+      <c r="J65">
+        <v>0.67</v>
+      </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
@@ -3636,6 +3852,9 @@
       <c r="I80">
         <v>0.38</v>
       </c>
+      <c r="J80">
+        <v>0.86</v>
+      </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
@@ -3957,6 +4176,9 @@
       <c r="I90">
         <v>0.63</v>
       </c>
+      <c r="J90">
+        <v>0.81</v>
+      </c>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
@@ -4635,6 +4857,9 @@
       </c>
       <c r="I111">
         <v>0.32</v>
+      </c>
+      <c r="J111">
+        <v>0.79</v>
       </c>
       <c r="M111" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466E746C-0700-B64E-82C6-9A41AB73966D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8070F7A5-BDBE-564E-8386-5B30600ADB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="1760" windowWidth="17960" windowHeight="17100" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="140" yWindow="1760" windowWidth="30820" windowHeight="17100" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1464,6 +1464,9 @@
       <c r="I5">
         <v>0.17</v>
       </c>
+      <c r="J5">
+        <v>0.68</v>
+      </c>
       <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:13">
@@ -1524,6 +1527,9 @@
       <c r="I7">
         <v>0.3</v>
       </c>
+      <c r="J7">
+        <v>0.88</v>
+      </c>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
@@ -2058,6 +2064,9 @@
       <c r="I24">
         <v>0.56999999999999995</v>
       </c>
+      <c r="J24">
+        <v>0.91</v>
+      </c>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
@@ -2466,6 +2475,9 @@
       <c r="I37">
         <v>0.5</v>
       </c>
+      <c r="J37">
+        <v>0.76</v>
+      </c>
       <c r="M37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20">
@@ -2529,6 +2541,9 @@
       <c r="I39">
         <v>0.7</v>
       </c>
+      <c r="J39">
+        <v>0.92</v>
+      </c>
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13">
@@ -2559,6 +2574,9 @@
       <c r="I40">
         <v>0.56999999999999995</v>
       </c>
+      <c r="J40">
+        <v>0.86</v>
+      </c>
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13">
@@ -2937,6 +2955,9 @@
       <c r="I52">
         <v>0.67</v>
       </c>
+      <c r="J52">
+        <v>0.88</v>
+      </c>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
@@ -3065,6 +3086,9 @@
       </c>
       <c r="I56">
         <v>0.54</v>
+      </c>
+      <c r="J56">
+        <v>0.76</v>
       </c>
       <c r="M56" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8070F7A5-BDBE-564E-8386-5B30600ADB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522A6DD8-3D09-0D46-9351-9415E589A444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="1760" windowWidth="30820" windowHeight="17100" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1560,6 +1560,9 @@
       <c r="I8">
         <v>0.3</v>
       </c>
+      <c r="J8">
+        <v>0.65</v>
+      </c>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
@@ -1749,6 +1752,9 @@
       <c r="I14">
         <v>0.5</v>
       </c>
+      <c r="J14">
+        <v>0.88</v>
+      </c>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13">
@@ -1779,6 +1785,9 @@
       <c r="I15">
         <v>0.63</v>
       </c>
+      <c r="J15">
+        <v>0.92</v>
+      </c>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13">
@@ -1809,6 +1818,9 @@
       <c r="I16">
         <v>0.3</v>
       </c>
+      <c r="J16">
+        <v>0.62</v>
+      </c>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
@@ -2097,6 +2109,9 @@
       <c r="I25">
         <v>0.5</v>
       </c>
+      <c r="J25">
+        <v>0.74</v>
+      </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
@@ -2352,6 +2367,9 @@
       <c r="I33">
         <v>0.39</v>
       </c>
+      <c r="J33">
+        <v>0.64</v>
+      </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
@@ -2640,6 +2658,9 @@
       <c r="I42">
         <v>0.5</v>
       </c>
+      <c r="J42">
+        <v>0.91</v>
+      </c>
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
@@ -2703,6 +2724,9 @@
       <c r="I44">
         <v>0.48</v>
       </c>
+      <c r="J44">
+        <v>0.92</v>
+      </c>
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
@@ -2765,6 +2789,9 @@
       </c>
       <c r="I46">
         <v>0.43</v>
+      </c>
+      <c r="J46">
+        <v>0.59</v>
       </c>
       <c r="M46" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522A6DD8-3D09-0D46-9351-9415E589A444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF466F87-83C4-F54F-A94A-3DC693C78AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="140" yWindow="1760" windowWidth="30820" windowHeight="17100" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1401,6 +1401,9 @@
       <c r="I3">
         <v>0.7</v>
       </c>
+      <c r="J3">
+        <v>0.94</v>
+      </c>
       <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:13">
@@ -1497,6 +1500,9 @@
       <c r="I6">
         <v>0.61</v>
       </c>
+      <c r="J6">
+        <v>0.98</v>
+      </c>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13">
@@ -1593,6 +1599,9 @@
       <c r="I9">
         <v>0.39</v>
       </c>
+      <c r="J9">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
@@ -1722,6 +1731,9 @@
       <c r="I13">
         <v>0.56999999999999995</v>
       </c>
+      <c r="J13">
+        <v>0.97</v>
+      </c>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13">
@@ -1851,6 +1863,9 @@
       <c r="I17">
         <v>0.59</v>
       </c>
+      <c r="J17">
+        <v>0.89</v>
+      </c>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13">
@@ -1980,6 +1995,9 @@
       <c r="I21">
         <v>0.52</v>
       </c>
+      <c r="J21">
+        <v>0.97</v>
+      </c>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
@@ -2142,6 +2160,9 @@
       <c r="I26">
         <v>0.5</v>
       </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
@@ -2304,6 +2325,9 @@
       <c r="I31">
         <v>0.52</v>
       </c>
+      <c r="J31">
+        <v>0.88</v>
+      </c>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
@@ -2400,6 +2424,9 @@
       <c r="I34">
         <v>0.56000000000000005</v>
       </c>
+      <c r="J34">
+        <v>0.89</v>
+      </c>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="1:13">
@@ -2430,6 +2457,9 @@
       <c r="I35">
         <v>0.52</v>
       </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
@@ -2856,6 +2886,9 @@
       <c r="I48">
         <v>0.59</v>
       </c>
+      <c r="J48">
+        <v>0.88</v>
+      </c>
       <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13">
@@ -2919,6 +2952,9 @@
       <c r="I50">
         <v>0.39</v>
       </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
@@ -3477,6 +3513,9 @@
       <c r="I67">
         <v>0.34</v>
       </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
@@ -3969,6 +4008,9 @@
       <c r="I82">
         <v>0.43</v>
       </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
@@ -3999,6 +4041,9 @@
       <c r="I83">
         <v>0.31</v>
       </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
@@ -4458,6 +4503,9 @@
       <c r="I97">
         <v>0.56000000000000005</v>
       </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
@@ -4717,6 +4765,9 @@
       <c r="I105">
         <v>0</v>
       </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
@@ -4878,6 +4929,9 @@
       </c>
       <c r="I110">
         <v>0.43</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
       </c>
       <c r="M110" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF466F87-83C4-F54F-A94A-3DC693C78AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC04E0D-036B-CA47-B361-F0A9E5AA5DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="1760" windowWidth="30820" windowHeight="17100" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1371,6 +1371,9 @@
       <c r="J2">
         <v>0.28999999999999998</v>
       </c>
+      <c r="K2">
+        <v>0.88</v>
+      </c>
       <c r="M2" s="17"/>
     </row>
     <row r="3" spans="1:13">
@@ -1404,6 +1407,9 @@
       <c r="J3">
         <v>0.94</v>
       </c>
+      <c r="K3">
+        <v>0.88</v>
+      </c>
       <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:13">
@@ -1437,6 +1443,9 @@
       <c r="J4">
         <v>0.91</v>
       </c>
+      <c r="K4">
+        <v>0.77</v>
+      </c>
       <c r="M4" s="17"/>
     </row>
     <row r="5" spans="1:13">
@@ -1503,6 +1512,9 @@
       <c r="J6">
         <v>0.98</v>
       </c>
+      <c r="K6">
+        <v>0.96</v>
+      </c>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13">
@@ -1569,6 +1581,9 @@
       <c r="J8">
         <v>0.65</v>
       </c>
+      <c r="K8">
+        <v>0.88</v>
+      </c>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
@@ -1602,6 +1617,9 @@
       <c r="J9">
         <v>0.56000000000000005</v>
       </c>
+      <c r="K9">
+        <v>0.73</v>
+      </c>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
@@ -1635,6 +1653,9 @@
       <c r="J10">
         <v>0.82</v>
       </c>
+      <c r="K10">
+        <v>0.94</v>
+      </c>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13">
@@ -1668,6 +1689,9 @@
       <c r="J11">
         <v>0.91</v>
       </c>
+      <c r="K11">
+        <v>0.94</v>
+      </c>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13">
@@ -1701,6 +1725,9 @@
       <c r="J12">
         <v>0.7</v>
       </c>
+      <c r="K12">
+        <v>0.88</v>
+      </c>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13">
@@ -1734,6 +1761,9 @@
       <c r="J13">
         <v>0.97</v>
       </c>
+      <c r="K13">
+        <v>0.81</v>
+      </c>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13">
@@ -1767,6 +1797,9 @@
       <c r="J14">
         <v>0.88</v>
       </c>
+      <c r="K14">
+        <v>0.92</v>
+      </c>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13">
@@ -1799,6 +1832,9 @@
       </c>
       <c r="J15">
         <v>0.92</v>
+      </c>
+      <c r="K15">
+        <v>0.85</v>
       </c>
       <c r="M15" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC04E0D-036B-CA47-B361-F0A9E5AA5DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA248089-6787-CC49-9300-DFFB6E019E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1869,6 +1869,9 @@
       <c r="J16">
         <v>0.62</v>
       </c>
+      <c r="K16">
+        <v>0.92</v>
+      </c>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
@@ -1902,6 +1905,9 @@
       <c r="J17">
         <v>0.89</v>
       </c>
+      <c r="K17">
+        <v>0.67</v>
+      </c>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13">
@@ -1968,6 +1974,9 @@
       <c r="J19">
         <v>0.94</v>
       </c>
+      <c r="K19">
+        <v>0.83</v>
+      </c>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
@@ -2001,6 +2010,9 @@
       <c r="J20">
         <v>0.92</v>
       </c>
+      <c r="K20">
+        <v>0.94</v>
+      </c>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
@@ -2034,6 +2046,9 @@
       <c r="J21">
         <v>0.97</v>
       </c>
+      <c r="K21">
+        <v>0.85</v>
+      </c>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
@@ -2067,6 +2082,9 @@
       <c r="J22">
         <v>0.65</v>
       </c>
+      <c r="K22">
+        <v>0.85</v>
+      </c>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
@@ -2100,6 +2118,9 @@
       <c r="J23">
         <v>0.85</v>
       </c>
+      <c r="K23">
+        <v>0.67</v>
+      </c>
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
@@ -2133,6 +2154,9 @@
       <c r="J24">
         <v>0.91</v>
       </c>
+      <c r="K24">
+        <v>0.88</v>
+      </c>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
@@ -2166,6 +2190,9 @@
       <c r="J25">
         <v>0.74</v>
       </c>
+      <c r="K25">
+        <v>0.69</v>
+      </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
@@ -2199,6 +2226,9 @@
       <c r="J26">
         <v>0</v>
       </c>
+      <c r="K26">
+        <v>0.92</v>
+      </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
@@ -2232,6 +2262,9 @@
       <c r="J27">
         <v>0.62</v>
       </c>
+      <c r="K27">
+        <v>0.6</v>
+      </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
@@ -2264,6 +2297,9 @@
       </c>
       <c r="J28">
         <v>0.94</v>
+      </c>
+      <c r="K28">
+        <v>0.48</v>
       </c>
       <c r="M28" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA248089-6787-CC49-9300-DFFB6E019E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B68F8F1-6977-4546-A69C-7DF0CEEC57C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2367,6 +2367,9 @@
       <c r="J30">
         <v>0.62</v>
       </c>
+      <c r="K30">
+        <v>0.9</v>
+      </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
@@ -2433,6 +2436,9 @@
       <c r="J32">
         <v>0.64</v>
       </c>
+      <c r="K32">
+        <v>0.81</v>
+      </c>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13">
@@ -2598,6 +2604,9 @@
       <c r="J37">
         <v>0.76</v>
       </c>
+      <c r="K37">
+        <v>0.92</v>
+      </c>
       <c r="M37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20">
@@ -2664,6 +2673,9 @@
       <c r="J39">
         <v>0.92</v>
       </c>
+      <c r="K39">
+        <v>0.92</v>
+      </c>
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13">
@@ -2697,6 +2709,9 @@
       <c r="J40">
         <v>0.86</v>
       </c>
+      <c r="K40">
+        <v>0.92</v>
+      </c>
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13">
@@ -2796,6 +2811,9 @@
       <c r="J43">
         <v>0.94</v>
       </c>
+      <c r="K43">
+        <v>0.83</v>
+      </c>
       <c r="M43" s="6"/>
     </row>
     <row r="44" spans="1:13">
@@ -2829,6 +2847,9 @@
       <c r="J44">
         <v>0.92</v>
       </c>
+      <c r="K44">
+        <v>0.92</v>
+      </c>
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
@@ -2928,6 +2949,9 @@
       <c r="J47">
         <v>0.86</v>
       </c>
+      <c r="K47">
+        <v>0.92</v>
+      </c>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
@@ -2994,6 +3018,9 @@
       <c r="J49">
         <v>0.89</v>
       </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
@@ -3060,6 +3087,9 @@
       <c r="J51">
         <v>0.94</v>
       </c>
+      <c r="K51">
+        <v>0.92</v>
+      </c>
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
@@ -3093,6 +3123,9 @@
       <c r="J52">
         <v>0.88</v>
       </c>
+      <c r="K52">
+        <v>0.94</v>
+      </c>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
@@ -3192,6 +3225,9 @@
       <c r="J55">
         <v>0.77</v>
       </c>
+      <c r="K55">
+        <v>0.9</v>
+      </c>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
@@ -3224,6 +3260,9 @@
       </c>
       <c r="J56">
         <v>0.76</v>
+      </c>
+      <c r="K56">
+        <v>0.65</v>
       </c>
       <c r="M56" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B68F8F1-6977-4546-A69C-7DF0CEEC57C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C72CDB0-3612-4F41-8EE9-F8D42D914DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1479,6 +1479,9 @@
       <c r="J5">
         <v>0.68</v>
       </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
       <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:13">
@@ -1548,6 +1551,9 @@
       <c r="J7">
         <v>0.88</v>
       </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
@@ -1941,6 +1947,9 @@
       <c r="J18">
         <v>0.26</v>
       </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
@@ -2334,6 +2343,9 @@
       <c r="J29">
         <v>0.88</v>
       </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -2403,6 +2415,9 @@
       <c r="J31">
         <v>0.88</v>
       </c>
+      <c r="K31">
+        <v>0.88</v>
+      </c>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
@@ -2472,6 +2487,9 @@
       <c r="J33">
         <v>0.64</v>
       </c>
+      <c r="K33">
+        <v>0.79</v>
+      </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
@@ -2505,6 +2523,9 @@
       <c r="J34">
         <v>0.89</v>
       </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="1:13">
@@ -2538,6 +2559,9 @@
       <c r="J35">
         <v>0</v>
       </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
@@ -2571,6 +2595,9 @@
       <c r="J36">
         <v>0.83</v>
       </c>
+      <c r="K36">
+        <v>0.92</v>
+      </c>
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="1:13">
@@ -2640,6 +2667,9 @@
       <c r="J38">
         <v>0.65</v>
       </c>
+      <c r="K38">
+        <v>0.77</v>
+      </c>
       <c r="M38" s="6"/>
     </row>
     <row r="39" spans="1:13">
@@ -2745,6 +2775,9 @@
       <c r="J41">
         <v>0.86</v>
       </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
@@ -2778,6 +2811,9 @@
       <c r="J42">
         <v>0.91</v>
       </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
@@ -2883,6 +2919,9 @@
       <c r="J45">
         <v>0.77</v>
       </c>
+      <c r="K45">
+        <v>0.92</v>
+      </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
@@ -2916,6 +2955,9 @@
       <c r="J46">
         <v>0.59</v>
       </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
@@ -2985,6 +3027,9 @@
       <c r="J48">
         <v>0.88</v>
       </c>
+      <c r="K48">
+        <v>0.94</v>
+      </c>
       <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13">
@@ -3054,6 +3099,9 @@
       <c r="J50">
         <v>0</v>
       </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
@@ -3159,6 +3207,9 @@
       <c r="J53">
         <v>0.91</v>
       </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
@@ -3191,6 +3242,9 @@
       </c>
       <c r="J54">
         <v>0.45</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
       </c>
       <c r="M54" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C72CDB0-3612-4F41-8EE9-F8D42D914DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859E48FF-25A2-FD44-90E8-B265961DE1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1446,6 +1446,9 @@
       <c r="K4">
         <v>0.77</v>
       </c>
+      <c r="L4">
+        <v>0.68</v>
+      </c>
       <c r="M4" s="17"/>
     </row>
     <row r="5" spans="1:13">
@@ -1662,6 +1665,9 @@
       <c r="K10">
         <v>0.94</v>
       </c>
+      <c r="L10">
+        <v>0.68</v>
+      </c>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13">
@@ -1698,6 +1704,9 @@
       <c r="K11">
         <v>0.94</v>
       </c>
+      <c r="L11">
+        <v>0.68</v>
+      </c>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13">
@@ -1986,6 +1995,9 @@
       <c r="K19">
         <v>0.83</v>
       </c>
+      <c r="L19">
+        <v>0.68</v>
+      </c>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
@@ -2022,6 +2034,9 @@
       <c r="K20">
         <v>0.94</v>
       </c>
+      <c r="L20">
+        <v>0.62</v>
+      </c>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
@@ -2094,6 +2109,9 @@
       <c r="K22">
         <v>0.85</v>
       </c>
+      <c r="L22">
+        <v>0.62</v>
+      </c>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
@@ -2238,6 +2256,9 @@
       <c r="K26">
         <v>0.92</v>
       </c>
+      <c r="L26">
+        <v>0.68</v>
+      </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
@@ -2274,6 +2295,9 @@
       <c r="K27">
         <v>0.6</v>
       </c>
+      <c r="L27">
+        <v>0.68</v>
+      </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
@@ -2454,6 +2478,9 @@
       <c r="K32">
         <v>0.81</v>
       </c>
+      <c r="L32">
+        <v>0.62</v>
+      </c>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13">
@@ -2922,6 +2949,9 @@
       <c r="K45">
         <v>0.92</v>
       </c>
+      <c r="L45">
+        <v>0.59</v>
+      </c>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
@@ -3137,6 +3167,9 @@
       </c>
       <c r="K51">
         <v>0.92</v>
+      </c>
+      <c r="L51">
+        <v>0.68</v>
       </c>
       <c r="M51" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859E48FF-25A2-FD44-90E8-B265961DE1A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03E78E9-7E65-234F-BEFC-4F6EC19065E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1374,6 +1374,9 @@
       <c r="K2">
         <v>0.88</v>
       </c>
+      <c r="L2">
+        <v>0.88</v>
+      </c>
       <c r="M2" s="17"/>
     </row>
     <row r="3" spans="1:13">
@@ -1485,6 +1488,9 @@
       <c r="K5">
         <v>0</v>
       </c>
+      <c r="L5">
+        <v>0.5</v>
+      </c>
       <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:13">
@@ -1557,6 +1563,9 @@
       <c r="K7">
         <v>0</v>
       </c>
+      <c r="L7">
+        <v>0.68</v>
+      </c>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
@@ -1593,6 +1602,9 @@
       <c r="K8">
         <v>0.88</v>
       </c>
+      <c r="L8">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
@@ -1959,6 +1971,9 @@
       <c r="K18">
         <v>0</v>
       </c>
+      <c r="L18">
+        <v>0.59</v>
+      </c>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
@@ -2184,6 +2199,9 @@
       <c r="K24">
         <v>0.88</v>
       </c>
+      <c r="L24">
+        <v>0.85</v>
+      </c>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
@@ -2220,6 +2238,9 @@
       <c r="K25">
         <v>0.69</v>
       </c>
+      <c r="L25">
+        <v>0.74</v>
+      </c>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
@@ -2370,6 +2391,9 @@
       <c r="K29">
         <v>0</v>
       </c>
+      <c r="L29">
+        <v>0.62</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -2406,6 +2430,9 @@
       <c r="K30">
         <v>0.9</v>
       </c>
+      <c r="L30">
+        <v>0.68</v>
+      </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
@@ -2661,6 +2688,9 @@
       <c r="K37">
         <v>0.92</v>
       </c>
+      <c r="L37">
+        <v>0.62</v>
+      </c>
       <c r="M37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20">
@@ -2733,6 +2763,9 @@
       <c r="K39">
         <v>0.92</v>
       </c>
+      <c r="L39">
+        <v>0.68</v>
+      </c>
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13">
@@ -2769,6 +2802,9 @@
       <c r="K40">
         <v>0.92</v>
       </c>
+      <c r="L40">
+        <v>0.62</v>
+      </c>
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13">
@@ -2841,6 +2877,9 @@
       <c r="K42">
         <v>0</v>
       </c>
+      <c r="L42">
+        <v>0.53</v>
+      </c>
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
@@ -2988,6 +3027,9 @@
       <c r="K46">
         <v>0</v>
       </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
@@ -3024,6 +3066,9 @@
       <c r="K47">
         <v>0.92</v>
       </c>
+      <c r="L47">
+        <v>0.68</v>
+      </c>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
@@ -3096,6 +3141,9 @@
       <c r="K49">
         <v>1</v>
       </c>
+      <c r="L49">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
@@ -3207,6 +3255,9 @@
       <c r="K52">
         <v>0.94</v>
       </c>
+      <c r="L52">
+        <v>0.5</v>
+      </c>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
@@ -3314,6 +3365,9 @@
       </c>
       <c r="K55">
         <v>0.9</v>
+      </c>
+      <c r="L55">
+        <v>0.68</v>
       </c>
       <c r="M55" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03E78E9-7E65-234F-BEFC-4F6EC19065E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CD54B5-DB03-0A42-87A8-406A41CE9E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1413,6 +1413,9 @@
       <c r="K3">
         <v>0.88</v>
       </c>
+      <c r="L3">
+        <v>0.62</v>
+      </c>
       <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:13">
@@ -1863,6 +1866,9 @@
       <c r="K15">
         <v>0.85</v>
       </c>
+      <c r="L15">
+        <v>0.65</v>
+      </c>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13">
@@ -1899,6 +1905,9 @@
       <c r="K16">
         <v>0.92</v>
       </c>
+      <c r="L16">
+        <v>0.91</v>
+      </c>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
@@ -2355,6 +2364,9 @@
       <c r="K28">
         <v>0.48</v>
       </c>
+      <c r="L28">
+        <v>0.68</v>
+      </c>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
@@ -2544,6 +2556,9 @@
       <c r="K33">
         <v>0.79</v>
       </c>
+      <c r="L33">
+        <v>0.62</v>
+      </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
@@ -2616,6 +2631,9 @@
       <c r="K35">
         <v>0</v>
       </c>
+      <c r="L35">
+        <v>0.74</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
@@ -2652,6 +2670,9 @@
       <c r="K36">
         <v>0.92</v>
       </c>
+      <c r="L36">
+        <v>0.76</v>
+      </c>
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="1:13">
@@ -2952,6 +2973,9 @@
       <c r="K44">
         <v>0.92</v>
       </c>
+      <c r="L44">
+        <v>0.65</v>
+      </c>
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
@@ -3329,6 +3353,9 @@
       </c>
       <c r="K54">
         <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0.5</v>
       </c>
       <c r="M54" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CD54B5-DB03-0A42-87A8-406A41CE9E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE3CABD-6EBA-9E47-9734-21385A36AD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1377,7 +1377,10 @@
       <c r="L2">
         <v>0.88</v>
       </c>
-      <c r="M2" s="17"/>
+      <c r="M2" s="17">
+        <f t="shared" ref="M2:M56" si="0">(((LARGE(D2:F2,1)+LARGE(D2:F2,2))*0.2/2+(LARGE(G2:I2,1)+LARGE(G2:I2,2))*0.5/2+(LARGE(J2:L2,1)+LARGE(J2:L2,2))*0.3/2))</f>
+        <v>0.70450000000000002</v>
+      </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="18" t="s">
@@ -1416,7 +1419,10 @@
       <c r="L3">
         <v>0.62</v>
       </c>
-      <c r="M3" s="17"/>
+      <c r="M3" s="17">
+        <f t="shared" si="0"/>
+        <v>0.80799999999999983</v>
+      </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="15" t="s">
@@ -1455,7 +1461,10 @@
       <c r="L4">
         <v>0.68</v>
       </c>
-      <c r="M4" s="17"/>
+      <c r="M4" s="17">
+        <f t="shared" si="0"/>
+        <v>0.70700000000000007</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="16" t="s">
@@ -1494,7 +1503,10 @@
       <c r="L5">
         <v>0.5</v>
       </c>
-      <c r="M5" s="17"/>
+      <c r="M5" s="17">
+        <f t="shared" si="0"/>
+        <v>0.49450000000000005</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="8" t="s">
@@ -1530,7 +1542,13 @@
       <c r="K6">
         <v>0.96</v>
       </c>
-      <c r="M6" s="6"/>
+      <c r="L6">
+        <v>0.44</v>
+      </c>
+      <c r="M6" s="17">
+        <f t="shared" si="0"/>
+        <v>0.84349999999999992</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="7" t="s">
@@ -1569,7 +1587,10 @@
       <c r="L7">
         <v>0.68</v>
       </c>
-      <c r="M7" s="6"/>
+      <c r="M7" s="17">
+        <f t="shared" si="0"/>
+        <v>0.67249999999999999</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="8" t="s">
@@ -1608,7 +1629,10 @@
       <c r="L8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="M8" s="6"/>
+      <c r="M8" s="17">
+        <f t="shared" si="0"/>
+        <v>0.63050000000000006</v>
+      </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="8" t="s">
@@ -1644,7 +1668,10 @@
       <c r="K9">
         <v>0.73</v>
       </c>
-      <c r="M9" s="6"/>
+      <c r="M9" s="17">
+        <f t="shared" si="0"/>
+        <v>0.65200000000000002</v>
+      </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="7" t="s">
@@ -1683,7 +1710,10 @@
       <c r="L10">
         <v>0.68</v>
       </c>
-      <c r="M10" s="6"/>
+      <c r="M10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.73649999999999993</v>
+      </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="9" t="s">
@@ -1722,7 +1752,10 @@
       <c r="L11">
         <v>0.68</v>
       </c>
-      <c r="M11" s="6"/>
+      <c r="M11" s="17">
+        <f t="shared" si="0"/>
+        <v>0.83000000000000007</v>
+      </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="8" t="s">
@@ -1758,7 +1791,13 @@
       <c r="K12">
         <v>0.88</v>
       </c>
-      <c r="M12" s="6"/>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="17">
+        <f t="shared" si="0"/>
+        <v>0.83900000000000008</v>
+      </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="7" t="s">
@@ -1794,7 +1833,13 @@
       <c r="K13">
         <v>0.81</v>
       </c>
-      <c r="M13" s="6"/>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="17">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="8" t="s">
@@ -1830,7 +1875,13 @@
       <c r="K14">
         <v>0.92</v>
       </c>
-      <c r="M14" s="6"/>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" s="17">
+        <f t="shared" si="0"/>
+        <v>0.73850000000000005</v>
+      </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="7" t="s">
@@ -1869,7 +1920,10 @@
       <c r="L15">
         <v>0.65</v>
       </c>
-      <c r="M15" s="6"/>
+      <c r="M15" s="17">
+        <f t="shared" si="0"/>
+        <v>0.75350000000000006</v>
+      </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="8" t="s">
@@ -1908,7 +1962,10 @@
       <c r="L16">
         <v>0.91</v>
       </c>
-      <c r="M16" s="6"/>
+      <c r="M16" s="17">
+        <f t="shared" si="0"/>
+        <v>0.65650000000000008</v>
+      </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="8" t="s">
@@ -1944,7 +2001,13 @@
       <c r="K17">
         <v>0.67</v>
       </c>
-      <c r="M17" s="6"/>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" s="17">
+        <f t="shared" si="0"/>
+        <v>0.77600000000000002</v>
+      </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="8" t="s">
@@ -1983,7 +2046,10 @@
       <c r="L18">
         <v>0.59</v>
       </c>
-      <c r="M18" s="6"/>
+      <c r="M18" s="17">
+        <f t="shared" si="0"/>
+        <v>0.64149999999999996</v>
+      </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="7" t="s">
@@ -2022,7 +2088,10 @@
       <c r="L19">
         <v>0.68</v>
       </c>
-      <c r="M19" s="6"/>
+      <c r="M19" s="17">
+        <f t="shared" si="0"/>
+        <v>0.52449999999999997</v>
+      </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="8" t="s">
@@ -2061,7 +2130,10 @@
       <c r="L20">
         <v>0.62</v>
       </c>
-      <c r="M20" s="6"/>
+      <c r="M20" s="17">
+        <f t="shared" si="0"/>
+        <v>0.80950000000000011</v>
+      </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="7" t="s">
@@ -2097,7 +2169,13 @@
       <c r="K21">
         <v>0.85</v>
       </c>
-      <c r="M21" s="6"/>
+      <c r="L21">
+        <v>0.62</v>
+      </c>
+      <c r="M21" s="17">
+        <f t="shared" si="0"/>
+        <v>0.85050000000000003</v>
+      </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
@@ -2136,7 +2214,10 @@
       <c r="L22">
         <v>0.62</v>
       </c>
-      <c r="M22" s="6"/>
+      <c r="M22" s="17">
+        <f t="shared" si="0"/>
+        <v>0.76300000000000001</v>
+      </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="8" t="s">
@@ -2172,7 +2253,13 @@
       <c r="K23">
         <v>0.67</v>
       </c>
-      <c r="M23" s="6"/>
+      <c r="L23">
+        <v>0.68</v>
+      </c>
+      <c r="M23" s="17">
+        <f t="shared" si="0"/>
+        <v>0.68199999999999994</v>
+      </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="7" t="s">
@@ -2211,7 +2298,10 @@
       <c r="L24">
         <v>0.85</v>
       </c>
-      <c r="M24" s="6"/>
+      <c r="M24" s="17">
+        <f t="shared" si="0"/>
+        <v>0.79500000000000015</v>
+      </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
@@ -2250,7 +2340,10 @@
       <c r="L25">
         <v>0.74</v>
       </c>
-      <c r="M25" s="6"/>
+      <c r="M25" s="17">
+        <f t="shared" si="0"/>
+        <v>0.70300000000000007</v>
+      </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="8" t="s">
@@ -2289,7 +2382,10 @@
       <c r="L26">
         <v>0.68</v>
       </c>
-      <c r="M26" s="6"/>
+      <c r="M26" s="17">
+        <f t="shared" si="0"/>
+        <v>0.71750000000000003</v>
+      </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="7" t="s">
@@ -2328,7 +2424,10 @@
       <c r="L27">
         <v>0.68</v>
       </c>
-      <c r="M27" s="6"/>
+      <c r="M27" s="17">
+        <f t="shared" si="0"/>
+        <v>0.64450000000000007</v>
+      </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
@@ -2367,7 +2466,10 @@
       <c r="L28">
         <v>0.68</v>
       </c>
-      <c r="M28" s="6"/>
+      <c r="M28" s="17">
+        <f t="shared" si="0"/>
+        <v>0.72</v>
+      </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="8" t="s">
@@ -2406,7 +2508,10 @@
       <c r="L29">
         <v>0.62</v>
       </c>
-      <c r="M29" s="6"/>
+      <c r="M29" s="17">
+        <f t="shared" si="0"/>
+        <v>0.73950000000000005</v>
+      </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="7" t="s">
@@ -2445,7 +2550,10 @@
       <c r="L30">
         <v>0.68</v>
       </c>
-      <c r="M30" s="6"/>
+      <c r="M30" s="17">
+        <f t="shared" si="0"/>
+        <v>0.74949999999999994</v>
+      </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="8" t="s">
@@ -2481,7 +2589,13 @@
       <c r="K31">
         <v>0.88</v>
       </c>
-      <c r="M31" s="6"/>
+      <c r="L31">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M31" s="17">
+        <f t="shared" si="0"/>
+        <v>0.78049999999999997</v>
+      </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="7" t="s">
@@ -2520,7 +2634,10 @@
       <c r="L32">
         <v>0.62</v>
       </c>
-      <c r="M32" s="6"/>
+      <c r="M32" s="17">
+        <f t="shared" si="0"/>
+        <v>0.61750000000000005</v>
+      </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="7" t="s">
@@ -2559,7 +2676,10 @@
       <c r="L33">
         <v>0.62</v>
       </c>
-      <c r="M33" s="6"/>
+      <c r="M33" s="17">
+        <f t="shared" si="0"/>
+        <v>0.63200000000000001</v>
+      </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="14" t="s">
@@ -2595,7 +2715,13 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="6"/>
+      <c r="L34">
+        <v>0.47</v>
+      </c>
+      <c r="M34" s="17">
+        <f t="shared" si="0"/>
+        <v>0.66300000000000003</v>
+      </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="9" t="s">
@@ -2634,7 +2760,10 @@
       <c r="L35">
         <v>0.74</v>
       </c>
-      <c r="M35" s="6"/>
+      <c r="M35" s="17">
+        <f t="shared" si="0"/>
+        <v>0.61499999999999999</v>
+      </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="8" t="s">
@@ -2673,7 +2802,10 @@
       <c r="L36">
         <v>0.76</v>
       </c>
-      <c r="M36" s="6"/>
+      <c r="M36" s="17">
+        <f t="shared" si="0"/>
+        <v>0.83749999999999991</v>
+      </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="14" t="s">
@@ -2712,7 +2844,10 @@
       <c r="L37">
         <v>0.62</v>
       </c>
-      <c r="M37" s="6"/>
+      <c r="M37" s="17">
+        <f t="shared" si="0"/>
+        <v>0.72950000000000004</v>
+      </c>
     </row>
     <row r="38" spans="1:13" ht="20">
       <c r="A38" s="10" t="s">
@@ -2748,7 +2883,13 @@
       <c r="K38">
         <v>0.77</v>
       </c>
-      <c r="M38" s="6"/>
+      <c r="L38">
+        <v>0.5</v>
+      </c>
+      <c r="M38" s="17">
+        <f t="shared" si="0"/>
+        <v>0.70599999999999996</v>
+      </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="8" t="s">
@@ -2787,7 +2928,10 @@
       <c r="L39">
         <v>0.68</v>
       </c>
-      <c r="M39" s="6"/>
+      <c r="M39" s="17">
+        <f t="shared" si="0"/>
+        <v>0.84350000000000003</v>
+      </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="7" t="s">
@@ -2826,7 +2970,10 @@
       <c r="L40">
         <v>0.62</v>
       </c>
-      <c r="M40" s="6"/>
+      <c r="M40" s="17">
+        <f t="shared" si="0"/>
+        <v>0.79400000000000004</v>
+      </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="8" t="s">
@@ -2862,7 +3009,13 @@
       <c r="K41">
         <v>0</v>
       </c>
-      <c r="M41" s="6"/>
+      <c r="L41">
+        <v>0.68</v>
+      </c>
+      <c r="M41" s="17">
+        <f t="shared" si="0"/>
+        <v>0.76200000000000001</v>
+      </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="8" t="s">
@@ -2901,7 +3054,10 @@
       <c r="L42">
         <v>0.53</v>
       </c>
-      <c r="M42" s="6"/>
+      <c r="M42" s="17">
+        <f t="shared" si="0"/>
+        <v>0.6885</v>
+      </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="7" t="s">
@@ -2937,7 +3093,13 @@
       <c r="K43">
         <v>0.83</v>
       </c>
-      <c r="M43" s="6"/>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" s="17">
+        <f t="shared" si="0"/>
+        <v>0.78700000000000014</v>
+      </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="7" t="s">
@@ -2976,7 +3138,10 @@
       <c r="L44">
         <v>0.65</v>
       </c>
-      <c r="M44" s="6"/>
+      <c r="M44" s="17">
+        <f t="shared" si="0"/>
+        <v>0.70599999999999996</v>
+      </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="12" t="s">
@@ -3015,7 +3180,10 @@
       <c r="L45">
         <v>0.59</v>
       </c>
-      <c r="M45" s="6"/>
+      <c r="M45" s="17">
+        <f t="shared" si="0"/>
+        <v>0.81150000000000011</v>
+      </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="12" t="s">
@@ -3054,7 +3222,10 @@
       <c r="L46">
         <v>1</v>
       </c>
-      <c r="M46" s="6"/>
+      <c r="M46" s="17">
+        <f t="shared" si="0"/>
+        <v>0.76400000000000001</v>
+      </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="11" t="s">
@@ -3093,7 +3264,10 @@
       <c r="L47">
         <v>0.68</v>
       </c>
-      <c r="M47" s="6"/>
+      <c r="M47" s="17">
+        <f t="shared" si="0"/>
+        <v>0.83199999999999996</v>
+      </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="11" t="s">
@@ -3129,7 +3303,13 @@
       <c r="K48">
         <v>0.94</v>
       </c>
-      <c r="M48" s="6"/>
+      <c r="L48">
+        <v>0.47</v>
+      </c>
+      <c r="M48" s="17">
+        <f t="shared" si="0"/>
+        <v>0.78350000000000009</v>
+      </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="11" t="s">
@@ -3168,7 +3348,10 @@
       <c r="L49">
         <v>0.28999999999999998</v>
       </c>
-      <c r="M49" s="6"/>
+      <c r="M49" s="17">
+        <f t="shared" si="0"/>
+        <v>0.70700000000000007</v>
+      </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="11" t="s">
@@ -3204,7 +3387,13 @@
       <c r="K50">
         <v>0</v>
       </c>
-      <c r="M50" s="6"/>
+      <c r="L50">
+        <v>0.68</v>
+      </c>
+      <c r="M50" s="17">
+        <f t="shared" si="0"/>
+        <v>0.56950000000000001</v>
+      </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="11" t="s">
@@ -3243,7 +3432,10 @@
       <c r="L51">
         <v>0.68</v>
       </c>
-      <c r="M51" s="6"/>
+      <c r="M51" s="17">
+        <f t="shared" si="0"/>
+        <v>0.8839999999999999</v>
+      </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="11" t="s">
@@ -3282,7 +3474,10 @@
       <c r="L52">
         <v>0.5</v>
       </c>
-      <c r="M52" s="6"/>
+      <c r="M52" s="17">
+        <f t="shared" si="0"/>
+        <v>0.7629999999999999</v>
+      </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="11" t="s">
@@ -3318,7 +3513,13 @@
       <c r="K53">
         <v>0</v>
       </c>
-      <c r="M53" s="6"/>
+      <c r="L53">
+        <v>0.59</v>
+      </c>
+      <c r="M53" s="17">
+        <f t="shared" si="0"/>
+        <v>0.76</v>
+      </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="11" t="s">
@@ -3357,7 +3558,10 @@
       <c r="L54">
         <v>0.5</v>
       </c>
-      <c r="M54" s="6"/>
+      <c r="M54" s="17">
+        <f t="shared" si="0"/>
+        <v>0.625</v>
+      </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="11" t="s">
@@ -3396,7 +3600,10 @@
       <c r="L55">
         <v>0.68</v>
       </c>
-      <c r="M55" s="6"/>
+      <c r="M55" s="17">
+        <f t="shared" si="0"/>
+        <v>0.83549999999999991</v>
+      </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="11" t="s">
@@ -3432,7 +3639,13 @@
       <c r="K56">
         <v>0.65</v>
       </c>
-      <c r="M56" s="6"/>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" s="17">
+        <f t="shared" si="0"/>
+        <v>0.72650000000000003</v>
+      </c>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="11" t="s">

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCE3CABD-6EBA-9E47-9734-21385A36AD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3651B49-4AC6-474F-9526-CBB49BD238C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1504,8 +1504,7 @@
         <v>0.5</v>
       </c>
       <c r="M5" s="17">
-        <f t="shared" si="0"/>
-        <v>0.49450000000000005</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3678,6 +3677,9 @@
       <c r="J57">
         <v>0.86</v>
       </c>
+      <c r="K57">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
@@ -4206,6 +4208,9 @@
       <c r="J73">
         <v>0.81</v>
       </c>
+      <c r="K73">
+        <v>0.91</v>
+      </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
@@ -4635,6 +4640,9 @@
       <c r="J86">
         <v>0.86</v>
       </c>
+      <c r="K86">
+        <v>0.91</v>
+      </c>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
@@ -4800,6 +4808,9 @@
       <c r="J91">
         <v>0.75</v>
       </c>
+      <c r="K91">
+        <v>0.63</v>
+      </c>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
@@ -5031,6 +5042,9 @@
       <c r="J98">
         <v>0.92</v>
       </c>
+      <c r="K98">
+        <v>0.94</v>
+      </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
@@ -5424,6 +5438,9 @@
       </c>
       <c r="J110">
         <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0.74</v>
       </c>
       <c r="M110" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3651B49-4AC6-474F-9526-CBB49BD238C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59ADA85A-071C-524B-9858-3FC006734904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2460,14 +2460,14 @@
         <v>0.94</v>
       </c>
       <c r="K28">
-        <v>0.48</v>
+        <v>0.91</v>
       </c>
       <c r="L28">
         <v>0.68</v>
       </c>
       <c r="M28" s="17">
         <f t="shared" si="0"/>
-        <v>0.72</v>
+        <v>0.75449999999999995</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -3048,14 +3048,14 @@
         <v>0.91</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="L42">
         <v>0.53</v>
       </c>
       <c r="M42" s="17">
         <f t="shared" si="0"/>
-        <v>0.6885</v>
+        <v>0.73649999999999993</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -3216,14 +3216,14 @@
         <v>0.59</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="L46">
         <v>1</v>
       </c>
       <c r="M46" s="17">
         <f t="shared" si="0"/>
-        <v>0.76400000000000001</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -3384,14 +3384,14 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="L50">
         <v>0.68</v>
       </c>
       <c r="M50" s="17">
         <f t="shared" si="0"/>
-        <v>0.56950000000000001</v>
+        <v>0.70150000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:13">

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59ADA85A-071C-524B-9858-3FC006734904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28F8DF8-D6AA-3742-9F1D-D3FB59DB160F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3746,6 +3746,9 @@
       <c r="J59">
         <v>0.72</v>
       </c>
+      <c r="K59">
+        <v>0.91</v>
+      </c>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
@@ -3944,6 +3947,9 @@
       <c r="J65">
         <v>0.67</v>
       </c>
+      <c r="K65">
+        <v>0.43</v>
+      </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
@@ -3977,6 +3983,9 @@
       <c r="J66">
         <v>0.83</v>
       </c>
+      <c r="K66">
+        <v>0.89</v>
+      </c>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
@@ -4010,6 +4019,9 @@
       <c r="J67">
         <v>0</v>
       </c>
+      <c r="K67">
+        <v>0.46</v>
+      </c>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
@@ -4043,6 +4055,9 @@
       <c r="J68">
         <v>0.69</v>
       </c>
+      <c r="K68">
+        <v>0.66</v>
+      </c>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
@@ -4109,6 +4124,9 @@
       <c r="J70">
         <v>0.86</v>
       </c>
+      <c r="K70">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
@@ -4277,6 +4295,9 @@
       <c r="J75">
         <v>0.53</v>
       </c>
+      <c r="K75">
+        <v>0.46</v>
+      </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
@@ -4310,6 +4331,9 @@
       <c r="J76">
         <v>0.78</v>
       </c>
+      <c r="K76">
+        <v>0.91</v>
+      </c>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
@@ -4376,6 +4400,9 @@
       <c r="J78">
         <v>0.94</v>
       </c>
+      <c r="K78">
+        <v>0.91</v>
+      </c>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
@@ -4475,6 +4502,9 @@
       <c r="J81">
         <v>0.69</v>
       </c>
+      <c r="K81">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
@@ -4508,6 +4538,9 @@
       <c r="J82">
         <v>0</v>
       </c>
+      <c r="K82">
+        <v>0.66</v>
+      </c>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
@@ -4574,6 +4607,9 @@
       <c r="J84">
         <v>0.78</v>
       </c>
+      <c r="K84">
+        <v>0.31</v>
+      </c>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
@@ -4607,6 +4643,9 @@
       <c r="J85">
         <v>0.86</v>
       </c>
+      <c r="K85">
+        <v>0.74</v>
+      </c>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
@@ -4709,6 +4748,9 @@
       <c r="J88">
         <v>0.83</v>
       </c>
+      <c r="K88">
+        <v>0.69</v>
+      </c>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
@@ -4742,6 +4784,9 @@
       <c r="J89">
         <v>0.75</v>
       </c>
+      <c r="K89">
+        <v>0.49</v>
+      </c>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
@@ -4775,6 +4820,9 @@
       <c r="J90">
         <v>0.81</v>
       </c>
+      <c r="K90">
+        <v>0.63</v>
+      </c>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
@@ -4844,6 +4892,9 @@
       <c r="J92">
         <v>0.83</v>
       </c>
+      <c r="K92">
+        <v>0.71</v>
+      </c>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
@@ -4877,6 +4928,9 @@
       <c r="J93">
         <v>0.83</v>
       </c>
+      <c r="K93">
+        <v>0.74</v>
+      </c>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
@@ -4910,6 +4964,9 @@
       <c r="J94">
         <v>0.78</v>
       </c>
+      <c r="K94">
+        <v>0.66</v>
+      </c>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
@@ -4943,6 +5000,9 @@
       <c r="J95">
         <v>0.83</v>
       </c>
+      <c r="K95">
+        <v>0.94</v>
+      </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
@@ -4976,6 +5036,9 @@
       <c r="J96">
         <v>0.86</v>
       </c>
+      <c r="K96">
+        <v>0.8</v>
+      </c>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
@@ -5009,6 +5072,9 @@
       <c r="J97">
         <v>0</v>
       </c>
+      <c r="K97">
+        <v>0.97</v>
+      </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
@@ -5144,6 +5210,9 @@
       <c r="J101">
         <v>0.81</v>
       </c>
+      <c r="K101">
+        <v>0.63</v>
+      </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
@@ -5243,6 +5312,9 @@
       <c r="J104">
         <v>0.89</v>
       </c>
+      <c r="K104">
+        <v>0.17</v>
+      </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
@@ -5340,6 +5412,9 @@
       <c r="J107">
         <v>0.81</v>
       </c>
+      <c r="K107">
+        <v>0.71</v>
+      </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
@@ -5373,6 +5448,9 @@
       <c r="J108">
         <v>0.92</v>
       </c>
+      <c r="K108">
+        <v>0.89</v>
+      </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
@@ -5405,6 +5483,9 @@
       </c>
       <c r="J109">
         <v>0.89</v>
+      </c>
+      <c r="K109">
+        <v>0.66</v>
       </c>
       <c r="M109" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28F8DF8-D6AA-3742-9F1D-D3FB59DB160F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205EAD6C-128B-9943-9C76-CC3E40461491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -3713,6 +3713,9 @@
       <c r="J58">
         <v>0.94</v>
       </c>
+      <c r="K58">
+        <v>0.94</v>
+      </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
@@ -3782,6 +3785,9 @@
       <c r="J60">
         <v>0.72</v>
       </c>
+      <c r="K60">
+        <v>0.77</v>
+      </c>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
@@ -3815,6 +3821,9 @@
       <c r="J61">
         <v>0.86</v>
       </c>
+      <c r="K61">
+        <v>0.69</v>
+      </c>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
@@ -3848,6 +3857,9 @@
       <c r="J62">
         <v>0.94</v>
       </c>
+      <c r="K62">
+        <v>0.91</v>
+      </c>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
@@ -3881,6 +3893,9 @@
       <c r="J63">
         <v>0.81</v>
       </c>
+      <c r="K63">
+        <v>0.66</v>
+      </c>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
@@ -3914,6 +3929,9 @@
       <c r="J64">
         <v>0.94</v>
       </c>
+      <c r="K64">
+        <v>0.69</v>
+      </c>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
@@ -4091,6 +4109,9 @@
       <c r="J69">
         <v>0.83</v>
       </c>
+      <c r="K69">
+        <v>0.71</v>
+      </c>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
@@ -4160,6 +4181,9 @@
       <c r="J71">
         <v>0.72</v>
       </c>
+      <c r="K71">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
@@ -4193,6 +4217,9 @@
       <c r="J72">
         <v>0.69</v>
       </c>
+      <c r="K72">
+        <v>0.6</v>
+      </c>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
@@ -4262,6 +4289,9 @@
       <c r="J74">
         <v>0.86</v>
       </c>
+      <c r="K74">
+        <v>0.8</v>
+      </c>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
@@ -4367,6 +4397,9 @@
       <c r="J77">
         <v>0.94</v>
       </c>
+      <c r="K77">
+        <v>0.69</v>
+      </c>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
@@ -4436,6 +4469,9 @@
       <c r="J79">
         <v>0.89</v>
       </c>
+      <c r="K79">
+        <v>0.91</v>
+      </c>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
@@ -4469,6 +4505,9 @@
       <c r="J80">
         <v>0.86</v>
       </c>
+      <c r="K80">
+        <v>0.91</v>
+      </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
@@ -4574,6 +4613,9 @@
       <c r="J83">
         <v>0</v>
       </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
@@ -4715,6 +4757,9 @@
       <c r="J87">
         <v>0.83</v>
       </c>
+      <c r="K87">
+        <v>0.77</v>
+      </c>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
@@ -5144,6 +5189,9 @@
       <c r="J99">
         <v>0.92</v>
       </c>
+      <c r="K99">
+        <v>0.66</v>
+      </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
@@ -5177,6 +5225,9 @@
       <c r="J100">
         <v>0.92</v>
       </c>
+      <c r="K100">
+        <v>0.66</v>
+      </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
@@ -5246,6 +5297,9 @@
       <c r="J102">
         <v>0.81</v>
       </c>
+      <c r="K102">
+        <v>0.71</v>
+      </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
@@ -5279,6 +5333,9 @@
       <c r="J103">
         <v>0.69</v>
       </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
@@ -5346,6 +5403,9 @@
       <c r="J105">
         <v>0</v>
       </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
@@ -5379,6 +5439,9 @@
       <c r="J106">
         <v>0.83</v>
       </c>
+      <c r="K106">
+        <v>0.77</v>
+      </c>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
@@ -5555,6 +5618,9 @@
       </c>
       <c r="J111">
         <v>0.79</v>
+      </c>
+      <c r="K111">
+        <v>0.74</v>
       </c>
       <c r="M111" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205EAD6C-128B-9943-9C76-CC3E40461491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CD800F-9E13-2D4E-972B-863AD6B94BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1378,7 +1378,7 @@
         <v>0.88</v>
       </c>
       <c r="M2" s="17">
-        <f t="shared" ref="M2:M56" si="0">(((LARGE(D2:F2,1)+LARGE(D2:F2,2))*0.2/2+(LARGE(G2:I2,1)+LARGE(G2:I2,2))*0.5/2+(LARGE(J2:L2,1)+LARGE(J2:L2,2))*0.3/2))</f>
+        <f t="shared" ref="M2:M65" si="0">(((LARGE(D2:F2,1)+LARGE(D2:F2,2))*0.2/2+(LARGE(G2:I2,1)+LARGE(G2:I2,2))*0.5/2+(LARGE(J2:L2,1)+LARGE(J2:L2,2))*0.3/2))</f>
         <v>0.70450000000000002</v>
       </c>
     </row>
@@ -3680,7 +3680,13 @@
       <c r="K57">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M57" s="6"/>
+      <c r="L57">
+        <v>0.54</v>
+      </c>
+      <c r="M57" s="17">
+        <f t="shared" si="0"/>
+        <v>0.71750000000000003</v>
+      </c>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="11" t="s">
@@ -3716,7 +3722,13 @@
       <c r="K58">
         <v>0.94</v>
       </c>
-      <c r="M58" s="6"/>
+      <c r="L58">
+        <v>0.59</v>
+      </c>
+      <c r="M58" s="17">
+        <f t="shared" si="0"/>
+        <v>0.81699999999999995</v>
+      </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="11" t="s">
@@ -3752,7 +3764,13 @@
       <c r="K59">
         <v>0.91</v>
       </c>
-      <c r="M59" s="6"/>
+      <c r="L59">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M59" s="17">
+        <f t="shared" si="0"/>
+        <v>0.73450000000000004</v>
+      </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="11" t="s">
@@ -3788,7 +3806,10 @@
       <c r="K60">
         <v>0.77</v>
       </c>
-      <c r="M60" s="6"/>
+      <c r="M60" s="17">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="11" t="s">
@@ -3824,7 +3845,13 @@
       <c r="K61">
         <v>0.69</v>
       </c>
-      <c r="M61" s="6"/>
+      <c r="L61">
+        <v>0.51</v>
+      </c>
+      <c r="M61" s="17">
+        <f t="shared" si="0"/>
+        <v>0.69850000000000001</v>
+      </c>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="11" t="s">
@@ -3860,7 +3887,13 @@
       <c r="K62">
         <v>0.91</v>
       </c>
-      <c r="M62" s="6"/>
+      <c r="L62">
+        <v>0.46</v>
+      </c>
+      <c r="M62" s="17">
+        <f t="shared" si="0"/>
+        <v>0.69199999999999995</v>
+      </c>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="11" t="s">
@@ -3896,7 +3929,13 @@
       <c r="K63">
         <v>0.66</v>
       </c>
-      <c r="M63" s="6"/>
+      <c r="L63">
+        <v>0.59</v>
+      </c>
+      <c r="M63" s="17">
+        <f t="shared" si="0"/>
+        <v>0.73299999999999998</v>
+      </c>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="11" t="s">
@@ -3932,7 +3971,13 @@
       <c r="K64">
         <v>0.69</v>
       </c>
-      <c r="M64" s="6"/>
+      <c r="L64">
+        <v>0.54</v>
+      </c>
+      <c r="M64" s="17">
+        <f t="shared" si="0"/>
+        <v>0.76800000000000002</v>
+      </c>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="11" t="s">
@@ -3968,7 +4013,10 @@
       <c r="K65">
         <v>0.43</v>
       </c>
-      <c r="M65" s="6"/>
+      <c r="M65" s="17">
+        <f t="shared" si="0"/>
+        <v>0.64200000000000002</v>
+      </c>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="11" t="s">
@@ -4004,7 +4052,13 @@
       <c r="K66">
         <v>0.89</v>
       </c>
-      <c r="M66" s="6"/>
+      <c r="L66">
+        <v>0.49</v>
+      </c>
+      <c r="M66" s="17">
+        <f t="shared" ref="M66:M111" si="1">(((LARGE(D66:F66,1)+LARGE(D66:F66,2))*0.2/2+(LARGE(G66:I66,1)+LARGE(G66:I66,2))*0.5/2+(LARGE(J66:L66,1)+LARGE(J66:L66,2))*0.3/2))</f>
+        <v>0.76300000000000001</v>
+      </c>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="11" t="s">
@@ -4040,7 +4094,13 @@
       <c r="K67">
         <v>0.46</v>
       </c>
-      <c r="M67" s="6"/>
+      <c r="L67">
+        <v>0.41</v>
+      </c>
+      <c r="M67" s="17">
+        <f t="shared" si="1"/>
+        <v>0.52100000000000013</v>
+      </c>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="11" t="s">
@@ -4076,7 +4136,13 @@
       <c r="K68">
         <v>0.66</v>
       </c>
-      <c r="M68" s="6"/>
+      <c r="L68">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M68" s="17">
+        <f t="shared" si="1"/>
+        <v>0.63200000000000001</v>
+      </c>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="11" t="s">
@@ -4112,7 +4178,13 @@
       <c r="K69">
         <v>0.71</v>
       </c>
-      <c r="M69" s="6"/>
+      <c r="L69">
+        <v>0.51</v>
+      </c>
+      <c r="M69" s="17">
+        <f t="shared" si="1"/>
+        <v>0.69350000000000001</v>
+      </c>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="11" t="s">
@@ -4148,7 +4220,13 @@
       <c r="K70">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M70" s="6"/>
+      <c r="L70">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M70" s="17">
+        <f t="shared" si="1"/>
+        <v>0.59850000000000003</v>
+      </c>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="11" t="s">
@@ -4184,7 +4262,13 @@
       <c r="K71">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M71" s="6"/>
+      <c r="L71">
+        <v>0.59</v>
+      </c>
+      <c r="M71" s="17">
+        <f t="shared" si="1"/>
+        <v>0.57150000000000001</v>
+      </c>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="11" t="s">
@@ -4220,7 +4304,10 @@
       <c r="K72">
         <v>0.6</v>
       </c>
-      <c r="M72" s="6"/>
+      <c r="M72" s="17">
+        <f t="shared" si="1"/>
+        <v>0.52249999999999996</v>
+      </c>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="11" t="s">
@@ -4256,7 +4343,10 @@
       <c r="K73">
         <v>0.91</v>
       </c>
-      <c r="M73" s="6"/>
+      <c r="M73" s="17">
+        <f t="shared" si="1"/>
+        <v>0.6895</v>
+      </c>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="11" t="s">
@@ -4292,7 +4382,13 @@
       <c r="K74">
         <v>0.8</v>
       </c>
-      <c r="M74" s="6"/>
+      <c r="L74">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M74" s="17">
+        <f t="shared" si="1"/>
+        <v>0.73</v>
+      </c>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="11" t="s">
@@ -4328,7 +4424,10 @@
       <c r="K75">
         <v>0.46</v>
       </c>
-      <c r="M75" s="6"/>
+      <c r="M75" s="17">
+        <f t="shared" si="1"/>
+        <v>0.55599999999999994</v>
+      </c>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="11" t="s">
@@ -4364,7 +4463,13 @@
       <c r="K76">
         <v>0.91</v>
       </c>
-      <c r="M76" s="6"/>
+      <c r="L76">
+        <v>0.54</v>
+      </c>
+      <c r="M76" s="17">
+        <f t="shared" si="1"/>
+        <v>0.63100000000000001</v>
+      </c>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="11" t="s">
@@ -4400,7 +4505,10 @@
       <c r="K77">
         <v>0.69</v>
       </c>
-      <c r="M77" s="6"/>
+      <c r="M77" s="17">
+        <f t="shared" si="1"/>
+        <v>0.83099999999999996</v>
+      </c>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="11" t="s">
@@ -4436,7 +4544,10 @@
       <c r="K78">
         <v>0.91</v>
       </c>
-      <c r="M78" s="6"/>
+      <c r="M78" s="17">
+        <f t="shared" si="1"/>
+        <v>0.57499999999999996</v>
+      </c>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="11" t="s">
@@ -4472,7 +4583,13 @@
       <c r="K79">
         <v>0.91</v>
       </c>
-      <c r="M79" s="6"/>
+      <c r="L79">
+        <v>0.65</v>
+      </c>
+      <c r="M79" s="17">
+        <f t="shared" si="1"/>
+        <v>0.85200000000000009</v>
+      </c>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="11" t="s">
@@ -4508,7 +4625,13 @@
       <c r="K80">
         <v>0.91</v>
       </c>
-      <c r="M80" s="6"/>
+      <c r="L80">
+        <v>0.54</v>
+      </c>
+      <c r="M80" s="17">
+        <f t="shared" si="1"/>
+        <v>0.72550000000000003</v>
+      </c>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" t="s">
@@ -4544,7 +4667,13 @@
       <c r="K81">
         <v>0.56999999999999995</v>
       </c>
-      <c r="M81" s="6"/>
+      <c r="L81">
+        <v>0.43</v>
+      </c>
+      <c r="M81" s="17">
+        <f t="shared" si="1"/>
+        <v>0.54149999999999998</v>
+      </c>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="11" t="s">
@@ -4580,7 +4709,10 @@
       <c r="K82">
         <v>0.66</v>
       </c>
-      <c r="M82" s="6"/>
+      <c r="M82" s="17">
+        <f t="shared" si="1"/>
+        <v>0.48299999999999998</v>
+      </c>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="11" t="s">
@@ -4616,7 +4748,10 @@
       <c r="K83">
         <v>0</v>
       </c>
-      <c r="M83" s="6"/>
+      <c r="M83" s="17">
+        <f t="shared" si="1"/>
+        <v>0.1875</v>
+      </c>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="11" t="s">
@@ -4652,7 +4787,13 @@
       <c r="K84">
         <v>0.31</v>
       </c>
-      <c r="M84" s="6"/>
+      <c r="L84">
+        <v>0.43</v>
+      </c>
+      <c r="M84" s="17">
+        <f t="shared" si="1"/>
+        <v>0.68399999999999994</v>
+      </c>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="11" t="s">
@@ -4688,7 +4829,13 @@
       <c r="K85">
         <v>0.74</v>
       </c>
-      <c r="M85" s="6"/>
+      <c r="L85">
+        <v>0.73</v>
+      </c>
+      <c r="M85" s="17">
+        <f t="shared" si="1"/>
+        <v>0.69750000000000001</v>
+      </c>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="11" t="s">
@@ -4724,7 +4871,13 @@
       <c r="K86">
         <v>0.91</v>
       </c>
-      <c r="M86" s="6"/>
+      <c r="L86">
+        <v>0.62</v>
+      </c>
+      <c r="M86" s="17">
+        <f t="shared" si="1"/>
+        <v>0.76800000000000002</v>
+      </c>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="11" t="s">
@@ -4760,7 +4913,13 @@
       <c r="K87">
         <v>0.77</v>
       </c>
-      <c r="M87" s="6"/>
+      <c r="L87">
+        <v>0.54</v>
+      </c>
+      <c r="M87" s="17">
+        <f t="shared" si="1"/>
+        <v>0.78749999999999998</v>
+      </c>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="11" t="s">
@@ -4796,7 +4955,10 @@
       <c r="K88">
         <v>0.69</v>
       </c>
-      <c r="M88" s="6"/>
+      <c r="M88" s="17">
+        <f t="shared" si="1"/>
+        <v>0.78299999999999992</v>
+      </c>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="11" t="s">
@@ -4832,7 +4994,13 @@
       <c r="K89">
         <v>0.49</v>
       </c>
-      <c r="M89" s="6"/>
+      <c r="L89">
+        <v>0.59</v>
+      </c>
+      <c r="M89" s="17">
+        <f t="shared" si="1"/>
+        <v>0.74399999999999999</v>
+      </c>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="11" t="s">
@@ -4868,7 +5036,10 @@
       <c r="K90">
         <v>0.63</v>
       </c>
-      <c r="M90" s="6"/>
+      <c r="M90" s="17">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="11" t="s">
@@ -4904,7 +5075,13 @@
       <c r="K91">
         <v>0.63</v>
       </c>
-      <c r="M91" s="6"/>
+      <c r="L91">
+        <v>0.64</v>
+      </c>
+      <c r="M91" s="17">
+        <f t="shared" si="1"/>
+        <v>0.66050000000000009</v>
+      </c>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="11" t="s">
@@ -4940,7 +5117,10 @@
       <c r="K92">
         <v>0.71</v>
       </c>
-      <c r="M92" s="6"/>
+      <c r="M92" s="17">
+        <f t="shared" si="1"/>
+        <v>0.7044999999999999</v>
+      </c>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="11" t="s">
@@ -4976,7 +5156,13 @@
       <c r="K93">
         <v>0.74</v>
       </c>
-      <c r="M93" s="6"/>
+      <c r="L93">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M93" s="17">
+        <f t="shared" si="1"/>
+        <v>0.74449999999999994</v>
+      </c>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="11" t="s">
@@ -5012,7 +5198,13 @@
       <c r="K94">
         <v>0.66</v>
       </c>
-      <c r="M94" s="6"/>
+      <c r="L94">
+        <v>0.54</v>
+      </c>
+      <c r="M94" s="17">
+        <f t="shared" si="1"/>
+        <v>0.67400000000000004</v>
+      </c>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="11" t="s">
@@ -5048,7 +5240,13 @@
       <c r="K95">
         <v>0.94</v>
       </c>
-      <c r="M95" s="6"/>
+      <c r="L95">
+        <v>0.59</v>
+      </c>
+      <c r="M95" s="17">
+        <f t="shared" si="1"/>
+        <v>0.81550000000000011</v>
+      </c>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="11" t="s">
@@ -5084,7 +5282,13 @@
       <c r="K96">
         <v>0.8</v>
       </c>
-      <c r="M96" s="6"/>
+      <c r="L96">
+        <v>0.54</v>
+      </c>
+      <c r="M96" s="17">
+        <f t="shared" si="1"/>
+        <v>0.74350000000000005</v>
+      </c>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="11" t="s">
@@ -5120,7 +5324,10 @@
       <c r="K97">
         <v>0.97</v>
       </c>
-      <c r="M97" s="6"/>
+      <c r="M97" s="17">
+        <f t="shared" si="1"/>
+        <v>0.58550000000000002</v>
+      </c>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="11" t="s">
@@ -5156,7 +5363,13 @@
       <c r="K98">
         <v>0.94</v>
       </c>
-      <c r="M98" s="6"/>
+      <c r="L98">
+        <v>0.54</v>
+      </c>
+      <c r="M98" s="17">
+        <f t="shared" si="1"/>
+        <v>0.88149999999999995</v>
+      </c>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="11" t="s">
@@ -5192,7 +5405,13 @@
       <c r="K99">
         <v>0.66</v>
       </c>
-      <c r="M99" s="6"/>
+      <c r="L99">
+        <v>0.65</v>
+      </c>
+      <c r="M99" s="17">
+        <f t="shared" si="1"/>
+        <v>0.61450000000000005</v>
+      </c>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="11" t="s">
@@ -5228,7 +5447,13 @@
       <c r="K100">
         <v>0.66</v>
       </c>
-      <c r="M100" s="6"/>
+      <c r="L100">
+        <v>0.59</v>
+      </c>
+      <c r="M100" s="17">
+        <f t="shared" si="1"/>
+        <v>0.63050000000000006</v>
+      </c>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="11" t="s">
@@ -5264,7 +5489,13 @@
       <c r="K101">
         <v>0.63</v>
       </c>
-      <c r="M101" s="6"/>
+      <c r="L101">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M101" s="17">
+        <f t="shared" si="1"/>
+        <v>0.59599999999999997</v>
+      </c>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="11" t="s">
@@ -5300,7 +5531,13 @@
       <c r="K102">
         <v>0.71</v>
       </c>
-      <c r="M102" s="6"/>
+      <c r="L102">
+        <v>0.59</v>
+      </c>
+      <c r="M102" s="17">
+        <f t="shared" si="1"/>
+        <v>0.7629999999999999</v>
+      </c>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="11" t="s">
@@ -5336,7 +5573,13 @@
       <c r="K103">
         <v>0</v>
       </c>
-      <c r="M103" s="6"/>
+      <c r="L103">
+        <v>0.41</v>
+      </c>
+      <c r="M103" s="17">
+        <f t="shared" si="1"/>
+        <v>0.67749999999999999</v>
+      </c>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="11" t="s">
@@ -5372,7 +5615,13 @@
       <c r="K104">
         <v>0.17</v>
       </c>
-      <c r="M104" s="6"/>
+      <c r="L104">
+        <v>0.51</v>
+      </c>
+      <c r="M104" s="17">
+        <f t="shared" si="1"/>
+        <v>0.63749999999999996</v>
+      </c>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="11" t="s">
@@ -5406,7 +5655,10 @@
       <c r="K105">
         <v>0</v>
       </c>
-      <c r="M105" s="6"/>
+      <c r="M105" s="17">
+        <f t="shared" si="1"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="11" t="s">
@@ -5442,7 +5694,13 @@
       <c r="K106">
         <v>0.77</v>
       </c>
-      <c r="M106" s="6"/>
+      <c r="L106">
+        <v>0.59</v>
+      </c>
+      <c r="M106" s="17">
+        <f t="shared" si="1"/>
+        <v>0.74249999999999994</v>
+      </c>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="11" t="s">
@@ -5478,7 +5736,10 @@
       <c r="K107">
         <v>0.71</v>
       </c>
-      <c r="M107" s="6"/>
+      <c r="M107" s="17">
+        <f t="shared" si="1"/>
+        <v>0.78299999999999992</v>
+      </c>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="11" t="s">
@@ -5514,7 +5775,13 @@
       <c r="K108">
         <v>0.89</v>
       </c>
-      <c r="M108" s="6"/>
+      <c r="L108">
+        <v>0.51</v>
+      </c>
+      <c r="M108" s="17">
+        <f t="shared" si="1"/>
+        <v>0.81200000000000006</v>
+      </c>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="11" t="s">
@@ -5550,7 +5817,13 @@
       <c r="K109">
         <v>0.66</v>
       </c>
-      <c r="M109" s="6"/>
+      <c r="L109">
+        <v>0.54</v>
+      </c>
+      <c r="M109" s="17">
+        <f t="shared" si="1"/>
+        <v>0.66300000000000003</v>
+      </c>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="11" t="s">
@@ -5586,7 +5859,13 @@
       <c r="K110">
         <v>0.74</v>
       </c>
-      <c r="M110" s="6"/>
+      <c r="L110">
+        <v>0.6</v>
+      </c>
+      <c r="M110" s="17">
+        <f t="shared" si="1"/>
+        <v>0.64300000000000002</v>
+      </c>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="11" t="s">
@@ -5622,7 +5901,13 @@
       <c r="K111">
         <v>0.74</v>
       </c>
-      <c r="M111" s="6"/>
+      <c r="L111">
+        <v>0.51</v>
+      </c>
+      <c r="M111" s="17">
+        <f t="shared" si="1"/>
+        <v>0.63700000000000001</v>
+      </c>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="11"/>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CD800F-9E13-2D4E-972B-863AD6B94BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37150C45-99FB-4D45-B91D-B26C8E1AC139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26140" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2712,14 +2712,14 @@
         <v>0.89</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="L34">
         <v>0.47</v>
       </c>
       <c r="M34" s="17">
         <f t="shared" si="0"/>
-        <v>0.66300000000000003</v>
+        <v>0.73199999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -3006,14 +3006,14 @@
         <v>0.86</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L41">
         <v>0.68</v>
       </c>
       <c r="M41" s="17">
         <f t="shared" si="0"/>
-        <v>0.76200000000000001</v>
+        <v>0.79500000000000004</v>
       </c>
     </row>
     <row r="42" spans="1:13">
